--- a/equipment/bill-of-materials-draft.xlsx
+++ b/equipment/bill-of-materials-draft.xlsx
@@ -14,15 +14,45 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RF и RSRP" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Покрытие сценарии" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Покрытие помещения" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Портовый план" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Размещение" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DCS сценарии" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Комплектность" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Спецификация'!$A$1:$E$11</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Спецификация'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Спецификация'!$A$1:$E$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Исходный перечень'!$A$1:$D$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Статус'!$A$1:$B$15</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Исходный перечень'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Исходный перечень'!$A$1:$D$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Статус'!$A$1:$B$17</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Статус'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Статус'!$A$1:$B$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Трассы'!$A$1:$F$45</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Трассы'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Трассы'!$A$1:$F$45</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'RF и RSRP'!$A$1:$F$385</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'RF и RSRP'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'RF и RSRP'!$A$1:$F$385</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Покрытие сценарии'!$A$1:$I$28</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Покрытие сценарии'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Покрытие сценарии'!$A$1:$I$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Покрытие помещения'!$A$1:$F$106</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Покрытие помещения'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'Покрытие помещения'!$A$1:$F$106</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Портовый план'!$A$1:$D$138</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="7">'Портовый план'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'Портовый план'!$A$1:$D$138</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Размещение'!$A$1:$E$72</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="8">'Размещение'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">'Размещение'!$A$1:$E$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'DCS сценарии'!$A$1:$F$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="9">'DCS сценарии'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="9">'DCS сценарии'!$A$1:$F$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Комплектность'!$A$1:$C$11</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="10">'Комплектность'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="10">'Комплектность'!$A$1:$C$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,7 +470,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -696,7 +726,7 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
@@ -721,7 +751,7 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
@@ -731,7 +761,359 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:E11"/>
+  <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="45" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Сценарий</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Мощность BCCH дБм</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Доп. потери дБ</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Доля от 2100, %</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Минимум дБм</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Модель ≥95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="21" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>D40_per_TRX</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>97.62342578309377</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>-101.059876113693</v>
+      </c>
+      <c r="F2" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" ht="21" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>D40_total_2TRX_equal</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>36.98970004336019</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>97.62080680807118</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>-104.0701760703328</v>
+      </c>
+      <c r="F3" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" ht="21" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>D30_per_TRX</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>97.59899679855863</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>-111.059876113693</v>
+      </c>
+      <c r="F4" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" ht="21" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>D40_RF_extra3dB</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>97.62080680807118</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>-104.059876113693</v>
+      </c>
+      <c r="F5" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F5"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="100" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="45" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Элемент / требование</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Количество / условие</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Основание и ограничение</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Нагрузки входов, только МТС</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>50 Ом; модели и допустимые мощности не предоставлены, в основную спецификацию не добавлены</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="36" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Нагрузки входов, три LTE-оператора</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Четвёртые входы гибридов B1/B7; отдельного резерва GSM О2/О3 нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="21" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Разъёмы 1/2</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>56 male + 56 female</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Это требуемые исполнения в рамках общей позиции перечня; доступность не подтверждена</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="21" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Разъёмы 7/8</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>44 male + 8 female</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Female на антенных концах для male/male джамперов; переходники не выдуманы</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="21" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>In06 / БС</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Интерфейс не задан</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>4.3-10F на In06 принят как условие стыковки, не характеристика из перечня</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="21" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Объединение двух GSM TRX</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Условно общий RF-порт БС</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>При раздельных выходах нужно дополнительное решение; его модели нет в исходных данных</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>DCS О2 / О3</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Отдельных входов нет</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Три LTE-оператора предусмотрены, полное трёхоператорское использование GSM не подтверждено</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="21" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Удалённое регулирование</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Не выполнено пассивной схемой</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Соответствующих модулей в перечне нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="21" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>PIM −160дБн</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Заявлено для пассивных компонентов в перечне</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Условия измерения, допустимая суммарная мощность и изоляция не предоставлены</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="21" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Пожарное исполнение</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>XLSX: огнестойкое, безгалогеновое; PDF: PE</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Расчёт затухания по PDF не подтверждает требуемую модификацию</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C11"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -739,7 +1121,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1094,7 +1476,9 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:D17"/>
+  <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1102,9 +1486,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1123,7 +1507,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="21" customHeight="1">
+    <row r="2" ht="36" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Проект</t>
@@ -1131,7 +1515,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Рабочий кандидат, не закупочная спецификация и не подтверждённый проект</t>
+          <t>Расчётный вариант финала с явно указанными ограничениями; не комплект для закупки без проверки паспортов и условий монтажа</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1591,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="36" customHeight="1">
+    <row r="9" ht="51" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Разъёмы</t>
@@ -1215,85 +1599,111 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>По два на каждый изготовляемый участок фидера; антенны/устройства/джамперы — 4.3-10, интерфейсы БС не подтверждены</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="36" customHeight="1">
+          <t>По два на каждый ненулевой изготовляемый участок фидера. Для связи с male/male джампером оконечный разъём фидера должен быть female; у делителя — male. Пол разъёмов 1/2 и 7/8 в перечне не задан, доступность модификаций не подтверждена. Интерфейсы БС и In06 также не указаны.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="51" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>109 джамперов</t>
+          <t>115 джамперов</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>18 входов LTE + 1 вход GSM + 2 связи после PC250 + 24 связи PC221→PC211 + 64 антенных. При подключённом только МТС 12 входных связей зарезервированы. Порты БС и пригодность длины 3 м не подтверждены.</t>
+          <t>18 входов LTE + 1 вход GSM + 2 связи после PC250 + 24 связи PC221→PC211 + 64 антенных + 6 местных связей PC250→PC252. При подключённом только МТС 12 входных связей зарезервированы. Порты БС и пригодность длины 3 м не подтверждены.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="51" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>Местные связи</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>F2-1/F3-1/F4-1: геометрическая длина 0 м означает соседние устройства; соединение выполнено джампером 3 м, по два на ID для MIMO. Добавлено 0,2 дБ на путь, собственное допущение. Монтажных фидеров и отдельных разъёмов для этих шести связей нет.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="51" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>GSM-интерфейс</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Один общий RF-выход GSM с двумя TRX принят условно: объединение передатчиков внутри БС не подтверждено. При раздельных RF-выходах требуется дополнительное решение объединения, отсутствующее в исходных данных. Отдельные входы DCS двух других операторов не выделены.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="51" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
           <t>Неиспользуемые порты</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>У B1/B7 гибридов остаются 4 незадействованных входа, а до подключения других операторов ещё 12. Нужны согласованные 50-омные нагрузки: их нет в разрешённом перечне; это открытое несоответствие, не выдуманная позиция спецификации.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="36" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Потери компонентов</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Кроме 6 дБ PC221 и идеального деления паспортные потери не заданы. Использованы сценарные оценки, см. RF-лист.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="36" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Пожарное исполнение</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>XLSX требует огнестойкую безгалогеновую оболочку; PDF описывают PE-варианты. Нужна допустимая модификация.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>ВК</t>
+          <t>Потери компонентов</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Проектная координата (9.2, 31.2); существующая ВК в DWG не найдена. Выделение части 104.2 под аппаратную — собственное решение, не исходное назначение комнаты.</t>
+          <t>Кроме 6 дБ PC221 и идеального деления паспортные потери не заданы. Использованы сценарные оценки, см. RF-лист.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>Пожарное исполнение</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>XLSX требует огнестойкую безгалогеновую оболочку; PDF описывают PE-варианты. Нужна допустимая модификация.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>ВК</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Проектная координата (9.2, 31.2); существующая ВК в DWG не найдена. Выделение части 104.2 под аппаратную — собственное решение, не исходное назначение комнаты.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
           <t>Удалённое управление</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>В перечне нет подходящих управляемых модулей. Пассивная схема не подтверждает требование регулировки на удалённых модулях.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B15"/>
+  <autoFilter ref="A1:B17"/>
+  <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1301,7 +1711,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1510,7 +1920,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>7/8</t>
+          <t>jumper</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
@@ -1524,7 +1934,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Проектная аппроксимация CAD-лотков; без запаса</t>
+          <t>Соседние устройства: два заводских джампера по 3 м; не нулевой фидер</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1972,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>7/8</t>
+          <t>jumper</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
@@ -1576,7 +1986,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Проектная аппроксимация CAD-лотков; без запаса</t>
+          <t>Соседние устройства: два заводских джампера по 3 м; не нулевой фидер</t>
         </is>
       </c>
     </row>
@@ -1614,7 +2024,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>7/8</t>
+          <t>jumper</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
@@ -1628,7 +2038,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Проектная аппроксимация CAD-лотков; без запаса</t>
+          <t>Соседние устройства: два заводских джампера по 3 м; не нулевой фидер</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2902,9 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:F45"/>
+  <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -2500,7 +2912,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F385"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -4673,10 +5085,10 @@
         <v>2.371462545490298</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>21.20236241540974</v>
+        <v>21.40236241540974</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>-77.54726600358002</v>
+        <v>-77.74726600358002</v>
       </c>
     </row>
     <row r="99" ht="21" customHeight="1">
@@ -4695,10 +5107,10 @@
         <v>2.371462545490298</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>21.20236241540974</v>
+        <v>21.40236241540974</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>-82.2028341237602</v>
+        <v>-82.4028341237602</v>
       </c>
     </row>
     <row r="100" ht="21" customHeight="1">
@@ -4717,10 +5129,10 @@
         <v>2.371462545490298</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>21.20236241540974</v>
+        <v>21.40236241540974</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>-85.85518435860251</v>
+        <v>-86.05518435860252</v>
       </c>
     </row>
     <row r="101" ht="21" customHeight="1">
@@ -4739,10 +5151,10 @@
         <v>2.371462545490298</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>21.20236241540974</v>
+        <v>21.40236241540974</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>-88.68962346161064</v>
+        <v>-88.88962346161064</v>
       </c>
     </row>
     <row r="102" ht="21" customHeight="1">
@@ -4761,10 +5173,10 @@
         <v>2.581263490255539</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>21.41216336017498</v>
+        <v>21.61216336017497</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>-77.84661537487452</v>
+        <v>-78.04661537487452</v>
       </c>
     </row>
     <row r="103" ht="21" customHeight="1">
@@ -4783,10 +5195,10 @@
         <v>2.581263490255539</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>21.41216336017498</v>
+        <v>21.61216336017497</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>-82.50218349505469</v>
+        <v>-82.7021834950547</v>
       </c>
     </row>
     <row r="104" ht="21" customHeight="1">
@@ -4805,10 +5217,10 @@
         <v>2.581263490255539</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>21.41216336017498</v>
+        <v>21.61216336017497</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>-86.15453372989701</v>
+        <v>-86.35453372989701</v>
       </c>
     </row>
     <row r="105" ht="21" customHeight="1">
@@ -4827,10 +5239,10 @@
         <v>2.581263490255539</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>21.41216336017498</v>
+        <v>21.61216336017497</v>
       </c>
       <c r="F105" s="2" t="n">
-        <v>-88.98897283290513</v>
+        <v>-89.18897283290514</v>
       </c>
     </row>
     <row r="106" ht="21" customHeight="1">
@@ -4849,10 +5261,10 @@
         <v>2.909094105061595</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>21.73999397498103</v>
+        <v>21.93999397498103</v>
       </c>
       <c r="F106" s="2" t="n">
-        <v>-78.26861446386174</v>
+        <v>-78.46861446386174</v>
       </c>
     </row>
     <row r="107" ht="21" customHeight="1">
@@ -4871,10 +5283,10 @@
         <v>2.909094105061595</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>21.73999397498103</v>
+        <v>21.93999397498103</v>
       </c>
       <c r="F107" s="2" t="n">
-        <v>-82.92418258404192</v>
+        <v>-83.12418258404192</v>
       </c>
     </row>
     <row r="108" ht="21" customHeight="1">
@@ -4893,10 +5305,10 @@
         <v>2.909094105061595</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>21.73999397498103</v>
+        <v>21.93999397498103</v>
       </c>
       <c r="F108" s="2" t="n">
-        <v>-86.57653281888423</v>
+        <v>-86.77653281888423</v>
       </c>
     </row>
     <row r="109" ht="21" customHeight="1">
@@ -4915,10 +5327,10 @@
         <v>2.909094105061595</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>21.73999397498103</v>
+        <v>21.93999397498103</v>
       </c>
       <c r="F109" s="2" t="n">
-        <v>-89.41097192189237</v>
+        <v>-89.61097192189237</v>
       </c>
     </row>
     <row r="110" ht="21" customHeight="1">
@@ -4937,10 +5349,10 @@
         <v>2.577672407416961</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>21.4085722773364</v>
+        <v>21.6085722773364</v>
       </c>
       <c r="F110" s="2" t="n">
-        <v>-77.75347586550669</v>
+        <v>-77.95347586550668</v>
       </c>
     </row>
     <row r="111" ht="21" customHeight="1">
@@ -4959,10 +5371,10 @@
         <v>2.577672407416961</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>21.4085722773364</v>
+        <v>21.6085722773364</v>
       </c>
       <c r="F111" s="2" t="n">
-        <v>-82.40904398568686</v>
+        <v>-82.60904398568687</v>
       </c>
     </row>
     <row r="112" ht="21" customHeight="1">
@@ -4981,10 +5393,10 @@
         <v>2.577672407416961</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>21.4085722773364</v>
+        <v>21.6085722773364</v>
       </c>
       <c r="F112" s="2" t="n">
-        <v>-86.06139422052918</v>
+        <v>-86.26139422052918</v>
       </c>
     </row>
     <row r="113" ht="21" customHeight="1">
@@ -5003,10 +5415,10 @@
         <v>2.577672407416961</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>21.4085722773364</v>
+        <v>21.6085722773364</v>
       </c>
       <c r="F113" s="2" t="n">
-        <v>-88.8958333235373</v>
+        <v>-89.09583332353731</v>
       </c>
     </row>
     <row r="114" ht="21" customHeight="1">
@@ -5025,10 +5437,10 @@
         <v>2.805866699628583</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>21.63676656954802</v>
+        <v>21.83676656954802</v>
       </c>
       <c r="F114" s="2" t="n">
-        <v>-78.07121858424756</v>
+        <v>-78.27121858424756</v>
       </c>
     </row>
     <row r="115" ht="21" customHeight="1">
@@ -5047,10 +5459,10 @@
         <v>2.805866699628583</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>21.63676656954802</v>
+        <v>21.83676656954802</v>
       </c>
       <c r="F115" s="2" t="n">
-        <v>-82.72678670442775</v>
+        <v>-82.92678670442774</v>
       </c>
     </row>
     <row r="116" ht="21" customHeight="1">
@@ -5069,10 +5481,10 @@
         <v>2.805866699628583</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>21.63676656954802</v>
+        <v>21.83676656954802</v>
       </c>
       <c r="F116" s="2" t="n">
-        <v>-86.37913693927007</v>
+        <v>-86.57913693927006</v>
       </c>
     </row>
     <row r="117" ht="21" customHeight="1">
@@ -5091,10 +5503,10 @@
         <v>2.805866699628583</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>21.63676656954802</v>
+        <v>21.83676656954802</v>
       </c>
       <c r="F117" s="2" t="n">
-        <v>-89.21357604227819</v>
+        <v>-89.41357604227818</v>
       </c>
     </row>
     <row r="118" ht="21" customHeight="1">
@@ -5113,10 +5525,10 @@
         <v>3.162241064731063</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>21.9931409346505</v>
+        <v>22.1931409346505</v>
       </c>
       <c r="F118" s="2" t="n">
-        <v>-78.5217614235312</v>
+        <v>-78.72176142353121</v>
       </c>
     </row>
     <row r="119" ht="21" customHeight="1">
@@ -5135,10 +5547,10 @@
         <v>3.162241064731063</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>21.9931409346505</v>
+        <v>22.1931409346505</v>
       </c>
       <c r="F119" s="2" t="n">
-        <v>-83.17732954371138</v>
+        <v>-83.37732954371138</v>
       </c>
     </row>
     <row r="120" ht="21" customHeight="1">
@@ -5157,10 +5569,10 @@
         <v>3.162241064731063</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>21.9931409346505</v>
+        <v>22.1931409346505</v>
       </c>
       <c r="F120" s="2" t="n">
-        <v>-86.8296797785537</v>
+        <v>-87.0296797785537</v>
       </c>
     </row>
     <row r="121" ht="21" customHeight="1">
@@ -5179,10 +5591,10 @@
         <v>3.162241064731063</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>21.9931409346505</v>
+        <v>22.1931409346505</v>
       </c>
       <c r="F121" s="2" t="n">
-        <v>-89.66411888156183</v>
+        <v>-89.86411888156184</v>
       </c>
     </row>
     <row r="122" ht="21" customHeight="1">
@@ -5201,10 +5613,10 @@
         <v>3.141736217028593</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>21.97263608694803</v>
+        <v>22.17263608694803</v>
       </c>
       <c r="F122" s="2" t="n">
-        <v>-78.31753967511831</v>
+        <v>-78.51753967511831</v>
       </c>
     </row>
     <row r="123" ht="21" customHeight="1">
@@ -5223,10 +5635,10 @@
         <v>3.141736217028593</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>21.97263608694803</v>
+        <v>22.17263608694803</v>
       </c>
       <c r="F123" s="2" t="n">
-        <v>-82.97310779529849</v>
+        <v>-83.17310779529849</v>
       </c>
     </row>
     <row r="124" ht="21" customHeight="1">
@@ -5245,10 +5657,10 @@
         <v>3.141736217028593</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>21.97263608694803</v>
+        <v>22.17263608694803</v>
       </c>
       <c r="F124" s="2" t="n">
-        <v>-86.62545803014081</v>
+        <v>-86.82545803014081</v>
       </c>
     </row>
     <row r="125" ht="21" customHeight="1">
@@ -5267,10 +5679,10 @@
         <v>3.141736217028593</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>21.97263608694803</v>
+        <v>22.17263608694803</v>
       </c>
       <c r="F125" s="2" t="n">
-        <v>-89.45989713314893</v>
+        <v>-89.65989713314893</v>
       </c>
     </row>
     <row r="126" ht="21" customHeight="1">
@@ -5289,10 +5701,10 @@
         <v>3.420243435766525</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>22.25114330568596</v>
+        <v>22.45114330568596</v>
       </c>
       <c r="F126" s="2" t="n">
-        <v>-78.68559532038552</v>
+        <v>-78.88559532038551</v>
       </c>
     </row>
     <row r="127" ht="21" customHeight="1">
@@ -5311,10 +5723,10 @@
         <v>3.420243435766525</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>22.25114330568596</v>
+        <v>22.45114330568596</v>
       </c>
       <c r="F127" s="2" t="n">
-        <v>-83.34116344056568</v>
+        <v>-83.54116344056568</v>
       </c>
     </row>
     <row r="128" ht="21" customHeight="1">
@@ -5333,10 +5745,10 @@
         <v>3.420243435766525</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>22.25114330568596</v>
+        <v>22.45114330568596</v>
       </c>
       <c r="F128" s="2" t="n">
-        <v>-86.993513675408</v>
+        <v>-87.193513675408</v>
       </c>
     </row>
     <row r="129" ht="21" customHeight="1">
@@ -5355,10 +5767,10 @@
         <v>3.420243435766525</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>22.25114330568596</v>
+        <v>22.45114330568596</v>
       </c>
       <c r="F129" s="2" t="n">
-        <v>-89.82795277841612</v>
+        <v>-90.02795277841612</v>
       </c>
     </row>
     <row r="130" ht="21" customHeight="1">
@@ -5377,10 +5789,10 @@
         <v>3.854696009070945</v>
       </c>
       <c r="E130" s="2" t="n">
-        <v>22.68559587899038</v>
+        <v>22.88559587899038</v>
       </c>
       <c r="F130" s="2" t="n">
-        <v>-79.21421636787109</v>
+        <v>-79.41421636787109</v>
       </c>
     </row>
     <row r="131" ht="21" customHeight="1">
@@ -5399,10 +5811,10 @@
         <v>3.854696009070945</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>22.68559587899038</v>
+        <v>22.88559587899038</v>
       </c>
       <c r="F131" s="2" t="n">
-        <v>-83.86978448805127</v>
+        <v>-84.06978448805127</v>
       </c>
     </row>
     <row r="132" ht="21" customHeight="1">
@@ -5421,10 +5833,10 @@
         <v>3.854696009070945</v>
       </c>
       <c r="E132" s="2" t="n">
-        <v>22.68559587899038</v>
+        <v>22.88559587899038</v>
       </c>
       <c r="F132" s="2" t="n">
-        <v>-87.52213472289358</v>
+        <v>-87.72213472289359</v>
       </c>
     </row>
     <row r="133" ht="21" customHeight="1">
@@ -5443,10 +5855,10 @@
         <v>3.854696009070945</v>
       </c>
       <c r="E133" s="2" t="n">
-        <v>22.68559587899038</v>
+        <v>22.88559587899038</v>
       </c>
       <c r="F133" s="2" t="n">
-        <v>-90.35657382590172</v>
+        <v>-90.55657382590172</v>
       </c>
     </row>
     <row r="134" ht="21" customHeight="1">
@@ -5465,10 +5877,10 @@
         <v>3.281907798617531</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>22.11280766853697</v>
+        <v>22.31280766853697</v>
       </c>
       <c r="F134" s="2" t="n">
-        <v>-78.45771125670726</v>
+        <v>-78.65771125670724</v>
       </c>
     </row>
     <row r="135" ht="21" customHeight="1">
@@ -5487,10 +5899,10 @@
         <v>3.281907798617531</v>
       </c>
       <c r="E135" s="2" t="n">
-        <v>22.11280766853697</v>
+        <v>22.31280766853697</v>
       </c>
       <c r="F135" s="2" t="n">
-        <v>-83.11327937688743</v>
+        <v>-83.31327937688744</v>
       </c>
     </row>
     <row r="136" ht="21" customHeight="1">
@@ -5509,10 +5921,10 @@
         <v>3.281907798617531</v>
       </c>
       <c r="E136" s="2" t="n">
-        <v>22.11280766853697</v>
+        <v>22.31280766853697</v>
       </c>
       <c r="F136" s="2" t="n">
-        <v>-86.76562961172975</v>
+        <v>-86.96562961172975</v>
       </c>
     </row>
     <row r="137" ht="21" customHeight="1">
@@ -5531,10 +5943,10 @@
         <v>3.281907798617531</v>
       </c>
       <c r="E137" s="2" t="n">
-        <v>22.11280766853697</v>
+        <v>22.31280766853697</v>
       </c>
       <c r="F137" s="2" t="n">
-        <v>-89.60006871473787</v>
+        <v>-89.80006871473788</v>
       </c>
     </row>
     <row r="138" ht="21" customHeight="1">
@@ -5553,10 +5965,10 @@
         <v>3.571673170472438</v>
       </c>
       <c r="E138" s="2" t="n">
-        <v>22.40257304039188</v>
+        <v>22.60257304039187</v>
       </c>
       <c r="F138" s="2" t="n">
-        <v>-78.83702505509142</v>
+        <v>-79.03702505509142</v>
       </c>
     </row>
     <row r="139" ht="21" customHeight="1">
@@ -5575,10 +5987,10 @@
         <v>3.571673170472438</v>
       </c>
       <c r="E139" s="2" t="n">
-        <v>22.40257304039188</v>
+        <v>22.60257304039187</v>
       </c>
       <c r="F139" s="2" t="n">
-        <v>-83.49259317527159</v>
+        <v>-83.6925931752716</v>
       </c>
     </row>
     <row r="140" ht="21" customHeight="1">
@@ -5597,10 +6009,10 @@
         <v>3.571673170472438</v>
       </c>
       <c r="E140" s="2" t="n">
-        <v>22.40257304039188</v>
+        <v>22.60257304039187</v>
       </c>
       <c r="F140" s="2" t="n">
-        <v>-87.14494341011391</v>
+        <v>-87.34494341011391</v>
       </c>
     </row>
     <row r="141" ht="21" customHeight="1">
@@ -5619,10 +6031,10 @@
         <v>3.571673170472438</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>22.40257304039188</v>
+        <v>22.60257304039187</v>
       </c>
       <c r="F141" s="2" t="n">
-        <v>-89.97938251312203</v>
+        <v>-90.17938251312204</v>
       </c>
     </row>
     <row r="142" ht="21" customHeight="1">
@@ -5641,10 +6053,10 @@
         <v>4.02521896989751</v>
       </c>
       <c r="E142" s="2" t="n">
-        <v>22.85611883981695</v>
+        <v>23.05611883981695</v>
       </c>
       <c r="F142" s="2" t="n">
-        <v>-79.38473932869765</v>
+        <v>-79.58473932869765</v>
       </c>
     </row>
     <row r="143" ht="21" customHeight="1">
@@ -5663,10 +6075,10 @@
         <v>4.02521896989751</v>
       </c>
       <c r="E143" s="2" t="n">
-        <v>22.85611883981695</v>
+        <v>23.05611883981695</v>
       </c>
       <c r="F143" s="2" t="n">
-        <v>-84.04030744887783</v>
+        <v>-84.24030744887783</v>
       </c>
     </row>
     <row r="144" ht="21" customHeight="1">
@@ -5685,10 +6097,10 @@
         <v>4.02521896989751</v>
       </c>
       <c r="E144" s="2" t="n">
-        <v>22.85611883981695</v>
+        <v>23.05611883981695</v>
       </c>
       <c r="F144" s="2" t="n">
-        <v>-87.69265768372014</v>
+        <v>-87.89265768372015</v>
       </c>
     </row>
     <row r="145" ht="21" customHeight="1">
@@ -5707,10 +6119,10 @@
         <v>4.02521896989751</v>
       </c>
       <c r="E145" s="2" t="n">
-        <v>22.85611883981695</v>
+        <v>23.05611883981695</v>
       </c>
       <c r="F145" s="2" t="n">
-        <v>-90.52709678672828</v>
+        <v>-90.72709678672828</v>
       </c>
     </row>
     <row r="146" ht="21" customHeight="1">
@@ -6785,10 +7197,10 @@
         <v>0.6891492731218927</v>
       </c>
       <c r="E194" s="2" t="n">
-        <v>19.52004914304133</v>
+        <v>19.72004914304133</v>
       </c>
       <c r="F194" s="2" t="n">
-        <v>-75.86495273121162</v>
+        <v>-76.0649527312116</v>
       </c>
     </row>
     <row r="195" ht="21" customHeight="1">
@@ -6807,10 +7219,10 @@
         <v>0.6891492731218927</v>
       </c>
       <c r="E195" s="2" t="n">
-        <v>19.52004914304133</v>
+        <v>19.72004914304133</v>
       </c>
       <c r="F195" s="2" t="n">
-        <v>-80.52052085139179</v>
+        <v>-80.7205208513918</v>
       </c>
     </row>
     <row r="196" ht="21" customHeight="1">
@@ -6829,10 +7241,10 @@
         <v>0.6891492731218927</v>
       </c>
       <c r="E196" s="2" t="n">
-        <v>19.52004914304133</v>
+        <v>19.72004914304133</v>
       </c>
       <c r="F196" s="2" t="n">
-        <v>-84.17287108623411</v>
+        <v>-84.37287108623411</v>
       </c>
     </row>
     <row r="197" ht="21" customHeight="1">
@@ -6851,10 +7263,10 @@
         <v>0.6891492731218927</v>
       </c>
       <c r="E197" s="2" t="n">
-        <v>19.52004914304133</v>
+        <v>19.72004914304133</v>
       </c>
       <c r="F197" s="2" t="n">
-        <v>-87.00731018924223</v>
+        <v>-87.20731018924224</v>
       </c>
     </row>
     <row r="198" ht="21" customHeight="1">
@@ -6873,10 +7285,10 @@
         <v>0.7504639302586325</v>
       </c>
       <c r="E198" s="2" t="n">
-        <v>19.58136380017807</v>
+        <v>19.78136380017807</v>
       </c>
       <c r="F198" s="2" t="n">
-        <v>-76.01581581487761</v>
+        <v>-76.21581581487762</v>
       </c>
     </row>
     <row r="199" ht="21" customHeight="1">
@@ -6895,10 +7307,10 @@
         <v>0.7504639302586325</v>
       </c>
       <c r="E199" s="2" t="n">
-        <v>19.58136380017807</v>
+        <v>19.78136380017807</v>
       </c>
       <c r="F199" s="2" t="n">
-        <v>-80.67138393505779</v>
+        <v>-80.87138393505779</v>
       </c>
     </row>
     <row r="200" ht="21" customHeight="1">
@@ -6917,10 +7329,10 @@
         <v>0.7504639302586325</v>
       </c>
       <c r="E200" s="2" t="n">
-        <v>19.58136380017807</v>
+        <v>19.78136380017807</v>
       </c>
       <c r="F200" s="2" t="n">
-        <v>-84.32373416990011</v>
+        <v>-84.52373416990011</v>
       </c>
     </row>
     <row r="201" ht="21" customHeight="1">
@@ -6939,10 +7351,10 @@
         <v>0.7504639302586325</v>
       </c>
       <c r="E201" s="2" t="n">
-        <v>19.58136380017807</v>
+        <v>19.78136380017807</v>
       </c>
       <c r="F201" s="2" t="n">
-        <v>-87.15817327290823</v>
+        <v>-87.35817327290823</v>
       </c>
     </row>
     <row r="202" ht="21" customHeight="1">
@@ -6961,10 +7373,10 @@
         <v>0.8458179096856471</v>
       </c>
       <c r="E202" s="2" t="n">
-        <v>19.67671777960508</v>
+        <v>19.87671777960508</v>
       </c>
       <c r="F202" s="2" t="n">
-        <v>-76.20533826848579</v>
+        <v>-76.40533826848579</v>
       </c>
     </row>
     <row r="203" ht="21" customHeight="1">
@@ -6983,10 +7395,10 @@
         <v>0.8458179096856471</v>
       </c>
       <c r="E203" s="2" t="n">
-        <v>19.67671777960508</v>
+        <v>19.87671777960508</v>
       </c>
       <c r="F203" s="2" t="n">
-        <v>-80.86090638866597</v>
+        <v>-81.06090638866597</v>
       </c>
     </row>
     <row r="204" ht="21" customHeight="1">
@@ -7005,10 +7417,10 @@
         <v>0.8458179096856471</v>
       </c>
       <c r="E204" s="2" t="n">
-        <v>19.67671777960508</v>
+        <v>19.87671777960508</v>
       </c>
       <c r="F204" s="2" t="n">
-        <v>-84.51325662350828</v>
+        <v>-84.71325662350829</v>
       </c>
     </row>
     <row r="205" ht="21" customHeight="1">
@@ -7027,10 +7439,10 @@
         <v>0.8458179096856471</v>
       </c>
       <c r="E205" s="2" t="n">
-        <v>19.67671777960508</v>
+        <v>19.87671777960508</v>
       </c>
       <c r="F205" s="2" t="n">
-        <v>-87.34769572651642</v>
+        <v>-87.54769572651642</v>
       </c>
     </row>
     <row r="206" ht="21" customHeight="1">
@@ -7049,10 +7461,10 @@
         <v>1.021395793958125</v>
       </c>
       <c r="E206" s="2" t="n">
-        <v>19.85229566387756</v>
+        <v>20.05229566387756</v>
       </c>
       <c r="F206" s="2" t="n">
-        <v>-76.19719925204785</v>
+        <v>-76.39719925204784</v>
       </c>
     </row>
     <row r="207" ht="21" customHeight="1">
@@ -7071,10 +7483,10 @@
         <v>1.021395793958125</v>
       </c>
       <c r="E207" s="2" t="n">
-        <v>19.85229566387756</v>
+        <v>20.05229566387756</v>
       </c>
       <c r="F207" s="2" t="n">
-        <v>-80.85276737222802</v>
+        <v>-81.05276737222802</v>
       </c>
     </row>
     <row r="208" ht="21" customHeight="1">
@@ -7093,10 +7505,10 @@
         <v>1.021395793958125</v>
       </c>
       <c r="E208" s="2" t="n">
-        <v>19.85229566387756</v>
+        <v>20.05229566387756</v>
       </c>
       <c r="F208" s="2" t="n">
-        <v>-84.50511760707033</v>
+        <v>-84.70511760707033</v>
       </c>
     </row>
     <row r="209" ht="21" customHeight="1">
@@ -7115,10 +7527,10 @@
         <v>1.021395793958125</v>
       </c>
       <c r="E209" s="2" t="n">
-        <v>19.85229566387756</v>
+        <v>20.05229566387756</v>
       </c>
       <c r="F209" s="2" t="n">
-        <v>-87.33955671007845</v>
+        <v>-87.53955671007846</v>
       </c>
     </row>
     <row r="210" ht="21" customHeight="1">
@@ -7137,10 +7549,10 @@
         <v>1.11234591876113</v>
       </c>
       <c r="E210" s="2" t="n">
-        <v>19.94324578868057</v>
+        <v>20.14324578868057</v>
       </c>
       <c r="F210" s="2" t="n">
-        <v>-76.37769780338012</v>
+        <v>-76.57769780338012</v>
       </c>
     </row>
     <row r="211" ht="21" customHeight="1">
@@ -7159,10 +7571,10 @@
         <v>1.11234591876113</v>
       </c>
       <c r="E211" s="2" t="n">
-        <v>19.94324578868057</v>
+        <v>20.14324578868057</v>
       </c>
       <c r="F211" s="2" t="n">
-        <v>-81.03326592356029</v>
+        <v>-81.23326592356028</v>
       </c>
     </row>
     <row r="212" ht="21" customHeight="1">
@@ -7181,10 +7593,10 @@
         <v>1.11234591876113</v>
       </c>
       <c r="E212" s="2" t="n">
-        <v>19.94324578868057</v>
+        <v>20.14324578868057</v>
       </c>
       <c r="F212" s="2" t="n">
-        <v>-84.68561615840261</v>
+        <v>-84.8856161584026</v>
       </c>
     </row>
     <row r="213" ht="21" customHeight="1">
@@ -7203,10 +7615,10 @@
         <v>1.11234591876113</v>
       </c>
       <c r="E213" s="2" t="n">
-        <v>19.94324578868057</v>
+        <v>20.14324578868057</v>
       </c>
       <c r="F213" s="2" t="n">
-        <v>-87.52005526141073</v>
+        <v>-87.72005526141072</v>
       </c>
     </row>
     <row r="214" ht="21" customHeight="1">
@@ -7225,10 +7637,10 @@
         <v>1.253689753566532</v>
       </c>
       <c r="E214" s="2" t="n">
-        <v>20.08458962348597</v>
+        <v>20.28458962348597</v>
       </c>
       <c r="F214" s="2" t="n">
-        <v>-76.61321011236667</v>
+        <v>-76.81321011236668</v>
       </c>
     </row>
     <row r="215" ht="21" customHeight="1">
@@ -7247,10 +7659,10 @@
         <v>1.253689753566532</v>
       </c>
       <c r="E215" s="2" t="n">
-        <v>20.08458962348597</v>
+        <v>20.28458962348597</v>
       </c>
       <c r="F215" s="2" t="n">
-        <v>-81.26877823254685</v>
+        <v>-81.46877823254685</v>
       </c>
     </row>
     <row r="216" ht="21" customHeight="1">
@@ -7269,10 +7681,10 @@
         <v>1.253689753566532</v>
       </c>
       <c r="E216" s="2" t="n">
-        <v>20.08458962348597</v>
+        <v>20.28458962348597</v>
       </c>
       <c r="F216" s="2" t="n">
-        <v>-84.92112846738917</v>
+        <v>-85.12112846738917</v>
       </c>
     </row>
     <row r="217" ht="21" customHeight="1">
@@ -7291,10 +7703,10 @@
         <v>1.253689753566532</v>
       </c>
       <c r="E217" s="2" t="n">
-        <v>20.08458962348597</v>
+        <v>20.28458962348597</v>
       </c>
       <c r="F217" s="2" t="n">
-        <v>-87.7555675703973</v>
+        <v>-87.95556757039731</v>
       </c>
     </row>
     <row r="218" ht="21" customHeight="1">
@@ -7313,10 +7725,10 @@
         <v>1.246710148742719</v>
       </c>
       <c r="E218" s="2" t="n">
-        <v>20.07761001866216</v>
+        <v>20.27761001866216</v>
       </c>
       <c r="F218" s="2" t="n">
-        <v>-76.42251360683244</v>
+        <v>-76.62251360683244</v>
       </c>
     </row>
     <row r="219" ht="21" customHeight="1">
@@ -7335,10 +7747,10 @@
         <v>1.246710148742719</v>
       </c>
       <c r="E219" s="2" t="n">
-        <v>20.07761001866216</v>
+        <v>20.27761001866216</v>
       </c>
       <c r="F219" s="2" t="n">
-        <v>-81.07808172701262</v>
+        <v>-81.27808172701262</v>
       </c>
     </row>
     <row r="220" ht="21" customHeight="1">
@@ -7357,10 +7769,10 @@
         <v>1.246710148742719</v>
       </c>
       <c r="E220" s="2" t="n">
-        <v>20.07761001866216</v>
+        <v>20.27761001866216</v>
       </c>
       <c r="F220" s="2" t="n">
-        <v>-84.73043196185493</v>
+        <v>-84.93043196185494</v>
       </c>
     </row>
     <row r="221" ht="21" customHeight="1">
@@ -7379,10 +7791,10 @@
         <v>1.246710148742719</v>
       </c>
       <c r="E221" s="2" t="n">
-        <v>20.07761001866216</v>
+        <v>20.27761001866216</v>
       </c>
       <c r="F221" s="2" t="n">
-        <v>-87.56487106486306</v>
+        <v>-87.76487106486306</v>
       </c>
     </row>
     <row r="222" ht="21" customHeight="1">
@@ -7401,10 +7813,10 @@
         <v>1.357757688739592</v>
       </c>
       <c r="E222" s="2" t="n">
-        <v>20.18865755865903</v>
+        <v>20.38865755865903</v>
       </c>
       <c r="F222" s="2" t="n">
-        <v>-76.62310957335858</v>
+        <v>-76.82310957335858</v>
       </c>
     </row>
     <row r="223" ht="21" customHeight="1">
@@ -7423,10 +7835,10 @@
         <v>1.357757688739592</v>
       </c>
       <c r="E223" s="2" t="n">
-        <v>20.18865755865903</v>
+        <v>20.38865755865903</v>
       </c>
       <c r="F223" s="2" t="n">
-        <v>-81.27867769353875</v>
+        <v>-81.47867769353876</v>
       </c>
     </row>
     <row r="224" ht="21" customHeight="1">
@@ -7445,10 +7857,10 @@
         <v>1.357757688739592</v>
       </c>
       <c r="E224" s="2" t="n">
-        <v>20.18865755865903</v>
+        <v>20.38865755865903</v>
       </c>
       <c r="F224" s="2" t="n">
-        <v>-84.93102792838107</v>
+        <v>-85.13102792838107</v>
       </c>
     </row>
     <row r="225" ht="21" customHeight="1">
@@ -7467,10 +7879,10 @@
         <v>1.357757688739592</v>
       </c>
       <c r="E225" s="2" t="n">
-        <v>20.18865755865903</v>
+        <v>20.38865755865903</v>
       </c>
       <c r="F225" s="2" t="n">
-        <v>-87.76546703138919</v>
+        <v>-87.9654670313892</v>
       </c>
     </row>
     <row r="226" ht="21" customHeight="1">
@@ -7489,10 +7901,10 @@
         <v>1.530289734531035</v>
       </c>
       <c r="E226" s="2" t="n">
-        <v>20.36118960445047</v>
+        <v>20.56118960445047</v>
       </c>
       <c r="F226" s="2" t="n">
-        <v>-76.88981009333118</v>
+        <v>-77.08981009333118</v>
       </c>
     </row>
     <row r="227" ht="21" customHeight="1">
@@ -7511,10 +7923,10 @@
         <v>1.530289734531035</v>
       </c>
       <c r="E227" s="2" t="n">
-        <v>20.36118960445047</v>
+        <v>20.56118960445047</v>
       </c>
       <c r="F227" s="2" t="n">
-        <v>-81.54537821351136</v>
+        <v>-81.74537821351136</v>
       </c>
     </row>
     <row r="228" ht="21" customHeight="1">
@@ -7533,10 +7945,10 @@
         <v>1.530289734531035</v>
       </c>
       <c r="E228" s="2" t="n">
-        <v>20.36118960445047</v>
+        <v>20.56118960445047</v>
       </c>
       <c r="F228" s="2" t="n">
-        <v>-85.19772844835367</v>
+        <v>-85.39772844835367</v>
       </c>
     </row>
     <row r="229" ht="21" customHeight="1">
@@ -7555,10 +7967,10 @@
         <v>1.530289734531035</v>
       </c>
       <c r="E229" s="2" t="n">
-        <v>20.36118960445047</v>
+        <v>20.56118960445047</v>
       </c>
       <c r="F229" s="2" t="n">
-        <v>-88.03216755136181</v>
+        <v>-88.23216755136181</v>
       </c>
     </row>
     <row r="230" ht="21" customHeight="1">
@@ -7577,10 +7989,10 @@
         <v>1.300707844936236</v>
       </c>
       <c r="E230" s="2" t="n">
-        <v>20.13160771485568</v>
+        <v>20.33160771485568</v>
       </c>
       <c r="F230" s="2" t="n">
-        <v>-76.47651130302596</v>
+        <v>-76.67651130302596</v>
       </c>
     </row>
     <row r="231" ht="21" customHeight="1">
@@ -7599,10 +8011,10 @@
         <v>1.300707844936236</v>
       </c>
       <c r="E231" s="2" t="n">
-        <v>20.13160771485568</v>
+        <v>20.33160771485568</v>
       </c>
       <c r="F231" s="2" t="n">
-        <v>-81.13207942320614</v>
+        <v>-81.33207942320614</v>
       </c>
     </row>
     <row r="232" ht="21" customHeight="1">
@@ -7621,10 +8033,10 @@
         <v>1.300707844936236</v>
       </c>
       <c r="E232" s="2" t="n">
-        <v>20.13160771485568</v>
+        <v>20.33160771485568</v>
       </c>
       <c r="F232" s="2" t="n">
-        <v>-84.78442965804845</v>
+        <v>-84.98442965804846</v>
       </c>
     </row>
     <row r="233" ht="21" customHeight="1">
@@ -7643,10 +8055,10 @@
         <v>1.300707844936236</v>
       </c>
       <c r="E233" s="2" t="n">
-        <v>20.13160771485568</v>
+        <v>20.33160771485568</v>
       </c>
       <c r="F233" s="2" t="n">
-        <v>-87.61886876105658</v>
+        <v>-87.81886876105658</v>
       </c>
     </row>
     <row r="234" ht="21" customHeight="1">
@@ -7665,10 +8077,10 @@
         <v>1.416571829588626</v>
       </c>
       <c r="E234" s="2" t="n">
-        <v>20.24747169950806</v>
+        <v>20.44747169950806</v>
       </c>
       <c r="F234" s="2" t="n">
-        <v>-76.68192371420761</v>
+        <v>-76.8819237142076</v>
       </c>
     </row>
     <row r="235" ht="21" customHeight="1">
@@ -7687,10 +8099,10 @@
         <v>1.416571829588626</v>
       </c>
       <c r="E235" s="2" t="n">
-        <v>20.24747169950806</v>
+        <v>20.44747169950806</v>
       </c>
       <c r="F235" s="2" t="n">
-        <v>-81.33749183438779</v>
+        <v>-81.53749183438779</v>
       </c>
     </row>
     <row r="236" ht="21" customHeight="1">
@@ -7709,10 +8121,10 @@
         <v>1.416571829588626</v>
       </c>
       <c r="E236" s="2" t="n">
-        <v>20.24747169950806</v>
+        <v>20.44747169950806</v>
       </c>
       <c r="F236" s="2" t="n">
-        <v>-84.98984206923011</v>
+        <v>-85.18984206923011</v>
       </c>
     </row>
     <row r="237" ht="21" customHeight="1">
@@ -7731,10 +8143,10 @@
         <v>1.416571829588626</v>
       </c>
       <c r="E237" s="2" t="n">
-        <v>20.24747169950806</v>
+        <v>20.44747169950806</v>
       </c>
       <c r="F237" s="2" t="n">
-        <v>-87.82428117223823</v>
+        <v>-88.02428117223823</v>
       </c>
     </row>
     <row r="238" ht="21" customHeight="1">
@@ -7753,10 +8165,10 @@
         <v>1.596578283938075</v>
       </c>
       <c r="E238" s="2" t="n">
-        <v>20.42747815385751</v>
+        <v>20.62747815385751</v>
       </c>
       <c r="F238" s="2" t="n">
-        <v>-76.95609864273823</v>
+        <v>-77.15609864273821</v>
       </c>
     </row>
     <row r="239" ht="21" customHeight="1">
@@ -7775,10 +8187,10 @@
         <v>1.596578283938075</v>
       </c>
       <c r="E239" s="2" t="n">
-        <v>20.42747815385751</v>
+        <v>20.62747815385751</v>
       </c>
       <c r="F239" s="2" t="n">
-        <v>-81.61166676291839</v>
+        <v>-81.81166676291839</v>
       </c>
     </row>
     <row r="240" ht="21" customHeight="1">
@@ -7797,10 +8209,10 @@
         <v>1.596578283938075</v>
       </c>
       <c r="E240" s="2" t="n">
-        <v>20.42747815385751</v>
+        <v>20.62747815385751</v>
       </c>
       <c r="F240" s="2" t="n">
-        <v>-85.26401699776071</v>
+        <v>-85.46401699776071</v>
       </c>
     </row>
     <row r="241" ht="21" customHeight="1">
@@ -7819,10 +8231,10 @@
         <v>1.596578283938075</v>
       </c>
       <c r="E241" s="2" t="n">
-        <v>20.42747815385751</v>
+        <v>20.62747815385751</v>
       </c>
       <c r="F241" s="2" t="n">
-        <v>-88.09845610076886</v>
+        <v>-88.29845610076885</v>
       </c>
     </row>
     <row r="242" ht="21" customHeight="1">
@@ -8897,10 +9309,10 @@
         <v>2.865079335175025</v>
       </c>
       <c r="E290" s="2" t="n">
-        <v>21.69597920509446</v>
+        <v>21.89597920509446</v>
       </c>
       <c r="F290" s="2" t="n">
-        <v>-78.04088279326474</v>
+        <v>-78.24088279326475</v>
       </c>
     </row>
     <row r="291" ht="21" customHeight="1">
@@ -8919,10 +9331,10 @@
         <v>2.865079335175025</v>
       </c>
       <c r="E291" s="2" t="n">
-        <v>21.69597920509446</v>
+        <v>21.89597920509446</v>
       </c>
       <c r="F291" s="2" t="n">
-        <v>-82.69645091344492</v>
+        <v>-82.89645091344492</v>
       </c>
     </row>
     <row r="292" ht="21" customHeight="1">
@@ -8941,10 +9353,10 @@
         <v>2.865079335175025</v>
       </c>
       <c r="E292" s="2" t="n">
-        <v>21.69597920509446</v>
+        <v>21.89597920509446</v>
       </c>
       <c r="F292" s="2" t="n">
-        <v>-86.34880114828724</v>
+        <v>-86.54880114828724</v>
       </c>
     </row>
     <row r="293" ht="21" customHeight="1">
@@ -8963,10 +9375,10 @@
         <v>2.865079335175025</v>
       </c>
       <c r="E293" s="2" t="n">
-        <v>21.69597920509446</v>
+        <v>21.89597920509446</v>
       </c>
       <c r="F293" s="2" t="n">
-        <v>-89.18324025129536</v>
+        <v>-89.38324025129536</v>
       </c>
     </row>
     <row r="294" ht="21" customHeight="1">
@@ -8985,10 +9397,10 @@
         <v>3.118955955519279</v>
       </c>
       <c r="E294" s="2" t="n">
-        <v>21.94985582543872</v>
+        <v>22.14985582543872</v>
       </c>
       <c r="F294" s="2" t="n">
-        <v>-78.38430784013826</v>
+        <v>-78.58430784013827</v>
       </c>
     </row>
     <row r="295" ht="21" customHeight="1">
@@ -9007,10 +9419,10 @@
         <v>3.118955955519279</v>
       </c>
       <c r="E295" s="2" t="n">
-        <v>21.94985582543872</v>
+        <v>22.14985582543872</v>
       </c>
       <c r="F295" s="2" t="n">
-        <v>-83.03987596031844</v>
+        <v>-83.23987596031844</v>
       </c>
     </row>
     <row r="296" ht="21" customHeight="1">
@@ -9029,10 +9441,10 @@
         <v>3.118955955519279</v>
       </c>
       <c r="E296" s="2" t="n">
-        <v>21.94985582543872</v>
+        <v>22.14985582543872</v>
       </c>
       <c r="F296" s="2" t="n">
-        <v>-86.69222619516076</v>
+        <v>-86.89222619516076</v>
       </c>
     </row>
     <row r="297" ht="21" customHeight="1">
@@ -9051,10 +9463,10 @@
         <v>3.118955955519279</v>
       </c>
       <c r="E297" s="2" t="n">
-        <v>21.94985582543872</v>
+        <v>22.14985582543872</v>
       </c>
       <c r="F297" s="2" t="n">
-        <v>-89.52666529816888</v>
+        <v>-89.72666529816888</v>
       </c>
     </row>
     <row r="298" ht="21" customHeight="1">
@@ -9073,10 +9485,10 @@
         <v>3.515124982032769</v>
       </c>
       <c r="E298" s="2" t="n">
-        <v>22.34602485195221</v>
+        <v>22.54602485195221</v>
       </c>
       <c r="F298" s="2" t="n">
-        <v>-78.87464534083291</v>
+        <v>-79.07464534083292</v>
       </c>
     </row>
     <row r="299" ht="21" customHeight="1">
@@ -9095,10 +9507,10 @@
         <v>3.515124982032769</v>
       </c>
       <c r="E299" s="2" t="n">
-        <v>22.34602485195221</v>
+        <v>22.54602485195221</v>
       </c>
       <c r="F299" s="2" t="n">
-        <v>-83.53021346101309</v>
+        <v>-83.73021346101309</v>
       </c>
     </row>
     <row r="300" ht="21" customHeight="1">
@@ -9117,10 +9529,10 @@
         <v>3.515124982032769</v>
       </c>
       <c r="E300" s="2" t="n">
-        <v>22.34602485195221</v>
+        <v>22.54602485195221</v>
       </c>
       <c r="F300" s="2" t="n">
-        <v>-87.18256369585541</v>
+        <v>-87.38256369585541</v>
       </c>
     </row>
     <row r="301" ht="21" customHeight="1">
@@ -9139,10 +9551,10 @@
         <v>3.515124982032769</v>
       </c>
       <c r="E301" s="2" t="n">
-        <v>22.34602485195221</v>
+        <v>22.54602485195221</v>
       </c>
       <c r="F301" s="2" t="n">
-        <v>-90.01700279886354</v>
+        <v>-90.21700279886355</v>
       </c>
     </row>
     <row r="302" ht="21" customHeight="1">
@@ -9161,10 +9573,10 @@
         <v>3.986793808897821</v>
       </c>
       <c r="E302" s="2" t="n">
-        <v>22.81769367881726</v>
+        <v>23.01769367881726</v>
       </c>
       <c r="F302" s="2" t="n">
-        <v>-79.16259726698755</v>
+        <v>-79.36259726698754</v>
       </c>
     </row>
     <row r="303" ht="21" customHeight="1">
@@ -9183,10 +9595,10 @@
         <v>3.986793808897821</v>
       </c>
       <c r="E303" s="2" t="n">
-        <v>22.81769367881726</v>
+        <v>23.01769367881726</v>
       </c>
       <c r="F303" s="2" t="n">
-        <v>-83.81816538716772</v>
+        <v>-84.01816538716773</v>
       </c>
     </row>
     <row r="304" ht="21" customHeight="1">
@@ -9205,10 +9617,10 @@
         <v>3.986793808897821</v>
       </c>
       <c r="E304" s="2" t="n">
-        <v>22.81769367881726</v>
+        <v>23.01769367881726</v>
       </c>
       <c r="F304" s="2" t="n">
-        <v>-87.47051562201004</v>
+        <v>-87.67051562201004</v>
       </c>
     </row>
     <row r="305" ht="21" customHeight="1">
@@ -9227,10 +9639,10 @@
         <v>3.986793808897821</v>
       </c>
       <c r="E305" s="2" t="n">
-        <v>22.81769367881726</v>
+        <v>23.01769367881726</v>
       </c>
       <c r="F305" s="2" t="n">
-        <v>-90.30495472501816</v>
+        <v>-90.50495472501817</v>
       </c>
     </row>
     <row r="306" ht="21" customHeight="1">
@@ -9249,10 +9661,10 @@
         <v>4.338794797783233</v>
       </c>
       <c r="E306" s="2" t="n">
-        <v>23.16969466770267</v>
+        <v>23.36969466770267</v>
       </c>
       <c r="F306" s="2" t="n">
-        <v>-79.60414668240222</v>
+        <v>-79.80414668240222</v>
       </c>
     </row>
     <row r="307" ht="21" customHeight="1">
@@ -9271,10 +9683,10 @@
         <v>4.338794797783233</v>
       </c>
       <c r="E307" s="2" t="n">
-        <v>23.16969466770267</v>
+        <v>23.36969466770267</v>
       </c>
       <c r="F307" s="2" t="n">
-        <v>-84.25971480258239</v>
+        <v>-84.4597148025824</v>
       </c>
     </row>
     <row r="308" ht="21" customHeight="1">
@@ -9293,10 +9705,10 @@
         <v>4.338794797783233</v>
       </c>
       <c r="E308" s="2" t="n">
-        <v>23.16969466770267</v>
+        <v>23.36969466770267</v>
       </c>
       <c r="F308" s="2" t="n">
-        <v>-87.91206503742471</v>
+        <v>-88.11206503742471</v>
       </c>
     </row>
     <row r="309" ht="21" customHeight="1">
@@ -9315,10 +9727,10 @@
         <v>4.338794797783233</v>
       </c>
       <c r="E309" s="2" t="n">
-        <v>23.16969466770267</v>
+        <v>23.36969466770267</v>
       </c>
       <c r="F309" s="2" t="n">
-        <v>-90.74650414043283</v>
+        <v>-90.94650414043284</v>
       </c>
     </row>
     <row r="310" ht="21" customHeight="1">
@@ -9337,10 +9749,10 @@
         <v>4.889752867343009</v>
       </c>
       <c r="E310" s="2" t="n">
-        <v>23.72065273726245</v>
+        <v>23.92065273726245</v>
       </c>
       <c r="F310" s="2" t="n">
-        <v>-80.24927322614315</v>
+        <v>-80.44927322614315</v>
       </c>
     </row>
     <row r="311" ht="21" customHeight="1">
@@ -9359,10 +9771,10 @@
         <v>4.889752867343009</v>
       </c>
       <c r="E311" s="2" t="n">
-        <v>23.72065273726245</v>
+        <v>23.92065273726245</v>
       </c>
       <c r="F311" s="2" t="n">
-        <v>-84.90484134632334</v>
+        <v>-85.10484134632333</v>
       </c>
     </row>
     <row r="312" ht="21" customHeight="1">
@@ -9381,10 +9793,10 @@
         <v>4.889752867343009</v>
       </c>
       <c r="E312" s="2" t="n">
-        <v>23.72065273726245</v>
+        <v>23.92065273726245</v>
       </c>
       <c r="F312" s="2" t="n">
-        <v>-88.55719158116565</v>
+        <v>-88.75719158116564</v>
       </c>
     </row>
     <row r="313" ht="21" customHeight="1">
@@ -9403,10 +9815,10 @@
         <v>4.889752867343009</v>
       </c>
       <c r="E313" s="2" t="n">
-        <v>23.72065273726245</v>
+        <v>23.92065273726245</v>
       </c>
       <c r="F313" s="2" t="n">
-        <v>-91.39163068417378</v>
+        <v>-91.59163068417378</v>
       </c>
     </row>
     <row r="314" ht="21" customHeight="1">
@@ -9425,10 +9837,10 @@
         <v>2.347346569064261</v>
       </c>
       <c r="E314" s="2" t="n">
-        <v>21.1782464389837</v>
+        <v>21.3782464389837</v>
       </c>
       <c r="F314" s="2" t="n">
-        <v>-77.52315002715397</v>
+        <v>-77.72315002715398</v>
       </c>
     </row>
     <row r="315" ht="21" customHeight="1">
@@ -9447,10 +9859,10 @@
         <v>2.347346569064261</v>
       </c>
       <c r="E315" s="2" t="n">
-        <v>21.1782464389837</v>
+        <v>21.3782464389837</v>
       </c>
       <c r="F315" s="2" t="n">
-        <v>-82.17871814733417</v>
+        <v>-82.37871814733415</v>
       </c>
     </row>
     <row r="316" ht="21" customHeight="1">
@@ -9469,10 +9881,10 @@
         <v>2.347346569064261</v>
       </c>
       <c r="E316" s="2" t="n">
-        <v>21.1782464389837</v>
+        <v>21.3782464389837</v>
       </c>
       <c r="F316" s="2" t="n">
-        <v>-85.83106838217648</v>
+        <v>-86.03106838217647</v>
       </c>
     </row>
     <row r="317" ht="21" customHeight="1">
@@ -9491,10 +9903,10 @@
         <v>2.347346569064261</v>
       </c>
       <c r="E317" s="2" t="n">
-        <v>21.1782464389837</v>
+        <v>21.3782464389837</v>
       </c>
       <c r="F317" s="2" t="n">
-        <v>-88.66550748518461</v>
+        <v>-88.86550748518459</v>
       </c>
     </row>
     <row r="318" ht="21" customHeight="1">
@@ -9513,10 +9925,10 @@
         <v>2.55504286339269</v>
       </c>
       <c r="E318" s="2" t="n">
-        <v>21.38594273331213</v>
+        <v>21.58594273331213</v>
       </c>
       <c r="F318" s="2" t="n">
-        <v>-77.82039474801167</v>
+        <v>-78.02039474801167</v>
       </c>
     </row>
     <row r="319" ht="21" customHeight="1">
@@ -9535,10 +9947,10 @@
         <v>2.55504286339269</v>
       </c>
       <c r="E319" s="2" t="n">
-        <v>21.38594273331213</v>
+        <v>21.58594273331213</v>
       </c>
       <c r="F319" s="2" t="n">
-        <v>-82.47596286819186</v>
+        <v>-82.67596286819185</v>
       </c>
     </row>
     <row r="320" ht="21" customHeight="1">
@@ -9557,10 +9969,10 @@
         <v>2.55504286339269</v>
       </c>
       <c r="E320" s="2" t="n">
-        <v>21.38594273331213</v>
+        <v>21.58594273331213</v>
       </c>
       <c r="F320" s="2" t="n">
-        <v>-86.12831310303417</v>
+        <v>-86.32831310303416</v>
       </c>
     </row>
     <row r="321" ht="21" customHeight="1">
@@ -9579,10 +9991,10 @@
         <v>2.55504286339269</v>
       </c>
       <c r="E321" s="2" t="n">
-        <v>21.38594273331213</v>
+        <v>21.58594273331213</v>
       </c>
       <c r="F321" s="2" t="n">
-        <v>-88.9627522060423</v>
+        <v>-89.16275220604228</v>
       </c>
     </row>
     <row r="322" ht="21" customHeight="1">
@@ -9601,10 +10013,10 @@
         <v>2.879546865459397</v>
       </c>
       <c r="E322" s="2" t="n">
-        <v>21.71044673537883</v>
+        <v>21.91044673537883</v>
       </c>
       <c r="F322" s="2" t="n">
-        <v>-78.23906722425954</v>
+        <v>-78.43906722425953</v>
       </c>
     </row>
     <row r="323" ht="21" customHeight="1">
@@ -9623,10 +10035,10 @@
         <v>2.879546865459397</v>
       </c>
       <c r="E323" s="2" t="n">
-        <v>21.71044673537883</v>
+        <v>21.91044673537883</v>
       </c>
       <c r="F323" s="2" t="n">
-        <v>-82.89463534443972</v>
+        <v>-83.09463534443972</v>
       </c>
     </row>
     <row r="324" ht="21" customHeight="1">
@@ -9645,10 +10057,10 @@
         <v>2.879546865459397</v>
       </c>
       <c r="E324" s="2" t="n">
-        <v>21.71044673537883</v>
+        <v>21.91044673537883</v>
       </c>
       <c r="F324" s="2" t="n">
-        <v>-86.54698557928204</v>
+        <v>-86.74698557928204</v>
       </c>
     </row>
     <row r="325" ht="21" customHeight="1">
@@ -9667,10 +10079,10 @@
         <v>2.879546865459397</v>
       </c>
       <c r="E325" s="2" t="n">
-        <v>21.71044673537883</v>
+        <v>21.91044673537883</v>
       </c>
       <c r="F325" s="2" t="n">
-        <v>-89.38142468229017</v>
+        <v>-89.58142468229016</v>
       </c>
     </row>
     <row r="326" ht="21" customHeight="1">
@@ -9689,10 +10101,10 @@
         <v>4.880901911498252</v>
       </c>
       <c r="E326" s="2" t="n">
-        <v>23.71180178141769</v>
+        <v>23.91180178141769</v>
       </c>
       <c r="F326" s="2" t="n">
-        <v>-80.05670536958797</v>
+        <v>-80.25670536958798</v>
       </c>
     </row>
     <row r="327" ht="21" customHeight="1">
@@ -9711,10 +10123,10 @@
         <v>4.880901911498252</v>
       </c>
       <c r="E327" s="2" t="n">
-        <v>23.71180178141769</v>
+        <v>23.91180178141769</v>
       </c>
       <c r="F327" s="2" t="n">
-        <v>-84.71227348976815</v>
+        <v>-84.91227348976815</v>
       </c>
     </row>
     <row r="328" ht="21" customHeight="1">
@@ -9733,10 +10145,10 @@
         <v>4.880901911498252</v>
       </c>
       <c r="E328" s="2" t="n">
-        <v>23.71180178141769</v>
+        <v>23.91180178141769</v>
       </c>
       <c r="F328" s="2" t="n">
-        <v>-88.36462372461047</v>
+        <v>-88.56462372461047</v>
       </c>
     </row>
     <row r="329" ht="21" customHeight="1">
@@ -9755,10 +10167,10 @@
         <v>4.880901911498252</v>
       </c>
       <c r="E329" s="2" t="n">
-        <v>23.71180178141769</v>
+        <v>23.91180178141769</v>
       </c>
       <c r="F329" s="2" t="n">
-        <v>-91.19906282761859</v>
+        <v>-91.39906282761859</v>
       </c>
     </row>
     <row r="330" ht="21" customHeight="1">
@@ -9777,10 +10189,10 @@
         <v>5.311845266448193</v>
       </c>
       <c r="E330" s="2" t="n">
-        <v>24.14274513636763</v>
+        <v>24.34274513636763</v>
       </c>
       <c r="F330" s="2" t="n">
-        <v>-80.57719715106717</v>
+        <v>-80.77719715106717</v>
       </c>
     </row>
     <row r="331" ht="21" customHeight="1">
@@ -9799,10 +10211,10 @@
         <v>5.311845266448193</v>
       </c>
       <c r="E331" s="2" t="n">
-        <v>24.14274513636763</v>
+        <v>24.34274513636763</v>
       </c>
       <c r="F331" s="2" t="n">
-        <v>-85.23276527124736</v>
+        <v>-85.43276527124735</v>
       </c>
     </row>
     <row r="332" ht="21" customHeight="1">
@@ -9821,10 +10233,10 @@
         <v>5.311845266448193</v>
       </c>
       <c r="E332" s="2" t="n">
-        <v>24.14274513636763</v>
+        <v>24.34274513636763</v>
       </c>
       <c r="F332" s="2" t="n">
-        <v>-88.88511550608968</v>
+        <v>-89.08511550608966</v>
       </c>
     </row>
     <row r="333" ht="21" customHeight="1">
@@ -9843,10 +10255,10 @@
         <v>5.311845266448193</v>
       </c>
       <c r="E333" s="2" t="n">
-        <v>24.14274513636763</v>
+        <v>24.34274513636763</v>
       </c>
       <c r="F333" s="2" t="n">
-        <v>-91.7195546090978</v>
+        <v>-91.91955460909779</v>
       </c>
     </row>
     <row r="334" ht="21" customHeight="1">
@@ -9865,10 +10277,10 @@
         <v>5.986365300282883</v>
       </c>
       <c r="E334" s="2" t="n">
-        <v>24.81726517020232</v>
+        <v>25.01726517020232</v>
       </c>
       <c r="F334" s="2" t="n">
-        <v>-81.34588565908302</v>
+        <v>-81.54588565908303</v>
       </c>
     </row>
     <row r="335" ht="21" customHeight="1">
@@ -9887,10 +10299,10 @@
         <v>5.986365300282883</v>
       </c>
       <c r="E335" s="2" t="n">
-        <v>24.81726517020232</v>
+        <v>25.01726517020232</v>
       </c>
       <c r="F335" s="2" t="n">
-        <v>-86.0014537792632</v>
+        <v>-86.2014537792632</v>
       </c>
     </row>
     <row r="336" ht="21" customHeight="1">
@@ -9909,10 +10321,10 @@
         <v>5.986365300282883</v>
       </c>
       <c r="E336" s="2" t="n">
-        <v>24.81726517020232</v>
+        <v>25.01726517020232</v>
       </c>
       <c r="F336" s="2" t="n">
-        <v>-89.65380401410552</v>
+        <v>-89.85380401410552</v>
       </c>
     </row>
     <row r="337" ht="21" customHeight="1">
@@ -9931,10 +10343,10 @@
         <v>5.986365300282883</v>
       </c>
       <c r="E337" s="2" t="n">
-        <v>24.81726517020232</v>
+        <v>25.01726517020232</v>
       </c>
       <c r="F337" s="2" t="n">
-        <v>-92.48824311711365</v>
+        <v>-92.68824311711366</v>
       </c>
     </row>
     <row r="338" ht="21" customHeight="1">
@@ -10995,7 +11407,9 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:F385"/>
+  <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -11003,7 +11417,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -11082,13 +11496,13 @@
         <v>32</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>2011.312062157148</v>
+        <v>2011.311445546711</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>95.77676486462612</v>
+        <v>95.77673550222434</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>97.84211369437413</v>
+        <v>97.84208421412936</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>-137.559876113693</v>
@@ -11113,13 +11527,13 @@
         <v>32</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>2039.09935735389</v>
+        <v>2038.846463073587</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>97.0999693978043</v>
+        <v>97.08792681302796</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>99.27444130386111</v>
+        <v>99.25896417535149</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>-133.567932754318</v>
@@ -11144,13 +11558,13 @@
         <v>32</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1876.544534762945</v>
+        <v>1869.06234272357</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>89.35926356014023</v>
+        <v>89.00296870112237</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>91.41195268164076</v>
+        <v>91.04750315554509</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>-141.551819473068</v>
@@ -11175,13 +11589,13 @@
         <v>32</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1983.844287705143</v>
+        <v>1978.573739975375</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>94.46877560500683</v>
+        <v>94.21779714168453</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>96.50841759376796</v>
+        <v>96.25046053856676</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>-140.559876113693</v>
@@ -11206,13 +11620,13 @@
         <v>32</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1973.750364719516</v>
+        <v>1971.937520713259</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>93.98811260569126</v>
+        <v>93.90178670063138</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>96.6241046254511</v>
+        <v>96.56855401753688</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>-137.7146727140348</v>
@@ -11237,13 +11651,13 @@
         <v>32</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1983.317596836807</v>
+        <v>1978.448337387676</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>94.44369508746701</v>
+        <v>94.21182558988933</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>96.48262237958525</v>
+        <v>96.24431882090421</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>-140.5701760703328</v>
@@ -11268,13 +11682,13 @@
         <v>32</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1738.833940934246</v>
+        <v>1727.099026456332</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>82.80161623496409</v>
+        <v>82.24281078363484</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>84.75263070798827</v>
+        <v>84.18378481808296</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>-145.3413886175294</v>
@@ -11330,13 +11744,13 @@
         <v>32</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1886.709940409763</v>
+        <v>1886.709323799326</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>89.843330495703</v>
+        <v>89.84330113330124</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>92.36277782504365</v>
+        <v>92.36274834479887</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>-137.559876113693</v>
@@ -11392,13 +11806,13 @@
         <v>32</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>2038.134959126734</v>
+        <v>2037.83198760072</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>97.0540456727016</v>
+        <v>97.03961845717714</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>99.2183072912615</v>
+        <v>99.1997593039206</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>-134.0291433850872</v>
@@ -11423,13 +11837,13 @@
         <v>32</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1862.503537879544</v>
+        <v>1854.576829233538</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>88.69064466093064</v>
+        <v>88.31318234445419</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>90.7386484577308</v>
+        <v>90.35258008546295</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>-142.0130301038372</v>
@@ -11454,13 +11868,13 @@
         <v>32</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1978.765058541093</v>
+        <v>1973.778539099014</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>94.22690754957588</v>
+        <v>93.98945424281018</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>96.25967311506058</v>
+        <v>96.01584692385737</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>-141.0210867444622</v>
@@ -11485,13 +11899,13 @@
         <v>32</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1970.733587619723</v>
+        <v>1969.290220667299</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>93.84445655332013</v>
+        <v>93.77572479368091</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>96.53134012187597</v>
+        <v>96.48711975470562</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>-138.175883344804</v>
@@ -11516,13 +11930,13 @@
         <v>32</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1978.51264602361</v>
+        <v>1973.590435217465</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>94.21488790588621</v>
+        <v>93.98049691511737</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>96.24738967973549</v>
+        <v>96.00663434736354</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>-141.031386701102</v>
@@ -11547,13 +11961,13 @@
         <v>32</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1715.71405831587</v>
+        <v>1704.034876321672</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>81.70066944361287</v>
+        <v>81.14451792007962</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>83.64201161963413</v>
+        <v>83.0770227284209</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>-145.8025992482987</v>
@@ -11671,13 +12085,13 @@
         <v>32</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>2034.104414214825</v>
+        <v>2033.450901968842</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>96.86211496261069</v>
+        <v>96.83099533184961</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>99.0038515271772</v>
+        <v>98.96380752801737</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>-134.7043477684897</v>
@@ -11702,13 +12116,13 @@
         <v>32</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>1841.282546964035</v>
+        <v>1832.083784918221</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>87.68012128400166</v>
+        <v>87.24208499610575</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>89.71141915511171</v>
+        <v>89.26347174905015</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>-142.6882344872397</v>
@@ -11733,13 +12147,13 @@
         <v>32</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>1972.214487720199</v>
+        <v>1966.691356161558</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>93.91497560572377</v>
+        <v>93.65196934102659</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>95.93904597283073</v>
+        <v>95.66920346560894</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>-141.6962911278647</v>
@@ -11795,13 +12209,13 @@
         <v>32</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>1972.02638383865</v>
+        <v>1966.372814304142</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>93.90601827803097</v>
+        <v>93.63680068114964</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>95.9298333963369</v>
+        <v>95.65360350274608</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>-141.7065910845045</v>
@@ -11826,13 +12240,13 @@
         <v>32</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>1683.326367898159</v>
+        <v>1671.123973005875</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>80.15839847134092</v>
+        <v>79.57733204789882</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>82.08392663588319</v>
+        <v>81.49402202445653</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>-146.4778036317011</v>
@@ -11905,7 +12319,9 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:I28"/>
+  <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -11913,7 +12329,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -12504,10 +12920,10 @@
         <v>17.18</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>17.17958892637523</v>
+        <v>17.17897231593808</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>99.99760725480344</v>
+        <v>99.9940181370086</v>
       </c>
     </row>
     <row r="25" ht="36" customHeight="1">
@@ -14480,6 +14896,4751 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:F106"/>
+  <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D138"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="45" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Источник</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Назначение</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Соединение</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="21" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>LTE-B3-О1:M1</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>H-B3-M1:I1</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>МТС</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="21" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>LTE-B3-О2:M1</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>H-B3-M1:I2</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Резерв, мощность не задана</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="21" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>LTE-B3-О3:M1</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>H-B3-M1:I3</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Резерв, мощность не задана</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="21" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>H-B3-M1:O1</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>TP-Z1-M1:B3</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="21" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>H-B3-M1:O2</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>TP-Z2-M1:B3</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="21" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>H-B3-M1:O3</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>TP-Z3-M1:B3</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="21" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>H-B3-M1:O4</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>TP-Z4-M1:B3</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="21" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>LTE-B1-О1:M1</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>H-B1-M1:I1</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>МТС</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="21" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>LTE-B1-О2:M1</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>H-B1-M1:I2</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Резерв, мощность не задана</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="21" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>LTE-B1-О3:M1</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>H-B1-M1:I3</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Резерв, мощность не задана</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="21" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Нагрузка 50 Ом</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>H-B1-M1:I4</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Не представлена в перечне</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Неукомплектовано</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="21" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>H-B1-M1:O1</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>TP-Z1-M1:B1</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="21" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>H-B1-M1:O2</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>TP-Z2-M1:B1</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="21" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>H-B1-M1:O3</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>TP-Z3-M1:B1</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="21" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>H-B1-M1:O4</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>TP-Z4-M1:B1</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="21" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>LTE-B7-О1:M1</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>H-B7-M1:I1</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>МТС</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="21" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>LTE-B7-О2:M1</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>H-B7-M1:I2</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Резерв, мощность не задана</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="21" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>LTE-B7-О3:M1</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>H-B7-M1:I3</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Резерв, мощность не задана</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="21" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Нагрузка 50 Ом</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>H-B7-M1:I4</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Не представлена в перечне</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Неукомплектовано</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="21" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>H-B7-M1:O1</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>TP-Z1-M1:B7</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="21" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>H-B7-M1:O2</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>TP-Z2-M1:B7</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="21" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>H-B7-M1:O3</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>TP-Z3-M1:B7</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="21" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>H-B7-M1:O4</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>TP-Z4-M1:B7</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="21" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>TP-Z1-M1:COMMON</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>S-Z1-M1:IN</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>T1-M1, 7/8</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="21" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>S-Z1-M1:O1</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z1-1-M1:IN</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>F1-1-M1, 7/8</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="21" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z1-1-M1:O1</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>A01:P1</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>A01-M1, 1/2 + джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="21" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z1-1-M1:O2</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>A02:P1</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>A02-M1, 1/2 + джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="21" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z1-1-M1:O3</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>A03:P1</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>A03-M1, 1/2 + джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="21" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z1-1-M1:O4</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>A04:P1</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>A04-M1, 1/2 + джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="21" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>S-Z1-M1:O2</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z1-2-M1:IN</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>F1-2-M1, 7/8</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="21" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z1-2-M1:O1</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>A05:P1</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>A05-M1, 1/2 + джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="21" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z1-2-M1:O2</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>A06:P1</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>A06-M1, 1/2 + джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="21" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z1-2-M1:O3</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>A07:P1</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>A07-M1, 1/2 + джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="21" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z1-2-M1:O4</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>A08:P1</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>A08-M1, 7/8 + джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="21" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>TP-Z2-M1:COMMON</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>S-Z2-M1:IN</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>T2-M1, 7/8</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="21" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>S-Z2-M1:O1</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z2-1-M1:IN</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>F2-1-M1, джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="21" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z2-1-M1:O1</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>A09:P1</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>A09-M1, 1/2 + джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="21" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z2-1-M1:O2</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>A10:P1</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>A10-M1, 1/2 + джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="21" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z2-1-M1:O3</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>A11:P1</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>A11-M1, 1/2 + джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="21" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z2-1-M1:O4</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>A12:P1</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>A12-M1, 7/8 + джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="21" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>S-Z2-M1:O2</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z2-2-M1:IN</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>F2-2-M1, 7/8</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="21" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z2-2-M1:O1</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>A13:P1</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>A13-M1, 1/2 + джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="21" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z2-2-M1:O2</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>A14:P1</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>A14-M1, 1/2 + джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="21" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z2-2-M1:O3</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>A15:P1</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>A15-M1, 1/2 + джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="21" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z2-2-M1:O4</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>A16:P1</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>A16-M1, 1/2 + джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="21" customHeight="1">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>TP-Z3-M1:COMMON</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>S-Z3-M1:IN</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>T3-M1, 7/8</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="21" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>S-Z3-M1:O1</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z3-1-M1:IN</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>F3-1-M1, джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="21" customHeight="1">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z3-1-M1:O1</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>A17:P1</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>A17-M1, 1/2 + джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="21" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z3-1-M1:O2</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>A18:P1</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>A18-M1, 1/2 + джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="21" customHeight="1">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z3-1-M1:O3</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>A19:P1</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>A19-M1, 1/2 + джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="21" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z3-1-M1:O4</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>A20:P1</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>A20-M1, 1/2 + джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="21" customHeight="1">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>S-Z3-M1:O2</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z3-2-M1:IN</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>F3-2-M1, 7/8</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="21" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z3-2-M1:O1</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>A21:P1</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>A21-M1, 1/2 + джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="21" customHeight="1">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z3-2-M1:O2</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>A22:P1</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>A22-M1, 1/2 + джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="21" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z3-2-M1:O3</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>A23:P1</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>A23-M1, 1/2 + джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="21" customHeight="1">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z3-2-M1:O4</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>A24:P1</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>A24-M1, 1/2 + джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="21" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>TP-Z4-M1:COMMON</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>S-Z4-M1:IN</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>T4-M1, 7/8</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="21" customHeight="1">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>S-Z4-M1:O1</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z4-1-M1:IN</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>F4-1-M1, джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="21" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z4-1-M1:O1</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>A25:P1</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>A25-M1, 1/2 + джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="21" customHeight="1">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z4-1-M1:O2</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>A26:P1</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>A26-M1, 7/8 + джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="21" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z4-1-M1:O3</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>A27:P1</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>A27-M1, 1/2 + джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="21" customHeight="1">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z4-1-M1:O4</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>A28:P1</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>A28-M1, 7/8 + джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="21" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>S-Z4-M1:O2</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z4-2-M1:IN</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>F4-2-M1, 7/8</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="21" customHeight="1">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z4-2-M1:O1</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>A29:P1</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>A29-M1, 1/2 + джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="21" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z4-2-M1:O2</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>A30:P1</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>A30-M1, 1/2 + джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="21" customHeight="1">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z4-2-M1:O3</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>A31:P1</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>A31-M1, 1/2 + джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="21" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z4-2-M1:O4</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>A32:P1</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>A32-M1, 1/2 + джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="21" customHeight="1">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>LTE-B3-О1:M2</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>H-B3-M2:I1</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>МТС</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="21" customHeight="1">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>LTE-B3-О2:M2</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>H-B3-M2:I2</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Резерв, мощность не задана</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="21" customHeight="1">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>LTE-B3-О3:M2</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>H-B3-M2:I3</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Резерв, мощность не задана</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="21" customHeight="1">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>H-B3-M2:O1</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>TP-Z1-M2:B3</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="21" customHeight="1">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>H-B3-M2:O2</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>TP-Z2-M2:B3</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="21" customHeight="1">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>H-B3-M2:O3</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>TP-Z3-M2:B3</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="21" customHeight="1">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>H-B3-M2:O4</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>TP-Z4-M2:B3</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="21" customHeight="1">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>LTE-B1-О1:M2</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>H-B1-M2:I1</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>МТС</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="21" customHeight="1">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>LTE-B1-О2:M2</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>H-B1-M2:I2</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Резерв, мощность не задана</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="21" customHeight="1">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>LTE-B1-О3:M2</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>H-B1-M2:I3</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Резерв, мощность не задана</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="21" customHeight="1">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Нагрузка 50 Ом</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>H-B1-M2:I4</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Не представлена в перечне</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Неукомплектовано</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="21" customHeight="1">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>H-B1-M2:O1</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>TP-Z1-M2:B1</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="21" customHeight="1">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>H-B1-M2:O2</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>TP-Z2-M2:B1</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="21" customHeight="1">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>H-B1-M2:O3</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>TP-Z3-M2:B1</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="21" customHeight="1">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>H-B1-M2:O4</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>TP-Z4-M2:B1</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="21" customHeight="1">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>LTE-B7-О1:M2</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>H-B7-M2:I1</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>МТС</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="21" customHeight="1">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>LTE-B7-О2:M2</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>H-B7-M2:I2</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Резерв, мощность не задана</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="21" customHeight="1">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>LTE-B7-О3:M2</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>H-B7-M2:I3</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Резерв, мощность не задана</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="21" customHeight="1">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Нагрузка 50 Ом</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>H-B7-M2:I4</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Не представлена в перечне</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Неукомплектовано</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="21" customHeight="1">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>H-B7-M2:O1</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>TP-Z1-M2:B7</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="21" customHeight="1">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>H-B7-M2:O2</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>TP-Z2-M2:B7</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="21" customHeight="1">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>H-B7-M2:O3</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>TP-Z3-M2:B7</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="21" customHeight="1">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>H-B7-M2:O4</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>TP-Z4-M2:B7</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="21" customHeight="1">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>TP-Z1-M2:COMMON</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>S-Z1-M2:IN</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>T1-M2, 7/8</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="21" customHeight="1">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>S-Z1-M2:O1</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z1-1-M2:IN</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>F1-1-M2, 7/8</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="21" customHeight="1">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z1-1-M2:O1</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>A01:P2</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>A01-M2, 1/2 + джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="21" customHeight="1">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z1-1-M2:O2</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>A02:P2</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>A02-M2, 1/2 + джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="21" customHeight="1">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z1-1-M2:O3</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>A03:P2</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>A03-M2, 1/2 + джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="21" customHeight="1">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z1-1-M2:O4</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>A04:P2</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>A04-M2, 1/2 + джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="21" customHeight="1">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>S-Z1-M2:O2</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z1-2-M2:IN</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>F1-2-M2, 7/8</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="21" customHeight="1">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z1-2-M2:O1</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>A05:P2</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>A05-M2, 1/2 + джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="21" customHeight="1">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z1-2-M2:O2</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>A06:P2</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>A06-M2, 1/2 + джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="21" customHeight="1">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z1-2-M2:O3</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>A07:P2</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>A07-M2, 1/2 + джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="21" customHeight="1">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z1-2-M2:O4</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>A08:P2</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>A08-M2, 7/8 + джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="21" customHeight="1">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>TP-Z2-M2:COMMON</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>S-Z2-M2:IN</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>T2-M2, 7/8</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="21" customHeight="1">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>S-Z2-M2:O1</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z2-1-M2:IN</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>F2-1-M2, джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="21" customHeight="1">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z2-1-M2:O1</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>A09:P2</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>A09-M2, 1/2 + джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="21" customHeight="1">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z2-1-M2:O2</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>A10:P2</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>A10-M2, 1/2 + джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="21" customHeight="1">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z2-1-M2:O3</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>A11:P2</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>A11-M2, 1/2 + джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="21" customHeight="1">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z2-1-M2:O4</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>A12:P2</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>A12-M2, 7/8 + джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="21" customHeight="1">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>S-Z2-M2:O2</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z2-2-M2:IN</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>F2-2-M2, 7/8</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="21" customHeight="1">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z2-2-M2:O1</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>A13:P2</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>A13-M2, 1/2 + джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="21" customHeight="1">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z2-2-M2:O2</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>A14:P2</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>A14-M2, 1/2 + джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="21" customHeight="1">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z2-2-M2:O3</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>A15:P2</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>A15-M2, 1/2 + джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="21" customHeight="1">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z2-2-M2:O4</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>A16:P2</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>A16-M2, 1/2 + джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="21" customHeight="1">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>TP-Z3-M2:COMMON</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>S-Z3-M2:IN</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>T3-M2, 7/8</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="21" customHeight="1">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>S-Z3-M2:O1</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z3-1-M2:IN</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>F3-1-M2, джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="21" customHeight="1">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z3-1-M2:O1</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>A17:P2</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>A17-M2, 1/2 + джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="21" customHeight="1">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z3-1-M2:O2</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>A18:P2</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>A18-M2, 1/2 + джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="21" customHeight="1">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z3-1-M2:O3</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>A19:P2</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>A19-M2, 1/2 + джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="21" customHeight="1">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z3-1-M2:O4</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>A20:P2</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>A20-M2, 1/2 + джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="21" customHeight="1">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>S-Z3-M2:O2</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z3-2-M2:IN</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>F3-2-M2, 7/8</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="21" customHeight="1">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z3-2-M2:O1</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>A21:P2</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>A21-M2, 1/2 + джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="21" customHeight="1">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z3-2-M2:O2</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>A22:P2</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>A22-M2, 1/2 + джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="21" customHeight="1">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z3-2-M2:O3</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>A23:P2</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>A23-M2, 1/2 + джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="21" customHeight="1">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z3-2-M2:O4</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>A24:P2</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>A24-M2, 1/2 + джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="21" customHeight="1">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>TP-Z4-M2:COMMON</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>S-Z4-M2:IN</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>T4-M2, 7/8</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="21" customHeight="1">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>S-Z4-M2:O1</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z4-1-M2:IN</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>F4-1-M2, джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="21" customHeight="1">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z4-1-M2:O1</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>A25:P2</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>A25-M2, 1/2 + джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="21" customHeight="1">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z4-1-M2:O2</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>A26:P2</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>A26-M2, 7/8 + джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="21" customHeight="1">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z4-1-M2:O3</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>A27:P2</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>A27-M2, 1/2 + джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="21" customHeight="1">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z4-1-M2:O4</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>A28:P2</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>A28-M2, 7/8 + джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="21" customHeight="1">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>S-Z4-M2:O2</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z4-2-M2:IN</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>F4-2-M2, 7/8</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="21" customHeight="1">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z4-2-M2:O1</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>A29:P2</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>A29-M2, 1/2 + джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="21" customHeight="1">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z4-2-M2:O2</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>A30:P2</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>A30-M2, 1/2 + джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="21" customHeight="1">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z4-2-M2:O3</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>A31:P2</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>A31-M2, 1/2 + джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="21" customHeight="1">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z4-2-M2:O4</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>A32:P2</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>A32-M2, 1/2 + джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="21" customHeight="1">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>GSM:COMMON (2 TRX)</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>S-DCS:IN</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>Джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Общий выход БС принят условно</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="21" customHeight="1">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>S-DCS:O1</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>H-B3-M1:I4</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>Джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="21" customHeight="1">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>S-DCS:O2</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>H-B3-M2:I4</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>Джампер 3 м</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D138"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E72"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="110" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="45" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Модель</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>X, м</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Y, м</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Основание / ограничение</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="21" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>H-B3-M1</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>PC221</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Головной узел; размеры и монтажная раскладка не заданы</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="21" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>H-B1-M1</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>PC221</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Головной узел; размеры и монтажная раскладка не заданы</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="21" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>H-B7-M1</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>PC221</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Головной узел; размеры и монтажная раскладка не заданы</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="21" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>TP-Z1-M1</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>PC211</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Головной узел</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="21" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>S-Z1-M1</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>PC250</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>11.40886</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Зональное распределение по трассе</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="21" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z1-1-M1</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>PC252</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>11.40886</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>54.232997</v>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Подгруппа на трассе; M1/M2 показаны одной геометрической точкой</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="21" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z1-2-M1</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>PC252</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>11.40886</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>46.02057642602261</v>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Подгруппа на трассе; M1/M2 показаны одной геометрической точкой</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="21" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>TP-Z2-M1</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>PC211</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Головной узел</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="21" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>S-Z2-M1</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>PC250</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>25.987715</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Зональное распределение по трассе</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="21" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z2-1-M1</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>PC252</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>25.987715</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Подгруппа на трассе; M1/M2 показаны одной геометрической точкой</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="21" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z2-2-M1</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>PC252</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>31.41208068932767</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>39.986112</v>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Подгруппа на трассе; M1/M2 показаны одной геометрической точкой</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="21" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>TP-Z3-M1</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>PC211</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Головной узел</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="21" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>S-Z3-M1</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>PC250</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>11.839271</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>30.542096</v>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Зональное распределение по трассе</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="21" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z3-1-M1</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>PC252</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>11.839271</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>30.542096</v>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Подгруппа на трассе; M1/M2 показаны одной геометрической точкой</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="21" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z3-2-M1</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>PC252</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>1.315304</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>28.115735</v>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Подгруппа на трассе; M1/M2 показаны одной геометрической точкой</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="21" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>TP-Z4-M1</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>PC211</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Головной узел</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="21" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>S-Z4-M1</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>PC250</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>1.315304</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Зональное распределение по трассе</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="21" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z4-1-M1</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>PC252</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>1.315304</v>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Подгруппа на трассе; M1/M2 показаны одной геометрической точкой</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="21" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z4-2-M1</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>PC252</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>27.77381178875924</v>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>4.584693</v>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Подгруппа на трассе; M1/M2 показаны одной геометрической точкой</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="21" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>H-B3-M2</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>PC221</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Головной узел; размеры и монтажная раскладка не заданы</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="21" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>H-B1-M2</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>PC221</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Головной узел; размеры и монтажная раскладка не заданы</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="21" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>H-B7-M2</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>PC221</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Головной узел; размеры и монтажная раскладка не заданы</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="21" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>TP-Z1-M2</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>PC211</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Головной узел</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="21" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>S-Z1-M2</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>PC250</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>11.40886</v>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Зональное распределение по трассе</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="21" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z1-1-M2</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>PC252</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>11.40886</v>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>54.232997</v>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Подгруппа на трассе; M1/M2 показаны одной геометрической точкой</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="21" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z1-2-M2</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>PC252</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>11.40886</v>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>46.02057642602261</v>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Подгруппа на трассе; M1/M2 показаны одной геометрической точкой</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="21" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>TP-Z2-M2</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>PC211</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Головной узел</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="21" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>S-Z2-M2</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>PC250</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>25.987715</v>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Зональное распределение по трассе</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="21" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z2-1-M2</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>PC252</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>25.987715</v>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Подгруппа на трассе; M1/M2 показаны одной геометрической точкой</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="21" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z2-2-M2</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>PC252</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>31.41208068932767</v>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>39.986112</v>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Подгруппа на трассе; M1/M2 показаны одной геометрической точкой</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="21" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>TP-Z3-M2</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>PC211</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Головной узел</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="21" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>S-Z3-M2</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>PC250</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>11.839271</v>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>30.542096</v>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Зональное распределение по трассе</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="21" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z3-1-M2</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>PC252</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>11.839271</v>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>30.542096</v>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Подгруппа на трассе; M1/M2 показаны одной геометрической точкой</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="21" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z3-2-M2</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>PC252</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>1.315304</v>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>28.115735</v>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Подгруппа на трассе; M1/M2 показаны одной геометрической точкой</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="21" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>TP-Z4-M2</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>PC211</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Головной узел</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="21" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>S-Z4-M2</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>PC250</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>1.315304</v>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Зональное распределение по трассе</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="21" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z4-1-M2</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>PC252</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>1.315304</v>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Подгруппа на трассе; M1/M2 показаны одной геометрической точкой</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="21" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Q-Z4-2-M2</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>PC252</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>27.77381178875924</v>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>4.584693</v>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Подгруппа на трассе; M1/M2 показаны одной геометрической точкой</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="21" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>S-DCS</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>PC250</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Головной узел; общий GSM-выход условен</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="21" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>A01</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>In06</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>14.91956208510882</v>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>49.02438226281524</v>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Проектная точка у метки помещения; не утверждённое место крепления</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="21" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>A02</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>In06</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Дополнительная проектная точка общественной зоны</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="21" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>A03</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>In06</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>17.81482442176836</v>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>57.42404058032748</v>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Проектная точка у метки помещения; не утверждённое место крепления</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="21" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>A04</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>In06</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>4.091118794241845</v>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>58.49460955452709</v>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Проектная точка у метки помещения; не утверждённое место крепления</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="21" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>A05</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>In06</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>6.919409400363969</v>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>49.00438226281524</v>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Проектная точка у метки помещения; не утверждённое место крепления</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="21" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>A06</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>In06</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>6.919409400363969</v>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>46.02057642602261</v>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Проектная точка у метки помещения; не утверждённое место крепления</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="21" customHeight="1">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>A07</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>In06</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>13.06139527504399</v>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>43.21100027232224</v>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Проектная точка у метки помещения; не утверждённое место крепления</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="21" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>A08</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>In06</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>21.15567090665015</v>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>43.21100027232223</v>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Проектная точка у метки помещения; не утверждённое место крепления</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="21" customHeight="1">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>A09</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>In06</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>29.19373086464296</v>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>50.39514233149479</v>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Проектная точка у метки помещения; не утверждённое место крепления</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="21" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>A10</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>In06</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>28.71498086464297</v>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>45.08240239668498</v>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Проектная точка у метки помещения; не утверждённое место крепления</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="21" customHeight="1">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>A11</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>In06</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>31.3720806893277</v>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>58.70952398557016</v>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Проектная точка у метки помещения; не утверждённое место крепления</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="21" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>A12</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>In06</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>32.32895091386823</v>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>32.12879322850282</v>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Проектная точка у метки помещения; не утверждённое место крепления</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="21" customHeight="1">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>A13</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>In06</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>33.07601869054855</v>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>47.28251056928649</v>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Проектная точка у метки помещения; не утверждённое место крепления</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="21" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>A14</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>In06</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>35.52368472074298</v>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>46.83554124130971</v>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Проектная точка у метки помещения; не утверждённое место крепления</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="21" customHeight="1">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>A15</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>In06</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>31.41208068932767</v>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>40.62021820570461</v>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Проектная точка у метки помещения; не утверждённое место крепления</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="21" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>A16</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>In06</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>29.08988086464297</v>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>36.82850186609248</v>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Проектная точка у метки помещения; не утверждённое место крепления</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="21" customHeight="1">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>A17</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>In06</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>14.47045902428027</v>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>28.04576712019808</v>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Проектная точка у метки помещения; не утверждённое место крепления</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="21" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>A18</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>In06</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>17.76328876497633</v>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>28.04576712019808</v>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Проектная точка у метки помещения; не утверждённое место крепления</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="21" customHeight="1">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>A19</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>In06</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>17.75628876497632</v>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>23.56811553916096</v>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Проектная точка у метки помещения; не утверждённое место крепления</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="21" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>A20</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>In06</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>6.504428906468076</v>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>24.68838479882195</v>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Проектная точка у метки помещения; не утверждённое место крепления</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="21" customHeight="1">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>A21</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>In06</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>3.59031425843235</v>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>30.792355587748</v>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Проектная точка у метки помещения; не утверждённое место крепления</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="36" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>A22</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>In06</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>0.3757184834514796</v>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>32.21789008037059</v>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Проектная точка у метки помещения; не утверждённое место крепления</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="21" customHeight="1">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>A23</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>In06</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>2.781136557840948</v>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>25.12117083652631</v>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Проектная точка у метки помещения; не утверждённое место крепления</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="21" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>A24</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>In06</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>1.034618740440041</v>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>27.93276712019818</v>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Проектная точка у метки помещения; не утверждённое место крепления</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="21" customHeight="1">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>A25</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>In06</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>2.98386788680957</v>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>3.667097893003584</v>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>Проектная точка у метки помещения; не утверждённое место крепления</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="21" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>A26</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>In06</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>25.94794473608991</v>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>13.43621536943447</v>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Проектная точка у метки помещения; не утверждённое место крепления</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="21" customHeight="1">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>A27</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>In06</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>3.043738882363523</v>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>15.14188377635066</v>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>Проектная точка у метки помещения; не утверждённое место крепления</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="21" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>A28</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>In06</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>33.49358964038934</v>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>21.87877117801221</v>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Проектная точка у метки помещения; не утверждённое место крепления</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="36" customHeight="1">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>A29</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>In06</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>26.02656051314887</v>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>3.839605595684517</v>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>Проектная точка перенесена на 1,5 м внутри CAD-группы 114.1+126; полный расчёт покрытия выполнен</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="21" customHeight="1">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>A30</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>In06</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>27.77381178875924</v>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>2.132269541326413</v>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Проектная точка у метки помещения; не утверждённое место крепления</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="21" customHeight="1">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>A31</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>In06</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>32.56868381663132</v>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>2.111169541326414</v>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>Проектная точка у метки помещения; не утверждённое место крепления</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="21" customHeight="1">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>A32</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>In06</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v>34.76515714743073</v>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>5.653403907351852</v>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Проектная точка перенесена на 1,5 м внутри CAD-группы 121; полный расчёт покрытия выполнен</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E72"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/equipment/bill-of-materials-draft.xlsx
+++ b/equipment/bill-of-materials-draft.xlsx
@@ -35,9 +35,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'RF и RSRP'!$A$1:$F$385</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'RF и RSRP'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'RF и RSRP'!$A$1:$F$385</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Покрытие сценарии'!$A$1:$I$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Покрытие сценарии'!$A$1:$I$40</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Покрытие сценарии'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'Покрытие сценарии'!$A$1:$I$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Покрытие сценарии'!$A$1:$I$40</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Покрытие помещения'!$A$1:$F$109</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Покрытие помещения'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'Покрытие помещения'!$A$1:$F$109</definedName>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>292</v>
+        <v>179</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1316</v>
+        <v>1366</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
@@ -829,10 +829,10 @@
         <v>0</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>97.65558306260813</v>
+        <v>97.6596979825995</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>-104.8734294869009</v>
+        <v>-103.8406708132619</v>
       </c>
       <c r="F2" s="2" t="b">
         <v>1</v>
@@ -854,7 +854,7 @@
         <v>97.65558306260813</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-107.8837294435407</v>
+        <v>-106.8509707699017</v>
       </c>
       <c r="F3" s="2" t="b">
         <v>1</v>
@@ -873,10 +873,10 @@
         <v>0</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>97.59410754880625</v>
+        <v>97.61633602937316</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>-114.8734294869009</v>
+        <v>-113.8406708132619</v>
       </c>
       <c r="F4" s="2" t="b">
         <v>1</v>
@@ -898,7 +898,7 @@
         <v>97.65558306260813</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-107.8734294869009</v>
+        <v>-106.8406708132619</v>
       </c>
       <c r="F5" s="2" t="b">
         <v>1</v>
@@ -981,7 +981,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>42 male + 42 female</t>
+          <t>34 male + 34 female</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>62 male + 22 female</t>
+          <t>70 male + 30 female</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>18 входов LTE + 1 вход GSM + 2 связи после PC250 + 24 связи PC221→PC211 + 64 антенных + 4 местных связей PC250→PC252. При подключённом только МТС 12 входных связей зарезервированы. Порты БС и пригодность длины 3 м не подтверждены.</t>
+          <t>18 входов LTE + 1 вход GSM + 2 связи после PC250 + 24 связи PC221→PC211 + 64 антенных + 4 местных связей S→Q. При подключённом только МТС 12 входных связей зарезервированы. Порты БС и пригодность длины 3 м не подтверждены.</t>
         </is>
       </c>
     </row>
@@ -1771,10 +1771,10 @@
         <v>2</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>20.0089</v>
+        <v>14.2199</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>40.0177</v>
+        <v>28.4397</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -1797,10 +1797,10 @@
         <v>2</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>36.6066</v>
+        <v>14.0957</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>73.2133</v>
+        <v>28.1914</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -1823,10 +1823,10 @@
         <v>2</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>3.2972</v>
+        <v>7.8193</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>6.5943</v>
+        <v>15.6385</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -1849,10 +1849,10 @@
         <v>2</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>35.6225</v>
+        <v>30.9806</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>71.245</v>
+        <v>61.9612</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -1875,10 +1875,10 @@
         <v>2</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>5.233</v>
+        <v>2.8096</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>10.466</v>
+        <v>5.6192</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -1894,21 +1894,21 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>7/8</t>
+          <t>jumper</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v>2</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>2.9794</v>
+        <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>5.9588</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Проектная аппроксимация CAD-лотков; без запаса</t>
+          <t>Соседние устройства: два заводских джампера по 3 м; не нулевой фидер</t>
         </is>
       </c>
     </row>
@@ -1920,21 +1920,21 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>jumper</t>
+          <t>7/8</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v>2</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0</v>
+        <v>0.2222</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0</v>
+        <v>0.4444</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Соседние устройства: два заводских джампера по 3 м; не нулевой фидер</t>
+          <t>Проектная аппроксимация CAD-лотков; без запаса</t>
         </is>
       </c>
     </row>
@@ -1953,10 +1953,10 @@
         <v>2</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>33.3263</v>
+        <v>18.2183</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>66.65260000000001</v>
+        <v>36.4366</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -2005,10 +2005,10 @@
         <v>2</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>12.7882</v>
+        <v>8.2661</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>25.5764</v>
+        <v>16.5322</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -2031,10 +2031,10 @@
         <v>2</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>32.0479</v>
+        <v>13.7258</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>64.0959</v>
+        <v>27.4515</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -2057,10 +2057,10 @@
         <v>2</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>9.0839</v>
+        <v>5.7734</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>18.1677</v>
+        <v>11.5469</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -2083,10 +2083,10 @@
         <v>2</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>3.5351</v>
+        <v>9.3241</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>7.0702</v>
+        <v>18.6482</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -2109,10 +2109,10 @@
         <v>2</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>9.8165</v>
+        <v>12.6261</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>19.6331</v>
+        <v>25.2522</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -2128,17 +2128,17 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>7/8</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v>2</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>8.9087</v>
+        <v>19.4156</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>17.8175</v>
+        <v>38.8312</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -2154,17 +2154,17 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>7/8</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v>2</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>11.8174</v>
+        <v>22.8394</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>23.6349</v>
+        <v>45.6789</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -2187,10 +2187,10 @@
         <v>2</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>56.7724</v>
+        <v>50.9834</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>113.5449</v>
+        <v>101.9669</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -2239,10 +2239,10 @@
         <v>2</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>4.4621</v>
+        <v>1.6525</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>8.924200000000001</v>
+        <v>3.3051</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -2265,10 +2265,10 @@
         <v>2</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>48.2614</v>
+        <v>39.4518</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>96.5228</v>
+        <v>78.9036</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -2284,17 +2284,17 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>7/8</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v>2</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>3.1012</v>
+        <v>37.4086</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>6.2023</v>
+        <v>74.8171</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -2310,17 +2310,17 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>7/8</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v>2</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>35.136</v>
+        <v>4.4471</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>70.2719</v>
+        <v>8.8942</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -2336,17 +2336,17 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>7/8</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v>2</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>14.3497</v>
+        <v>36.6384</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>28.6993</v>
+        <v>73.27679999999999</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -2369,10 +2369,10 @@
         <v>2</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>41.4686</v>
+        <v>26.3606</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>82.9372</v>
+        <v>52.7212</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -2421,10 +2421,10 @@
         <v>2</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>43.641</v>
+        <v>28.533</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>87.282</v>
+        <v>57.066</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -2499,10 +2499,10 @@
         <v>2</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>10.4401</v>
+        <v>6.9038</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>20.8802</v>
+        <v>13.8075</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2525,10 +2525,10 @@
         <v>2</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>8.420299999999999</v>
+        <v>3.4432</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>16.8407</v>
+        <v>6.8864</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2544,17 +2544,17 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>7/8</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v>2</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>15.3296</v>
+        <v>7.0635</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>30.6593</v>
+        <v>14.127</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2577,10 +2577,10 @@
         <v>2</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>26.453</v>
+        <v>21.9309</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>52.906</v>
+        <v>43.8618</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2648,17 +2648,17 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>7/8</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v>2</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>7.8818</v>
+        <v>16.9779</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>15.7635</v>
+        <v>33.9558</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2674,17 +2674,17 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>7/8</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v>2</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>16.6732</v>
+        <v>3.885</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>33.3465</v>
+        <v>7.77</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2726,17 +2726,17 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>7/8</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v>2</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>8.8515</v>
+        <v>45.5431</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>17.703</v>
+        <v>91.08629999999999</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2759,10 +2759,10 @@
         <v>2</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>6.3703</v>
+        <v>2.5328</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>12.7406</v>
+        <v>5.0656</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2785,10 +2785,10 @@
         <v>2</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>67.1447</v>
+        <v>59.1924</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>134.2894</v>
+        <v>118.3848</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2811,10 +2811,10 @@
         <v>2</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>24.2408</v>
+        <v>32.1931</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>48.4817</v>
+        <v>64.38630000000001</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2830,17 +2830,17 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>7/8</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v>2</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>4.2783</v>
+        <v>35.1947</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>8.5566</v>
+        <v>70.38939999999999</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2863,10 +2863,10 @@
         <v>2</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>1.1854</v>
+        <v>0.0663</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>2.3708</v>
+        <v>0.1325</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2970,13 +2970,13 @@
         <v>5</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1.399151616705539</v>
+        <v>1.681654803416214</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>16.71975152998516</v>
+        <v>17.00225471669584</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-73.06465511815544</v>
+        <v>-73.34715830486613</v>
       </c>
     </row>
     <row r="3" ht="21" customHeight="1">
@@ -2992,13 +2992,13 @@
         <v>10</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1.399151616705539</v>
+        <v>1.681654803416214</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>16.71975152998516</v>
+        <v>17.00225471669584</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-77.72022323833562</v>
+        <v>-78.00272642504629</v>
       </c>
     </row>
     <row r="4" ht="21" customHeight="1">
@@ -3014,13 +3014,13 @@
         <v>15</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1.399151616705539</v>
+        <v>1.681654803416214</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>16.71975152998516</v>
+        <v>17.00225471669584</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-81.37257347317794</v>
+        <v>-81.65507665988861</v>
       </c>
     </row>
     <row r="5" ht="21" customHeight="1">
@@ -3036,13 +3036,13 @@
         <v>20</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1.399151616705539</v>
+        <v>1.681654803416214</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>16.71975152998516</v>
+        <v>17.00225471669584</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-84.20701257618606</v>
+        <v>-84.48951576289673</v>
       </c>
     </row>
     <row r="6" ht="21" customHeight="1">
@@ -3058,13 +3058,13 @@
         <v>5</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1.523008131836856</v>
+        <v>1.830982917349313</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>16.84360804511648</v>
+        <v>17.15158283062894</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-73.27806005981603</v>
+        <v>-73.58603484532848</v>
       </c>
     </row>
     <row r="7" ht="21" customHeight="1">
@@ -3080,13 +3080,13 @@
         <v>10</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1.523008131836856</v>
+        <v>1.830982917349313</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>16.84360804511648</v>
+        <v>17.15158283062894</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-77.93362817999621</v>
+        <v>-78.24160296550866</v>
       </c>
     </row>
     <row r="8" ht="21" customHeight="1">
@@ -3102,13 +3102,13 @@
         <v>15</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1.523008131836856</v>
+        <v>1.830982917349313</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>16.84360804511648</v>
+        <v>17.15158283062894</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-81.58597841483852</v>
+        <v>-81.89395320035098</v>
       </c>
     </row>
     <row r="9" ht="21" customHeight="1">
@@ -3124,13 +3124,13 @@
         <v>20</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1.523008131836856</v>
+        <v>1.830982917349313</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>16.84360804511648</v>
+        <v>17.15158283062894</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-84.42041751784664</v>
+        <v>-84.7283923033591</v>
       </c>
     </row>
     <row r="10" ht="21" customHeight="1">
@@ -3146,13 +3146,13 @@
         <v>5</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1.716445268562862</v>
+        <v>2.063592285565938</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>17.03704518184249</v>
+        <v>17.38419219884556</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-73.56566567072319</v>
+        <v>-73.91281268772627</v>
       </c>
     </row>
     <row r="11" ht="21" customHeight="1">
@@ -3168,13 +3168,13 @@
         <v>10</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1.716445268562862</v>
+        <v>2.063592285565938</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>17.03704518184249</v>
+        <v>17.38419219884556</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-78.22123379090337</v>
+        <v>-78.56838080790645</v>
       </c>
     </row>
     <row r="12" ht="21" customHeight="1">
@@ -3190,13 +3190,13 @@
         <v>15</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>1.716445268562862</v>
+        <v>2.063592285565938</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>17.03704518184249</v>
+        <v>17.38419219884556</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-81.87358402574569</v>
+        <v>-82.22073104274877</v>
       </c>
     </row>
     <row r="13" ht="21" customHeight="1">
@@ -3212,13 +3212,13 @@
         <v>20</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>1.716445268562862</v>
+        <v>2.063592285565938</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>17.03704518184249</v>
+        <v>17.38419219884556</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-84.70802312875382</v>
+        <v>-85.0551701457569</v>
       </c>
     </row>
     <row r="14" ht="21" customHeight="1">
@@ -3234,13 +3234,13 @@
         <v>5</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>2.188177861662389</v>
+        <v>2.014829241554524</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>24.02937768822164</v>
+        <v>24.05602906811377</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-80.37428127639193</v>
+        <v>-80.40093265628406</v>
       </c>
     </row>
     <row r="15" ht="21" customHeight="1">
@@ -3256,13 +3256,13 @@
         <v>10</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>2.188177861662389</v>
+        <v>2.014829241554524</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>24.02937768822164</v>
+        <v>24.05602906811377</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-85.0298493965721</v>
+        <v>-85.05650077646423</v>
       </c>
     </row>
     <row r="16" ht="21" customHeight="1">
@@ -3278,13 +3278,13 @@
         <v>15</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>2.188177861662389</v>
+        <v>2.014829241554524</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>24.02937768822164</v>
+        <v>24.05602906811377</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-88.68219963141442</v>
+        <v>-88.70885101130655</v>
       </c>
     </row>
     <row r="17" ht="21" customHeight="1">
@@ -3300,13 +3300,13 @@
         <v>20</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>2.188177861662389</v>
+        <v>2.014829241554524</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>24.02937768822164</v>
+        <v>24.05602906811377</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-91.51663873442254</v>
+        <v>-91.54329011431467</v>
       </c>
     </row>
     <row r="18" ht="21" customHeight="1">
@@ -3322,13 +3322,13 @@
         <v>5</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>2.382272772714414</v>
+        <v>2.193875590802238</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>24.22347259927366</v>
+        <v>24.23507541736149</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-80.65792461397321</v>
+        <v>-80.66952743206103</v>
       </c>
     </row>
     <row r="19" ht="21" customHeight="1">
@@ -3344,13 +3344,13 @@
         <v>10</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>2.382272772714414</v>
+        <v>2.193875590802238</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>24.22347259927366</v>
+        <v>24.23507541736149</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-85.31349273415339</v>
+        <v>-85.32509555224121</v>
       </c>
     </row>
     <row r="20" ht="21" customHeight="1">
@@ -3366,13 +3366,13 @@
         <v>15</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>2.382272772714414</v>
+        <v>2.193875590802238</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>24.22347259927366</v>
+        <v>24.23507541736149</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-88.9658429689957</v>
+        <v>-88.97744578708352</v>
       </c>
     </row>
     <row r="21" ht="21" customHeight="1">
@@ -3388,13 +3388,13 @@
         <v>20</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>2.382272772714414</v>
+        <v>2.193875590802238</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>24.22347259927366</v>
+        <v>24.23507541736149</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-91.80028207200382</v>
+        <v>-91.81188489009165</v>
       </c>
     </row>
     <row r="22" ht="21" customHeight="1">
@@ -3410,13 +3410,13 @@
         <v>5</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>2.684892673596365</v>
+        <v>2.472603257525621</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>24.52609250015562</v>
+        <v>24.51380308408487</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-81.05471298903632</v>
+        <v>-81.04242357296557</v>
       </c>
     </row>
     <row r="23" ht="21" customHeight="1">
@@ -3432,13 +3432,13 @@
         <v>10</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>2.684892673596365</v>
+        <v>2.472603257525621</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>24.52609250015562</v>
+        <v>24.51380308408487</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-85.7102811092165</v>
+        <v>-85.69799169314575</v>
       </c>
     </row>
     <row r="24" ht="21" customHeight="1">
@@ -3454,13 +3454,13 @@
         <v>15</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>2.684892673596365</v>
+        <v>2.472603257525621</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>24.52609250015562</v>
+        <v>24.51380308408487</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-89.36263134405881</v>
+        <v>-89.35034192798807</v>
       </c>
     </row>
     <row r="25" ht="21" customHeight="1">
@@ -3476,13 +3476,13 @@
         <v>20</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>2.684892673596365</v>
+        <v>2.472603257525621</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>24.52609250015562</v>
+        <v>24.51380308408487</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-92.19707044706695</v>
+        <v>-92.18478103099621</v>
       </c>
     </row>
     <row r="26" ht="21" customHeight="1">
@@ -3498,13 +3498,13 @@
         <v>5</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>2.213991213539151</v>
+        <v>1.89878740465973</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>21.04489108345859</v>
+        <v>20.72968727457917</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-77.38979467162886</v>
+        <v>-77.07459086274946</v>
       </c>
     </row>
     <row r="27" ht="21" customHeight="1">
@@ -3520,13 +3520,13 @@
         <v>10</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>2.213991213539151</v>
+        <v>1.89878740465973</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>21.04489108345859</v>
+        <v>20.72968727457917</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-82.04536279180905</v>
+        <v>-81.73015898292962</v>
       </c>
     </row>
     <row r="28" ht="21" customHeight="1">
@@ -3542,13 +3542,13 @@
         <v>15</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>2.213991213539151</v>
+        <v>1.89878740465973</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>21.04489108345859</v>
+        <v>20.72968727457917</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-85.69771302665137</v>
+        <v>-85.38250921777194</v>
       </c>
     </row>
     <row r="29" ht="21" customHeight="1">
@@ -3564,13 +3564,13 @@
         <v>20</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>2.213991213539151</v>
+        <v>1.89878740465973</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>21.04489108345859</v>
+        <v>20.72968727457917</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>-88.53215212965949</v>
+        <v>-88.21694832078006</v>
       </c>
     </row>
     <row r="30" ht="21" customHeight="1">
@@ -3586,13 +3586,13 @@
         <v>5</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>2.410282290670294</v>
+        <v>2.066434661117211</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>21.24118216058973</v>
+        <v>20.89733453103665</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>-77.67563417528928</v>
+        <v>-77.33178654573619</v>
       </c>
     </row>
     <row r="31" ht="21" customHeight="1">
@@ -3608,13 +3608,13 @@
         <v>10</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>2.410282290670294</v>
+        <v>2.066434661117211</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>21.24118216058973</v>
+        <v>20.89733453103665</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>-82.33120229546945</v>
+        <v>-81.98735466591637</v>
       </c>
     </row>
     <row r="32" ht="21" customHeight="1">
@@ -3630,13 +3630,13 @@
         <v>15</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>2.410282290670294</v>
+        <v>2.066434661117211</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>21.24118216058973</v>
+        <v>20.89733453103665</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-85.98355253031177</v>
+        <v>-85.63970490075869</v>
       </c>
     </row>
     <row r="33" ht="21" customHeight="1">
@@ -3652,13 +3652,13 @@
         <v>20</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>2.410282290670294</v>
+        <v>2.066434661117211</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>21.24118216058973</v>
+        <v>20.89733453103665</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>-88.81799163331989</v>
+        <v>-88.47414400376681</v>
       </c>
     </row>
     <row r="34" ht="21" customHeight="1">
@@ -3674,13 +3674,13 @@
         <v>5</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>2.716448868981957</v>
+        <v>2.328839062528921</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>21.54734873890139</v>
+        <v>21.15973893244836</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-78.0759692277821</v>
+        <v>-77.68835942132907</v>
       </c>
     </row>
     <row r="35" ht="21" customHeight="1">
@@ -3696,13 +3696,13 @@
         <v>10</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>2.716448868981957</v>
+        <v>2.328839062528921</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>21.54734873890139</v>
+        <v>21.15973893244836</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>-82.73153734796227</v>
+        <v>-82.34392754150925</v>
       </c>
     </row>
     <row r="36" ht="21" customHeight="1">
@@ -3718,13 +3718,13 @@
         <v>15</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>2.716448868981957</v>
+        <v>2.328839062528921</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>21.54734873890139</v>
+        <v>21.15973893244836</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-86.38388758280459</v>
+        <v>-85.99627777635156</v>
       </c>
     </row>
     <row r="37" ht="21" customHeight="1">
@@ -3740,13 +3740,13 @@
         <v>20</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>2.716448868981957</v>
+        <v>2.328839062528921</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>21.54734873890139</v>
+        <v>21.15973893244836</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>-89.21832668581273</v>
+        <v>-88.8307168793597</v>
       </c>
     </row>
     <row r="38" ht="21" customHeight="1">
@@ -3762,13 +3762,13 @@
         <v>5</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>2.507480764448599</v>
+        <v>1.930789538286739</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>21.33838063436804</v>
+        <v>17.25138945156636</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>-77.68328422253832</v>
+        <v>-73.59629303973665</v>
       </c>
     </row>
     <row r="39" ht="21" customHeight="1">
@@ -3784,13 +3784,13 @@
         <v>10</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>2.507480764448599</v>
+        <v>1.930789538286739</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>21.33838063436804</v>
+        <v>17.25138945156636</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>-82.3388523427185</v>
+        <v>-78.25186115991683</v>
       </c>
     </row>
     <row r="40" ht="21" customHeight="1">
@@ -3806,13 +3806,13 @@
         <v>15</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>2.507480764448599</v>
+        <v>1.930789538286739</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>21.33838063436804</v>
+        <v>17.25138945156636</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>-85.99120257756081</v>
+        <v>-81.90421139475914</v>
       </c>
     </row>
     <row r="41" ht="21" customHeight="1">
@@ -3828,13 +3828,13 @@
         <v>20</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>2.507480764448599</v>
+        <v>1.930789538286739</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>21.33838063436804</v>
+        <v>17.25138945156636</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>-88.82564168056894</v>
+        <v>-84.73865049776727</v>
       </c>
     </row>
     <row r="42" ht="21" customHeight="1">
@@ -3850,13 +3850,13 @@
         <v>5</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>2.729950295080089</v>
+        <v>2.10126231901839</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>21.56085016499953</v>
+        <v>17.42186223229801</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>-77.99530217969908</v>
+        <v>-73.85631424699756</v>
       </c>
     </row>
     <row r="43" ht="21" customHeight="1">
@@ -3872,13 +3872,13 @@
         <v>10</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>2.729950295080089</v>
+        <v>2.10126231901839</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>21.56085016499953</v>
+        <v>17.42186223229801</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>-82.65087029987924</v>
+        <v>-78.51188236717773</v>
       </c>
     </row>
     <row r="44" ht="21" customHeight="1">
@@ -3894,13 +3894,13 @@
         <v>15</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>2.729950295080089</v>
+        <v>2.10126231901839</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>21.56085016499953</v>
+        <v>17.42186223229801</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>-86.30322053472156</v>
+        <v>-82.16423260202005</v>
       </c>
     </row>
     <row r="45" ht="21" customHeight="1">
@@ -3916,13 +3916,13 @@
         <v>20</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>2.729950295080089</v>
+        <v>2.10126231901839</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>21.56085016499953</v>
+        <v>17.42186223229801</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>-89.13765963772968</v>
+        <v>-84.99867170502817</v>
       </c>
     </row>
     <row r="46" ht="21" customHeight="1">
@@ -3938,13 +3938,13 @@
         <v>5</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>3.076741954934884</v>
+        <v>2.368089280163582</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>21.90764182485432</v>
+        <v>17.68868919344321</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>-78.43626231373503</v>
+        <v>-74.21730968232391</v>
       </c>
     </row>
     <row r="47" ht="21" customHeight="1">
@@ -3960,13 +3960,13 @@
         <v>10</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>3.076741954934884</v>
+        <v>2.368089280163582</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>21.90764182485432</v>
+        <v>17.68868919344321</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>-83.09183043391521</v>
+        <v>-78.87287780250409</v>
       </c>
     </row>
     <row r="48" ht="21" customHeight="1">
@@ -3982,13 +3982,13 @@
         <v>15</v>
       </c>
       <c r="D48" s="2" t="n">
-        <v>3.076741954934884</v>
+        <v>2.368089280163582</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>21.90764182485432</v>
+        <v>17.68868919344321</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>-86.74418066875752</v>
+        <v>-82.52522803734641</v>
       </c>
     </row>
     <row r="49" ht="21" customHeight="1">
@@ -4004,13 +4004,13 @@
         <v>20</v>
       </c>
       <c r="D49" s="2" t="n">
-        <v>3.076741954934884</v>
+        <v>2.368089280163582</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>21.90764182485432</v>
+        <v>17.68868919344321</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>-89.57861977176566</v>
+        <v>-85.35966714035455</v>
       </c>
     </row>
     <row r="50" ht="21" customHeight="1">
@@ -4026,13 +4026,13 @@
         <v>5</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>4.000305096120518</v>
+        <v>3.397091324496495</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>19.32090500940014</v>
+        <v>25.43829115105574</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>-75.66580859757042</v>
+        <v>-81.78319473922602</v>
       </c>
     </row>
     <row r="51" ht="21" customHeight="1">
@@ -4048,13 +4048,13 @@
         <v>10</v>
       </c>
       <c r="D51" s="2" t="n">
-        <v>4.000305096120518</v>
+        <v>3.397091324496495</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>19.32090500940014</v>
+        <v>25.43829115105574</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>-80.32137671775061</v>
+        <v>-86.43876285940621</v>
       </c>
     </row>
     <row r="52" ht="21" customHeight="1">
@@ -4070,13 +4070,13 @@
         <v>15</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>4.000305096120518</v>
+        <v>3.397091324496495</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>19.32090500940014</v>
+        <v>25.43829115105574</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>-83.97372695259293</v>
+        <v>-90.09111309424853</v>
       </c>
     </row>
     <row r="53" ht="21" customHeight="1">
@@ -4092,13 +4092,13 @@
         <v>20</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>4.000305096120518</v>
+        <v>3.397091324496495</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>19.32090500940014</v>
+        <v>25.43829115105574</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>-86.80816605560105</v>
+        <v>-92.92555219725665</v>
       </c>
     </row>
     <row r="54" ht="21" customHeight="1">
@@ -4114,13 +4114,13 @@
         <v>5</v>
       </c>
       <c r="D54" s="2" t="n">
-        <v>4.353499020154191</v>
+        <v>3.697026451035533</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>19.67409893343382</v>
+        <v>25.73822627759478</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>-76.10855094813337</v>
+        <v>-82.17267829229434</v>
       </c>
     </row>
     <row r="55" ht="21" customHeight="1">
@@ -4136,13 +4136,13 @@
         <v>10</v>
       </c>
       <c r="D55" s="2" t="n">
-        <v>4.353499020154191</v>
+        <v>3.697026451035533</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>19.67409893343382</v>
+        <v>25.73822627759478</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>-80.76411906831353</v>
+        <v>-86.8282464124745</v>
       </c>
     </row>
     <row r="56" ht="21" customHeight="1">
@@ -4158,13 +4158,13 @@
         <v>15</v>
       </c>
       <c r="D56" s="2" t="n">
-        <v>4.353499020154191</v>
+        <v>3.697026451035533</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>19.67409893343382</v>
+        <v>25.73822627759478</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>-84.41646930315585</v>
+        <v>-90.48059664731682</v>
       </c>
     </row>
     <row r="57" ht="21" customHeight="1">
@@ -4180,13 +4180,13 @@
         <v>20</v>
       </c>
       <c r="D57" s="2" t="n">
-        <v>4.353499020154191</v>
+        <v>3.697026451035533</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>19.67409893343382</v>
+        <v>25.73822627759478</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>-87.25090840616397</v>
+        <v>-93.31503575032494</v>
       </c>
     </row>
     <row r="58" ht="21" customHeight="1">
@@ -4202,13 +4202,13 @@
         <v>5</v>
       </c>
       <c r="D58" s="2" t="n">
-        <v>4.906324292554723</v>
+        <v>4.166490127357505</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>20.22692420583435</v>
+        <v>26.20768995391676</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>-76.75554469471506</v>
+        <v>-82.73631044279746</v>
       </c>
     </row>
     <row r="59" ht="21" customHeight="1">
@@ -4224,13 +4224,13 @@
         <v>10</v>
       </c>
       <c r="D59" s="2" t="n">
-        <v>4.906324292554723</v>
+        <v>4.166490127357505</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>20.22692420583435</v>
+        <v>26.20768995391676</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>-81.41111281489523</v>
+        <v>-87.39187856297764</v>
       </c>
     </row>
     <row r="60" ht="21" customHeight="1">
@@ -4246,13 +4246,13 @@
         <v>15</v>
       </c>
       <c r="D60" s="2" t="n">
-        <v>4.906324292554723</v>
+        <v>4.166490127357505</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>20.22692420583435</v>
+        <v>26.20768995391676</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>-85.06346304973755</v>
+        <v>-91.04422879781995</v>
       </c>
     </row>
     <row r="61" ht="21" customHeight="1">
@@ -4268,13 +4268,13 @@
         <v>20</v>
       </c>
       <c r="D61" s="2" t="n">
-        <v>4.906324292554723</v>
+        <v>4.166490127357505</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>20.22692420583435</v>
+        <v>26.20768995391676</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>-87.89790215274569</v>
+        <v>-93.87866790082809</v>
       </c>
     </row>
     <row r="62" ht="21" customHeight="1">
@@ -4290,13 +4290,13 @@
         <v>5</v>
       </c>
       <c r="D62" s="2" t="n">
-        <v>1.650675139707497</v>
+        <v>1.340219203299054</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>23.49187496626675</v>
+        <v>20.17111907321849</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>-79.83677855443703</v>
+        <v>-76.51602266138877</v>
       </c>
     </row>
     <row r="63" ht="21" customHeight="1">
@@ -4312,13 +4312,13 @@
         <v>10</v>
       </c>
       <c r="D63" s="2" t="n">
-        <v>1.650675139707497</v>
+        <v>1.340219203299054</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>23.49187496626675</v>
+        <v>20.17111907321849</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>-84.49234667461721</v>
+        <v>-81.17159078156895</v>
       </c>
     </row>
     <row r="64" ht="21" customHeight="1">
@@ -4334,13 +4334,13 @@
         <v>15</v>
       </c>
       <c r="D64" s="2" t="n">
-        <v>1.650675139707497</v>
+        <v>1.340219203299054</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>23.49187496626675</v>
+        <v>20.17111907321849</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>-88.14469690945953</v>
+        <v>-84.82394101641127</v>
       </c>
     </row>
     <row r="65" ht="21" customHeight="1">
@@ -4356,13 +4356,13 @@
         <v>20</v>
       </c>
       <c r="D65" s="2" t="n">
-        <v>1.650675139707497</v>
+        <v>1.340219203299054</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>23.49187496626675</v>
+        <v>20.17111907321849</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>-90.97913601246765</v>
+        <v>-87.65838011941939</v>
       </c>
     </row>
     <row r="66" ht="21" customHeight="1">
@@ -4378,13 +4378,13 @@
         <v>5</v>
       </c>
       <c r="D66" s="2" t="n">
-        <v>1.796826299544518</v>
+        <v>1.458959666255482</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>23.63802612610377</v>
+        <v>20.28985953617492</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>-80.07247814080331</v>
+        <v>-76.72431155087446</v>
       </c>
     </row>
     <row r="67" ht="21" customHeight="1">
@@ -4400,13 +4400,13 @@
         <v>10</v>
       </c>
       <c r="D67" s="2" t="n">
-        <v>1.796826299544518</v>
+        <v>1.458959666255482</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>23.63802612610377</v>
+        <v>20.28985953617492</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>-84.72804626098349</v>
+        <v>-81.37987967105464</v>
       </c>
     </row>
     <row r="68" ht="21" customHeight="1">
@@ -4422,13 +4422,13 @@
         <v>15</v>
       </c>
       <c r="D68" s="2" t="n">
-        <v>1.796826299544518</v>
+        <v>1.458959666255482</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>23.63802612610377</v>
+        <v>20.28985953617492</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>-88.38039649582581</v>
+        <v>-85.03222990589695</v>
       </c>
     </row>
     <row r="69" ht="21" customHeight="1">
@@ -4444,13 +4444,13 @@
         <v>20</v>
       </c>
       <c r="D69" s="2" t="n">
-        <v>1.796826299544518</v>
+        <v>1.458959666255482</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>23.63802612610377</v>
+        <v>20.28985953617492</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>-91.21483559883393</v>
+        <v>-87.86666900890508</v>
       </c>
     </row>
     <row r="70" ht="21" customHeight="1">
@@ -4466,13 +4466,13 @@
         <v>5</v>
       </c>
       <c r="D70" s="2" t="n">
-        <v>2.025044601318738</v>
+        <v>1.644274268564428</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>23.86624442787799</v>
+        <v>20.47517413848387</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>-80.39486491675869</v>
+        <v>-77.00379462736457</v>
       </c>
     </row>
     <row r="71" ht="21" customHeight="1">
@@ -4488,13 +4488,13 @@
         <v>10</v>
       </c>
       <c r="D71" s="2" t="n">
-        <v>2.025044601318738</v>
+        <v>1.644274268564428</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>23.86624442787799</v>
+        <v>20.47517413848387</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>-85.05043303693887</v>
+        <v>-81.65936274754475</v>
       </c>
     </row>
     <row r="72" ht="21" customHeight="1">
@@ -4510,13 +4510,13 @@
         <v>15</v>
       </c>
       <c r="D72" s="2" t="n">
-        <v>2.025044601318738</v>
+        <v>1.644274268564428</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>23.86624442787799</v>
+        <v>20.47517413848387</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>-88.70278327178119</v>
+        <v>-85.31171298238706</v>
       </c>
     </row>
     <row r="73" ht="21" customHeight="1">
@@ -4532,13 +4532,13 @@
         <v>20</v>
       </c>
       <c r="D73" s="2" t="n">
-        <v>2.025044601318738</v>
+        <v>1.644274268564428</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>23.86624442787799</v>
+        <v>20.47517413848387</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>-91.53722237478932</v>
+        <v>-88.1461520853952</v>
       </c>
     </row>
     <row r="74" ht="21" customHeight="1">
@@ -4554,13 +4554,13 @@
         <v>5</v>
       </c>
       <c r="D74" s="2" t="n">
-        <v>1.647916617364528</v>
+        <v>0.9075955294399269</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>23.48911644392378</v>
+        <v>22.94879535599918</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>-79.83402003209406</v>
+        <v>-79.29369894416946</v>
       </c>
     </row>
     <row r="75" ht="21" customHeight="1">
@@ -4576,13 +4576,13 @@
         <v>10</v>
       </c>
       <c r="D75" s="2" t="n">
-        <v>1.647916617364528</v>
+        <v>0.9075955294399269</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>23.48911644392378</v>
+        <v>22.94879535599918</v>
       </c>
       <c r="F75" s="2" t="n">
-        <v>-84.48958815227424</v>
+        <v>-83.94926706434964</v>
       </c>
     </row>
     <row r="76" ht="21" customHeight="1">
@@ -4598,13 +4598,13 @@
         <v>15</v>
       </c>
       <c r="D76" s="2" t="n">
-        <v>1.647916617364528</v>
+        <v>0.9075955294399269</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>23.48911644392378</v>
+        <v>22.94879535599918</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>-88.14193838711655</v>
+        <v>-87.60161729919196</v>
       </c>
     </row>
     <row r="77" ht="21" customHeight="1">
@@ -4620,13 +4620,13 @@
         <v>20</v>
       </c>
       <c r="D77" s="2" t="n">
-        <v>1.647916617364528</v>
+        <v>0.9075955294399269</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>23.48911644392378</v>
+        <v>22.94879535599918</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>-90.97637749012468</v>
+        <v>-90.43605640220008</v>
       </c>
     </row>
     <row r="78" ht="21" customHeight="1">
@@ -4642,13 +4642,13 @@
         <v>5</v>
       </c>
       <c r="D78" s="2" t="n">
-        <v>1.793821724663523</v>
+        <v>0.9878797041680051</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>23.63502155122277</v>
+        <v>23.02907953072726</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>-80.06947356592232</v>
+        <v>-79.4635315454268</v>
       </c>
     </row>
     <row r="79" ht="21" customHeight="1">
@@ -4664,13 +4664,13 @@
         <v>10</v>
       </c>
       <c r="D79" s="2" t="n">
-        <v>1.793821724663523</v>
+        <v>0.9878797041680051</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>23.63502155122277</v>
+        <v>23.02907953072726</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>-84.7250416861025</v>
+        <v>-84.11909966560698</v>
       </c>
     </row>
     <row r="80" ht="21" customHeight="1">
@@ -4686,13 +4686,13 @@
         <v>15</v>
       </c>
       <c r="D80" s="2" t="n">
-        <v>1.793821724663523</v>
+        <v>0.9878797041680051</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>23.63502155122277</v>
+        <v>23.02907953072726</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>-88.37739192094482</v>
+        <v>-87.7714499004493</v>
       </c>
     </row>
     <row r="81" ht="21" customHeight="1">
@@ -4708,13 +4708,13 @@
         <v>20</v>
       </c>
       <c r="D81" s="2" t="n">
-        <v>1.793821724663523</v>
+        <v>0.9878797041680051</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>23.63502155122277</v>
+        <v>23.02907953072726</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>-91.21183102395294</v>
+        <v>-90.60588900345742</v>
       </c>
     </row>
     <row r="82" ht="21" customHeight="1">
@@ -4730,13 +4730,13 @@
         <v>5</v>
       </c>
       <c r="D82" s="2" t="n">
-        <v>2.021658189350957</v>
+        <v>1.113343107470173</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>23.86285801591021</v>
+        <v>23.15454293402942</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>-80.39147850479091</v>
+        <v>-79.68316342291013</v>
       </c>
     </row>
     <row r="83" ht="21" customHeight="1">
@@ -4752,13 +4752,13 @@
         <v>10</v>
       </c>
       <c r="D83" s="2" t="n">
-        <v>2.021658189350957</v>
+        <v>1.113343107470173</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>23.86285801591021</v>
+        <v>23.15454293402942</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>-85.04704662497109</v>
+        <v>-84.3387315430903</v>
       </c>
     </row>
     <row r="84" ht="21" customHeight="1">
@@ -4774,13 +4774,13 @@
         <v>15</v>
       </c>
       <c r="D84" s="2" t="n">
-        <v>2.021658189350957</v>
+        <v>1.113343107470173</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>23.86285801591021</v>
+        <v>23.15454293402942</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>-88.6993968598134</v>
+        <v>-87.99108177793262</v>
       </c>
     </row>
     <row r="85" ht="21" customHeight="1">
@@ -4796,13 +4796,13 @@
         <v>20</v>
       </c>
       <c r="D85" s="2" t="n">
-        <v>2.021658189350957</v>
+        <v>1.113343107470173</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>23.86285801591021</v>
+        <v>23.15454293402942</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>-91.53383596282154</v>
+        <v>-90.82552088094076</v>
       </c>
     </row>
     <row r="86" ht="21" customHeight="1">
@@ -4818,13 +4818,13 @@
         <v>5</v>
       </c>
       <c r="D86" s="2" t="n">
-        <v>3.712108294951515</v>
+        <v>2.796294523327493</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>25.55330812151077</v>
+        <v>24.83749434988674</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>-81.89821170968105</v>
+        <v>-81.18239793805702</v>
       </c>
     </row>
     <row r="87" ht="21" customHeight="1">
@@ -4840,13 +4840,13 @@
         <v>10</v>
       </c>
       <c r="D87" s="2" t="n">
-        <v>3.712108294951515</v>
+        <v>2.796294523327493</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>25.55330812151077</v>
+        <v>24.83749434988674</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>-86.55377982986123</v>
+        <v>-85.8379660582372</v>
       </c>
     </row>
     <row r="88" ht="21" customHeight="1">
@@ -4862,13 +4862,13 @@
         <v>15</v>
       </c>
       <c r="D88" s="2" t="n">
-        <v>3.712108294951515</v>
+        <v>2.796294523327493</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>25.55330812151077</v>
+        <v>24.83749434988674</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>-90.20613006470354</v>
+        <v>-89.49031629307952</v>
       </c>
     </row>
     <row r="89" ht="21" customHeight="1">
@@ -4884,13 +4884,13 @@
         <v>20</v>
       </c>
       <c r="D89" s="2" t="n">
-        <v>3.712108294951515</v>
+        <v>2.796294523327493</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>25.55330812151077</v>
+        <v>24.83749434988674</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>-93.04056916771167</v>
+        <v>-92.32475539608764</v>
       </c>
     </row>
     <row r="90" ht="21" customHeight="1">
@@ -4906,13 +4906,13 @@
         <v>5</v>
       </c>
       <c r="D90" s="2" t="n">
-        <v>4.039856820033607</v>
+        <v>3.043184250914949</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>25.88105664659286</v>
+        <v>25.0843840774742</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>-82.3155086612924</v>
+        <v>-81.51883609217374</v>
       </c>
     </row>
     <row r="91" ht="21" customHeight="1">
@@ -4928,13 +4928,13 @@
         <v>10</v>
       </c>
       <c r="D91" s="2" t="n">
-        <v>4.039856820033607</v>
+        <v>3.043184250914949</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>25.88105664659286</v>
+        <v>25.0843840774742</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>-86.97107678147258</v>
+        <v>-86.17440421235392</v>
       </c>
     </row>
     <row r="92" ht="21" customHeight="1">
@@ -4950,13 +4950,13 @@
         <v>15</v>
       </c>
       <c r="D92" s="2" t="n">
-        <v>4.039856820033607</v>
+        <v>3.043184250914949</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>25.88105664659286</v>
+        <v>25.0843840774742</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>-90.62342701631489</v>
+        <v>-89.82675444719624</v>
       </c>
     </row>
     <row r="93" ht="21" customHeight="1">
@@ -4972,13 +4972,13 @@
         <v>20</v>
       </c>
       <c r="D93" s="2" t="n">
-        <v>4.039856820033607</v>
+        <v>3.043184250914949</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>25.88105664659286</v>
+        <v>25.0843840774742</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>-93.45786611932301</v>
+        <v>-92.66119355020436</v>
       </c>
     </row>
     <row r="94" ht="21" customHeight="1">
@@ -4994,13 +4994,13 @@
         <v>5</v>
       </c>
       <c r="D94" s="2" t="n">
-        <v>4.552854511466446</v>
+        <v>3.429620346269228</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>26.3940543380257</v>
+        <v>25.47082017282848</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>-82.9226748269064</v>
+        <v>-81.99944066170919</v>
       </c>
     </row>
     <row r="95" ht="21" customHeight="1">
@@ -5016,13 +5016,13 @@
         <v>10</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>4.552854511466446</v>
+        <v>3.429620346269228</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>26.3940543380257</v>
+        <v>25.47082017282848</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>-87.57824294708658</v>
+        <v>-86.65500878188936</v>
       </c>
     </row>
     <row r="96" ht="21" customHeight="1">
@@ -5038,13 +5038,13 @@
         <v>15</v>
       </c>
       <c r="D96" s="2" t="n">
-        <v>4.552854511466446</v>
+        <v>3.429620346269228</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>26.3940543380257</v>
+        <v>25.47082017282848</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>-91.2305931819289</v>
+        <v>-90.30735901673168</v>
       </c>
     </row>
     <row r="97" ht="21" customHeight="1">
@@ -5060,13 +5060,13 @@
         <v>20</v>
       </c>
       <c r="D97" s="2" t="n">
-        <v>4.552854511466446</v>
+        <v>3.429620346269228</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>26.3940543380257</v>
+        <v>25.47082017282848</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>-94.06503228493703</v>
+        <v>-93.14179811973982</v>
       </c>
     </row>
     <row r="98" ht="21" customHeight="1">
@@ -5082,13 +5082,13 @@
         <v>5</v>
       </c>
       <c r="D98" s="2" t="n">
-        <v>2.220112545490299</v>
+        <v>3.632545968827942</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>17.54071245876992</v>
+        <v>25.47374579538719</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>-73.88561604694021</v>
+        <v>-81.81864938355747</v>
       </c>
     </row>
     <row r="99" ht="21" customHeight="1">
@@ -5104,13 +5104,13 @@
         <v>10</v>
       </c>
       <c r="D99" s="2" t="n">
-        <v>2.220112545490299</v>
+        <v>3.632545968827942</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>17.54071245876992</v>
+        <v>25.47374579538719</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>-78.54118416712038</v>
+        <v>-86.47421750373765</v>
       </c>
     </row>
     <row r="100" ht="21" customHeight="1">
@@ -5126,13 +5126,13 @@
         <v>15</v>
       </c>
       <c r="D100" s="2" t="n">
-        <v>2.220112545490299</v>
+        <v>3.632545968827942</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>17.54071245876992</v>
+        <v>25.47374579538719</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>-82.19353440196269</v>
+        <v>-90.12656773857996</v>
       </c>
     </row>
     <row r="101" ht="21" customHeight="1">
@@ -5148,13 +5148,13 @@
         <v>20</v>
       </c>
       <c r="D101" s="2" t="n">
-        <v>2.220112545490299</v>
+        <v>3.632545968827942</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>17.54071245876992</v>
+        <v>25.47374579538719</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>-85.02797350497082</v>
+        <v>-92.96100684158809</v>
       </c>
     </row>
     <row r="102" ht="21" customHeight="1">
@@ -5170,13 +5170,13 @@
         <v>5</v>
       </c>
       <c r="D102" s="2" t="n">
-        <v>2.416413490255539</v>
+        <v>3.953269797169757</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>17.73701340353517</v>
+        <v>25.79446962372901</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>-74.1714654182347</v>
+        <v>-82.22892163842855</v>
       </c>
     </row>
     <row r="103" ht="21" customHeight="1">
@@ -5192,13 +5192,13 @@
         <v>10</v>
       </c>
       <c r="D103" s="2" t="n">
-        <v>2.416413490255539</v>
+        <v>3.953269797169757</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>17.73701340353517</v>
+        <v>25.79446962372901</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>-78.8270335384149</v>
+        <v>-86.88448975860874</v>
       </c>
     </row>
     <row r="104" ht="21" customHeight="1">
@@ -5214,13 +5214,13 @@
         <v>15</v>
       </c>
       <c r="D104" s="2" t="n">
-        <v>2.416413490255539</v>
+        <v>3.953269797169757</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>17.73701340353517</v>
+        <v>25.79446962372901</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>-82.47938377325721</v>
+        <v>-90.53683999345105</v>
       </c>
     </row>
     <row r="105" ht="21" customHeight="1">
@@ -5236,13 +5236,13 @@
         <v>20</v>
       </c>
       <c r="D105" s="2" t="n">
-        <v>2.416413490255539</v>
+        <v>3.953269797169757</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>17.73701340353517</v>
+        <v>25.79446962372901</v>
       </c>
       <c r="F105" s="2" t="n">
-        <v>-85.31382287626533</v>
+        <v>-93.37127909645918</v>
       </c>
     </row>
     <row r="106" ht="21" customHeight="1">
@@ -5258,13 +5258,13 @@
         <v>5</v>
       </c>
       <c r="D106" s="2" t="n">
-        <v>2.723294105061596</v>
+        <v>4.455272311096074</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>18.04389401834122</v>
+        <v>26.29647213765532</v>
       </c>
       <c r="F106" s="2" t="n">
-        <v>-74.57251450722192</v>
+        <v>-82.82509262653603</v>
       </c>
     </row>
     <row r="107" ht="21" customHeight="1">
@@ -5280,13 +5280,13 @@
         <v>10</v>
       </c>
       <c r="D107" s="2" t="n">
-        <v>2.723294105061596</v>
+        <v>4.455272311096074</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>18.04389401834122</v>
+        <v>26.29647213765532</v>
       </c>
       <c r="F107" s="2" t="n">
-        <v>-79.2280826274021</v>
+        <v>-87.48066074671621</v>
       </c>
     </row>
     <row r="108" ht="21" customHeight="1">
@@ -5302,13 +5302,13 @@
         <v>15</v>
       </c>
       <c r="D108" s="2" t="n">
-        <v>2.723294105061596</v>
+        <v>4.455272311096074</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>18.04389401834122</v>
+        <v>26.29647213765532</v>
       </c>
       <c r="F108" s="2" t="n">
-        <v>-82.88043286224442</v>
+        <v>-91.13301098155853</v>
       </c>
     </row>
     <row r="109" ht="21" customHeight="1">
@@ -5324,13 +5324,13 @@
         <v>20</v>
       </c>
       <c r="D109" s="2" t="n">
-        <v>2.723294105061596</v>
+        <v>4.455272311096074</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>18.04389401834122</v>
+        <v>26.29647213765532</v>
       </c>
       <c r="F109" s="2" t="n">
-        <v>-85.71487196525256</v>
+        <v>-93.96745008456666</v>
       </c>
     </row>
     <row r="110" ht="21" customHeight="1">
@@ -5346,13 +5346,13 @@
         <v>5</v>
       </c>
       <c r="D110" s="2" t="n">
-        <v>5.474088368743129</v>
+        <v>1.1946747848</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>27.31528819530238</v>
+        <v>20.02557465471944</v>
       </c>
       <c r="F110" s="2" t="n">
-        <v>-83.66019178347267</v>
+        <v>-76.37047824288972</v>
       </c>
     </row>
     <row r="111" ht="21" customHeight="1">
@@ -5368,13 +5368,13 @@
         <v>10</v>
       </c>
       <c r="D111" s="2" t="n">
-        <v>5.474088368743129</v>
+        <v>1.1946747848</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>27.31528819530238</v>
+        <v>20.02557465471944</v>
       </c>
       <c r="F111" s="2" t="n">
-        <v>-88.31575990365283</v>
+        <v>-81.0260463630699</v>
       </c>
     </row>
     <row r="112" ht="21" customHeight="1">
@@ -5390,13 +5390,13 @@
         <v>15</v>
       </c>
       <c r="D112" s="2" t="n">
-        <v>5.474088368743129</v>
+        <v>1.1946747848</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>27.31528819530238</v>
+        <v>20.02557465471944</v>
       </c>
       <c r="F112" s="2" t="n">
-        <v>-91.96811013849515</v>
+        <v>-84.67839659791221</v>
       </c>
     </row>
     <row r="113" ht="21" customHeight="1">
@@ -5412,13 +5412,13 @@
         <v>20</v>
       </c>
       <c r="D113" s="2" t="n">
-        <v>5.474088368743129</v>
+        <v>1.1946747848</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>27.31528819530238</v>
+        <v>20.02557465471944</v>
       </c>
       <c r="F113" s="2" t="n">
-        <v>-94.80254924150327</v>
+        <v>-87.51283570092033</v>
       </c>
     </row>
     <row r="114" ht="21" customHeight="1">
@@ -5434,13 +5434,13 @@
         <v>5</v>
       </c>
       <c r="D114" s="2" t="n">
-        <v>5.957405192087053</v>
+        <v>1.3005610072</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>27.7986050186463</v>
+        <v>20.13146087711944</v>
       </c>
       <c r="F114" s="2" t="n">
-        <v>-84.23305703334584</v>
+        <v>-76.56591289181898</v>
       </c>
     </row>
     <row r="115" ht="21" customHeight="1">
@@ -5456,13 +5456,13 @@
         <v>10</v>
       </c>
       <c r="D115" s="2" t="n">
-        <v>5.957405192087053</v>
+        <v>1.3005610072</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>27.7986050186463</v>
+        <v>20.13146087711944</v>
       </c>
       <c r="F115" s="2" t="n">
-        <v>-88.88862515352602</v>
+        <v>-81.22148101199916</v>
       </c>
     </row>
     <row r="116" ht="21" customHeight="1">
@@ -5478,13 +5478,13 @@
         <v>15</v>
       </c>
       <c r="D116" s="2" t="n">
-        <v>5.957405192087053</v>
+        <v>1.3005610072</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>27.7986050186463</v>
+        <v>20.13146087711944</v>
       </c>
       <c r="F116" s="2" t="n">
-        <v>-92.54097538836834</v>
+        <v>-84.87383124684148</v>
       </c>
     </row>
     <row r="117" ht="21" customHeight="1">
@@ -5500,13 +5500,13 @@
         <v>20</v>
       </c>
       <c r="D117" s="2" t="n">
-        <v>5.957405192087053</v>
+        <v>1.3005610072</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>27.7986050186463</v>
+        <v>20.13146087711944</v>
       </c>
       <c r="F117" s="2" t="n">
-        <v>-95.37541449137646</v>
+        <v>-87.7082703498496</v>
       </c>
     </row>
     <row r="118" ht="21" customHeight="1">
@@ -5522,13 +5522,13 @@
         <v>5</v>
       </c>
       <c r="D118" s="2" t="n">
-        <v>6.71390108949493</v>
+        <v>1.465761023466667</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>28.55510091605418</v>
+        <v>20.2966608933861</v>
       </c>
       <c r="F118" s="2" t="n">
-        <v>-85.08372140493489</v>
+        <v>-76.82528138226681</v>
       </c>
     </row>
     <row r="119" ht="21" customHeight="1">
@@ -5544,13 +5544,13 @@
         <v>10</v>
       </c>
       <c r="D119" s="2" t="n">
-        <v>6.71390108949493</v>
+        <v>1.465761023466667</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>28.55510091605418</v>
+        <v>20.2966608933861</v>
       </c>
       <c r="F119" s="2" t="n">
-        <v>-89.73928952511505</v>
+        <v>-81.48084950244699</v>
       </c>
     </row>
     <row r="120" ht="21" customHeight="1">
@@ -5566,13 +5566,13 @@
         <v>15</v>
       </c>
       <c r="D120" s="2" t="n">
-        <v>6.71390108949493</v>
+        <v>1.465761023466667</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>28.55510091605418</v>
+        <v>20.2966608933861</v>
       </c>
       <c r="F120" s="2" t="n">
-        <v>-93.39163975995737</v>
+        <v>-85.1331997372893</v>
       </c>
     </row>
     <row r="121" ht="21" customHeight="1">
@@ -5588,13 +5588,13 @@
         <v>20</v>
       </c>
       <c r="D121" s="2" t="n">
-        <v>6.71390108949493</v>
+        <v>1.465761023466667</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>28.55510091605418</v>
+        <v>20.2966608933861</v>
       </c>
       <c r="F121" s="2" t="n">
-        <v>-96.22607886296552</v>
+        <v>-87.96763884029744</v>
       </c>
     </row>
     <row r="122" ht="21" customHeight="1">
@@ -5610,13 +5610,13 @@
         <v>5</v>
       </c>
       <c r="D122" s="2" t="n">
-        <v>3.355085389701381</v>
+        <v>2.654822459447393</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>22.38598525962082</v>
+        <v>21.48572232936683</v>
       </c>
       <c r="F122" s="2" t="n">
-        <v>-78.73088884779111</v>
+        <v>-77.83062591753711</v>
       </c>
     </row>
     <row r="123" ht="21" customHeight="1">
@@ -5632,13 +5632,13 @@
         <v>10</v>
       </c>
       <c r="D123" s="2" t="n">
-        <v>3.355085389701381</v>
+        <v>2.654822459447393</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>22.38598525962082</v>
+        <v>21.48572232936683</v>
       </c>
       <c r="F123" s="2" t="n">
-        <v>-83.38645696797127</v>
+        <v>-82.4861940377173</v>
       </c>
     </row>
     <row r="124" ht="21" customHeight="1">
@@ -5654,13 +5654,13 @@
         <v>15</v>
       </c>
       <c r="D124" s="2" t="n">
-        <v>3.355085389701381</v>
+        <v>2.654822459447393</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>22.38598525962082</v>
+        <v>21.48572232936683</v>
       </c>
       <c r="F124" s="2" t="n">
-        <v>-87.03880720281359</v>
+        <v>-86.13854427255961</v>
       </c>
     </row>
     <row r="125" ht="21" customHeight="1">
@@ -5676,13 +5676,13 @@
         <v>20</v>
       </c>
       <c r="D125" s="2" t="n">
-        <v>3.355085389701381</v>
+        <v>2.654822459447393</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>22.38598525962082</v>
+        <v>21.48572232936683</v>
       </c>
       <c r="F125" s="2" t="n">
-        <v>-89.87324630582171</v>
+        <v>-88.97298337556774</v>
       </c>
     </row>
     <row r="126" ht="21" customHeight="1">
@@ -5698,13 +5698,13 @@
         <v>5</v>
       </c>
       <c r="D126" s="2" t="n">
-        <v>3.652622762592486</v>
+        <v>2.889221371413957</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>22.68352263251192</v>
+        <v>21.72012124133339</v>
       </c>
       <c r="F126" s="2" t="n">
-        <v>-79.11797464721147</v>
+        <v>-78.15457325603293</v>
       </c>
     </row>
     <row r="127" ht="21" customHeight="1">
@@ -5720,13 +5720,13 @@
         <v>10</v>
       </c>
       <c r="D127" s="2" t="n">
-        <v>3.652622762592486</v>
+        <v>2.889221371413957</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>22.68352263251192</v>
+        <v>21.72012124133339</v>
       </c>
       <c r="F127" s="2" t="n">
-        <v>-83.77354276739165</v>
+        <v>-82.81014137621312</v>
       </c>
     </row>
     <row r="128" ht="21" customHeight="1">
@@ -5742,13 +5742,13 @@
         <v>15</v>
       </c>
       <c r="D128" s="2" t="n">
-        <v>3.652622762592486</v>
+        <v>2.889221371413957</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>22.68352263251192</v>
+        <v>21.72012124133339</v>
       </c>
       <c r="F128" s="2" t="n">
-        <v>-87.42589300223396</v>
+        <v>-86.46249161105544</v>
       </c>
     </row>
     <row r="129" ht="21" customHeight="1">
@@ -5764,13 +5764,13 @@
         <v>20</v>
       </c>
       <c r="D129" s="2" t="n">
-        <v>3.652622762592486</v>
+        <v>2.889221371413957</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>22.68352263251192</v>
+        <v>21.72012124133339</v>
       </c>
       <c r="F129" s="2" t="n">
-        <v>-90.26033210524209</v>
+        <v>-89.29693071406356</v>
       </c>
     </row>
     <row r="130" ht="21" customHeight="1">
@@ -5786,13 +5786,13 @@
         <v>5</v>
       </c>
       <c r="D130" s="2" t="n">
-        <v>4.116607315860533</v>
+        <v>3.256106624926841</v>
       </c>
       <c r="E130" s="2" t="n">
-        <v>23.14750718577997</v>
+        <v>22.08700649484628</v>
       </c>
       <c r="F130" s="2" t="n">
-        <v>-79.67612767466068</v>
+        <v>-78.61562698372698</v>
       </c>
     </row>
     <row r="131" ht="21" customHeight="1">
@@ -5808,13 +5808,13 @@
         <v>10</v>
       </c>
       <c r="D131" s="2" t="n">
-        <v>4.116607315860533</v>
+        <v>3.256106624926841</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>23.14750718577997</v>
+        <v>22.08700649484628</v>
       </c>
       <c r="F131" s="2" t="n">
-        <v>-84.33169579484085</v>
+        <v>-83.27119510390716</v>
       </c>
     </row>
     <row r="132" ht="21" customHeight="1">
@@ -5830,13 +5830,13 @@
         <v>15</v>
       </c>
       <c r="D132" s="2" t="n">
-        <v>4.116607315860533</v>
+        <v>3.256106624926841</v>
       </c>
       <c r="E132" s="2" t="n">
-        <v>23.14750718577997</v>
+        <v>22.08700649484628</v>
       </c>
       <c r="F132" s="2" t="n">
-        <v>-87.98404602968317</v>
+        <v>-86.92354533874948</v>
       </c>
     </row>
     <row r="133" ht="21" customHeight="1">
@@ -5852,13 +5852,13 @@
         <v>20</v>
       </c>
       <c r="D133" s="2" t="n">
-        <v>4.116607315860533</v>
+        <v>3.256106624926841</v>
       </c>
       <c r="E133" s="2" t="n">
-        <v>23.14750718577997</v>
+        <v>22.08700649484628</v>
       </c>
       <c r="F133" s="2" t="n">
-        <v>-90.81848513269131</v>
+        <v>-89.75798444175761</v>
       </c>
     </row>
     <row r="134" ht="21" customHeight="1">
@@ -5874,13 +5874,13 @@
         <v>5</v>
       </c>
       <c r="D134" s="2" t="n">
-        <v>4.067719584178708</v>
+        <v>2.107773852178709</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>19.38831949745833</v>
+        <v>17.42837376545834</v>
       </c>
       <c r="F134" s="2" t="n">
-        <v>-75.73322308562862</v>
+        <v>-73.77327735362861</v>
       </c>
     </row>
     <row r="135" ht="21" customHeight="1">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="D135" s="2" t="n">
-        <v>4.067719584178708</v>
+        <v>2.107773852178709</v>
       </c>
       <c r="E135" s="2" t="n">
-        <v>19.38831949745833</v>
+        <v>17.42837376545834</v>
       </c>
       <c r="F135" s="2" t="n">
-        <v>-80.38879120580879</v>
+        <v>-78.42884547380879</v>
       </c>
     </row>
     <row r="136" ht="21" customHeight="1">
@@ -5918,13 +5918,13 @@
         <v>15</v>
       </c>
       <c r="D136" s="2" t="n">
-        <v>4.067719584178708</v>
+        <v>2.107773852178709</v>
       </c>
       <c r="E136" s="2" t="n">
-        <v>19.38831949745833</v>
+        <v>17.42837376545834</v>
       </c>
       <c r="F136" s="2" t="n">
-        <v>-84.0411414406511</v>
+        <v>-82.08119570865111</v>
       </c>
     </row>
     <row r="137" ht="21" customHeight="1">
@@ -5940,13 +5940,13 @@
         <v>20</v>
       </c>
       <c r="D137" s="2" t="n">
-        <v>4.067719584178708</v>
+        <v>2.107773852178709</v>
       </c>
       <c r="E137" s="2" t="n">
-        <v>19.38831949745833</v>
+        <v>17.42837376545834</v>
       </c>
       <c r="F137" s="2" t="n">
-        <v>-86.87558054365923</v>
+        <v>-84.91563481165923</v>
       </c>
     </row>
     <row r="138" ht="21" customHeight="1">
@@ -5962,13 +5962,13 @@
         <v>5</v>
       </c>
       <c r="D138" s="2" t="n">
-        <v>4.426865651111954</v>
+        <v>2.293872887111954</v>
       </c>
       <c r="E138" s="2" t="n">
-        <v>19.74746556439158</v>
+        <v>17.61447280039158</v>
       </c>
       <c r="F138" s="2" t="n">
-        <v>-76.18191757909112</v>
+        <v>-74.04892481509113</v>
       </c>
     </row>
     <row r="139" ht="21" customHeight="1">
@@ -5984,13 +5984,13 @@
         <v>10</v>
       </c>
       <c r="D139" s="2" t="n">
-        <v>4.426865651111954</v>
+        <v>2.293872887111954</v>
       </c>
       <c r="E139" s="2" t="n">
-        <v>19.74746556439158</v>
+        <v>17.61447280039158</v>
       </c>
       <c r="F139" s="2" t="n">
-        <v>-80.8374856992713</v>
+        <v>-78.7044929352713</v>
       </c>
     </row>
     <row r="140" ht="21" customHeight="1">
@@ -6006,13 +6006,13 @@
         <v>15</v>
       </c>
       <c r="D140" s="2" t="n">
-        <v>4.426865651111954</v>
+        <v>2.293872887111954</v>
       </c>
       <c r="E140" s="2" t="n">
-        <v>19.74746556439158</v>
+        <v>17.61447280039158</v>
       </c>
       <c r="F140" s="2" t="n">
-        <v>-84.48983593411361</v>
+        <v>-82.35684317011362</v>
       </c>
     </row>
     <row r="141" ht="21" customHeight="1">
@@ -6028,13 +6028,13 @@
         <v>20</v>
       </c>
       <c r="D141" s="2" t="n">
-        <v>4.426865651111954</v>
+        <v>2.293872887111954</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>19.74746556439158</v>
+        <v>17.61447280039158</v>
       </c>
       <c r="F141" s="2" t="n">
-        <v>-87.32427503712174</v>
+        <v>-85.19128227312174</v>
       </c>
     </row>
     <row r="142" ht="21" customHeight="1">
@@ -6050,13 +6050,13 @@
         <v>5</v>
       </c>
       <c r="D142" s="2" t="n">
-        <v>4.989007321094423</v>
+        <v>2.585158333094425</v>
       </c>
       <c r="E142" s="2" t="n">
-        <v>20.30960723437405</v>
+        <v>17.90575824637405</v>
       </c>
       <c r="F142" s="2" t="n">
-        <v>-76.83822772325476</v>
+        <v>-74.43437873525475</v>
       </c>
     </row>
     <row r="143" ht="21" customHeight="1">
@@ -6072,13 +6072,13 @@
         <v>10</v>
       </c>
       <c r="D143" s="2" t="n">
-        <v>4.989007321094423</v>
+        <v>2.585158333094425</v>
       </c>
       <c r="E143" s="2" t="n">
-        <v>20.30960723437405</v>
+        <v>17.90575824637405</v>
       </c>
       <c r="F143" s="2" t="n">
-        <v>-81.49379584343492</v>
+        <v>-79.08994685543493</v>
       </c>
     </row>
     <row r="144" ht="21" customHeight="1">
@@ -6094,13 +6094,13 @@
         <v>15</v>
       </c>
       <c r="D144" s="2" t="n">
-        <v>4.989007321094423</v>
+        <v>2.585158333094425</v>
       </c>
       <c r="E144" s="2" t="n">
-        <v>20.30960723437405</v>
+        <v>17.90575824637405</v>
       </c>
       <c r="F144" s="2" t="n">
-        <v>-85.14614607827724</v>
+        <v>-82.74229709027725</v>
       </c>
     </row>
     <row r="145" ht="21" customHeight="1">
@@ -6116,13 +6116,13 @@
         <v>20</v>
       </c>
       <c r="D145" s="2" t="n">
-        <v>4.989007321094423</v>
+        <v>2.585158333094425</v>
       </c>
       <c r="E145" s="2" t="n">
-        <v>20.30960723437405</v>
+        <v>17.90575824637405</v>
       </c>
       <c r="F145" s="2" t="n">
-        <v>-87.98058518128539</v>
+        <v>-85.57673619328538</v>
       </c>
     </row>
     <row r="146" ht="21" customHeight="1">
@@ -6138,13 +6138,13 @@
         <v>5</v>
       </c>
       <c r="D146" s="2" t="n">
-        <v>4.547603127878165</v>
+        <v>2.587657395878165</v>
       </c>
       <c r="E146" s="2" t="n">
-        <v>26.38880295443742</v>
+        <v>24.42885722243741</v>
       </c>
       <c r="F146" s="2" t="n">
-        <v>-82.73370654260771</v>
+        <v>-80.7737608106077</v>
       </c>
     </row>
     <row r="147" ht="21" customHeight="1">
@@ -6160,13 +6160,13 @@
         <v>10</v>
       </c>
       <c r="D147" s="2" t="n">
-        <v>4.547603127878165</v>
+        <v>2.587657395878165</v>
       </c>
       <c r="E147" s="2" t="n">
-        <v>26.38880295443742</v>
+        <v>24.42885722243741</v>
       </c>
       <c r="F147" s="2" t="n">
-        <v>-87.38927466278787</v>
+        <v>-85.42932893078788</v>
       </c>
     </row>
     <row r="148" ht="21" customHeight="1">
@@ -6182,13 +6182,13 @@
         <v>15</v>
       </c>
       <c r="D148" s="2" t="n">
-        <v>4.547603127878165</v>
+        <v>2.587657395878165</v>
       </c>
       <c r="E148" s="2" t="n">
-        <v>26.38880295443742</v>
+        <v>24.42885722243741</v>
       </c>
       <c r="F148" s="2" t="n">
-        <v>-91.04162489763019</v>
+        <v>-89.08167916563019</v>
       </c>
     </row>
     <row r="149" ht="21" customHeight="1">
@@ -6204,13 +6204,13 @@
         <v>20</v>
       </c>
       <c r="D149" s="2" t="n">
-        <v>4.547603127878165</v>
+        <v>2.587657395878165</v>
       </c>
       <c r="E149" s="2" t="n">
-        <v>26.38880295443742</v>
+        <v>24.42885722243741</v>
       </c>
       <c r="F149" s="2" t="n">
-        <v>-93.87606400063831</v>
+        <v>-91.91611826863831</v>
       </c>
     </row>
     <row r="150" ht="21" customHeight="1">
@@ -6226,13 +6226,13 @@
         <v>5</v>
       </c>
       <c r="D150" s="2" t="n">
-        <v>4.949937592183638</v>
+        <v>2.816944828183639</v>
       </c>
       <c r="E150" s="2" t="n">
-        <v>26.79113741874289</v>
+        <v>24.65814465474289</v>
       </c>
       <c r="F150" s="2" t="n">
-        <v>-83.22558943344244</v>
+        <v>-81.09259666944243</v>
       </c>
     </row>
     <row r="151" ht="21" customHeight="1">
@@ -6248,13 +6248,13 @@
         <v>10</v>
       </c>
       <c r="D151" s="2" t="n">
-        <v>4.949937592183638</v>
+        <v>2.816944828183639</v>
       </c>
       <c r="E151" s="2" t="n">
-        <v>26.79113741874289</v>
+        <v>24.65814465474289</v>
       </c>
       <c r="F151" s="2" t="n">
-        <v>-87.88115755362261</v>
+        <v>-85.74816478962262</v>
       </c>
     </row>
     <row r="152" ht="21" customHeight="1">
@@ -6270,13 +6270,13 @@
         <v>15</v>
       </c>
       <c r="D152" s="2" t="n">
-        <v>4.949937592183638</v>
+        <v>2.816944828183639</v>
       </c>
       <c r="E152" s="2" t="n">
-        <v>26.79113741874289</v>
+        <v>24.65814465474289</v>
       </c>
       <c r="F152" s="2" t="n">
-        <v>-91.53350778846493</v>
+        <v>-89.40051502446494</v>
       </c>
     </row>
     <row r="153" ht="21" customHeight="1">
@@ -6292,13 +6292,13 @@
         <v>20</v>
       </c>
       <c r="D153" s="2" t="n">
-        <v>4.949937592183638</v>
+        <v>2.816944828183639</v>
       </c>
       <c r="E153" s="2" t="n">
-        <v>26.79113741874289</v>
+        <v>24.65814465474289</v>
       </c>
       <c r="F153" s="2" t="n">
-        <v>-94.36794689147305</v>
+        <v>-92.23495412747306</v>
       </c>
     </row>
     <row r="154" ht="21" customHeight="1">
@@ -6314,13 +6314,13 @@
         <v>5</v>
       </c>
       <c r="D154" s="2" t="n">
-        <v>5.578600655248216</v>
+        <v>3.174751667248217</v>
       </c>
       <c r="E154" s="2" t="n">
-        <v>27.41980048180747</v>
+        <v>25.01595149380747</v>
       </c>
       <c r="F154" s="2" t="n">
-        <v>-83.94842097068818</v>
+        <v>-81.54457198268817</v>
       </c>
     </row>
     <row r="155" ht="21" customHeight="1">
@@ -6336,13 +6336,13 @@
         <v>10</v>
       </c>
       <c r="D155" s="2" t="n">
-        <v>5.578600655248216</v>
+        <v>3.174751667248217</v>
       </c>
       <c r="E155" s="2" t="n">
-        <v>27.41980048180747</v>
+        <v>25.01595149380747</v>
       </c>
       <c r="F155" s="2" t="n">
-        <v>-88.60398909086835</v>
+        <v>-86.20014010286835</v>
       </c>
     </row>
     <row r="156" ht="21" customHeight="1">
@@ -6358,13 +6358,13 @@
         <v>15</v>
       </c>
       <c r="D156" s="2" t="n">
-        <v>5.578600655248216</v>
+        <v>3.174751667248217</v>
       </c>
       <c r="E156" s="2" t="n">
-        <v>27.41980048180747</v>
+        <v>25.01595149380747</v>
       </c>
       <c r="F156" s="2" t="n">
-        <v>-92.25633932571067</v>
+        <v>-89.85249033771066</v>
       </c>
     </row>
     <row r="157" ht="21" customHeight="1">
@@ -6380,13 +6380,13 @@
         <v>20</v>
       </c>
       <c r="D157" s="2" t="n">
-        <v>5.578600655248216</v>
+        <v>3.174751667248217</v>
       </c>
       <c r="E157" s="2" t="n">
-        <v>27.41980048180747</v>
+        <v>25.01595149380747</v>
       </c>
       <c r="F157" s="2" t="n">
-        <v>-95.09077842871881</v>
+        <v>-92.6869294407188</v>
       </c>
     </row>
     <row r="158" ht="21" customHeight="1">
@@ -6402,13 +6402,13 @@
         <v>5</v>
       </c>
       <c r="D158" s="2" t="n">
-        <v>4.180902288058597</v>
+        <v>2.220956556058597</v>
       </c>
       <c r="E158" s="2" t="n">
-        <v>23.21180215797803</v>
+        <v>17.54155646933822</v>
       </c>
       <c r="F158" s="2" t="n">
-        <v>-79.55670574614831</v>
+        <v>-73.8864600575085</v>
       </c>
     </row>
     <row r="159" ht="21" customHeight="1">
@@ -6424,13 +6424,13 @@
         <v>10</v>
       </c>
       <c r="D159" s="2" t="n">
-        <v>4.180902288058597</v>
+        <v>2.220956556058597</v>
       </c>
       <c r="E159" s="2" t="n">
-        <v>23.21180215797803</v>
+        <v>17.54155646933822</v>
       </c>
       <c r="F159" s="2" t="n">
-        <v>-84.2122738663285</v>
+        <v>-78.54202817768868</v>
       </c>
     </row>
     <row r="160" ht="21" customHeight="1">
@@ -6446,13 +6446,13 @@
         <v>15</v>
       </c>
       <c r="D160" s="2" t="n">
-        <v>4.180902288058597</v>
+        <v>2.220956556058597</v>
       </c>
       <c r="E160" s="2" t="n">
-        <v>23.21180215797803</v>
+        <v>17.54155646933822</v>
       </c>
       <c r="F160" s="2" t="n">
-        <v>-87.86462410117082</v>
+        <v>-82.19437841253099</v>
       </c>
     </row>
     <row r="161" ht="21" customHeight="1">
@@ -6468,13 +6468,13 @@
         <v>20</v>
       </c>
       <c r="D161" s="2" t="n">
-        <v>4.180902288058597</v>
+        <v>2.220956556058597</v>
       </c>
       <c r="E161" s="2" t="n">
-        <v>23.21180215797803</v>
+        <v>17.54155646933822</v>
       </c>
       <c r="F161" s="2" t="n">
-        <v>-90.69906320417894</v>
+        <v>-85.02881751553912</v>
       </c>
     </row>
     <row r="162" ht="21" customHeight="1">
@@ -6490,13 +6490,13 @@
         <v>5</v>
       </c>
       <c r="D162" s="2" t="n">
-        <v>4.550041453606957</v>
+        <v>2.417048689606957</v>
       </c>
       <c r="E162" s="2" t="n">
-        <v>23.5809413235264</v>
+        <v>17.73764860288658</v>
       </c>
       <c r="F162" s="2" t="n">
-        <v>-80.01539333822595</v>
+        <v>-74.17210061758612</v>
       </c>
     </row>
     <row r="163" ht="21" customHeight="1">
@@ -6512,13 +6512,13 @@
         <v>10</v>
       </c>
       <c r="D163" s="2" t="n">
-        <v>4.550041453606957</v>
+        <v>2.417048689606957</v>
       </c>
       <c r="E163" s="2" t="n">
-        <v>23.5809413235264</v>
+        <v>17.73764860288658</v>
       </c>
       <c r="F163" s="2" t="n">
-        <v>-84.67096145840611</v>
+        <v>-78.8276687377663</v>
       </c>
     </row>
     <row r="164" ht="21" customHeight="1">
@@ -6534,13 +6534,13 @@
         <v>15</v>
       </c>
       <c r="D164" s="2" t="n">
-        <v>4.550041453606957</v>
+        <v>2.417048689606957</v>
       </c>
       <c r="E164" s="2" t="n">
-        <v>23.5809413235264</v>
+        <v>17.73764860288658</v>
       </c>
       <c r="F164" s="2" t="n">
-        <v>-88.32331169324843</v>
+        <v>-82.48001897260862</v>
       </c>
     </row>
     <row r="165" ht="21" customHeight="1">
@@ -6556,13 +6556,13 @@
         <v>20</v>
       </c>
       <c r="D165" s="2" t="n">
-        <v>4.550041453606957</v>
+        <v>2.417048689606957</v>
       </c>
       <c r="E165" s="2" t="n">
-        <v>23.5809413235264</v>
+        <v>17.73764860288658</v>
       </c>
       <c r="F165" s="2" t="n">
-        <v>-91.15775079625655</v>
+        <v>-85.31445807561674</v>
       </c>
     </row>
     <row r="166" ht="21" customHeight="1">
@@ -6578,13 +6578,13 @@
         <v>5</v>
       </c>
       <c r="D166" s="2" t="n">
-        <v>5.127824495334824</v>
+        <v>2.723975507334824</v>
       </c>
       <c r="E166" s="2" t="n">
-        <v>24.15872436525426</v>
+        <v>18.04457542061445</v>
       </c>
       <c r="F166" s="2" t="n">
-        <v>-80.68734485413496</v>
+        <v>-74.57319590949515</v>
       </c>
     </row>
     <row r="167" ht="21" customHeight="1">
@@ -6600,13 +6600,13 @@
         <v>10</v>
       </c>
       <c r="D167" s="2" t="n">
-        <v>5.127824495334824</v>
+        <v>2.723975507334824</v>
       </c>
       <c r="E167" s="2" t="n">
-        <v>24.15872436525426</v>
+        <v>18.04457542061445</v>
       </c>
       <c r="F167" s="2" t="n">
-        <v>-85.34291297431514</v>
+        <v>-79.22876402967533</v>
       </c>
     </row>
     <row r="168" ht="21" customHeight="1">
@@ -6622,13 +6622,13 @@
         <v>15</v>
       </c>
       <c r="D168" s="2" t="n">
-        <v>5.127824495334824</v>
+        <v>2.723975507334824</v>
       </c>
       <c r="E168" s="2" t="n">
-        <v>24.15872436525426</v>
+        <v>18.04457542061445</v>
       </c>
       <c r="F168" s="2" t="n">
-        <v>-88.99526320915746</v>
+        <v>-82.88111426451765</v>
       </c>
     </row>
     <row r="169" ht="21" customHeight="1">
@@ -6644,13 +6644,13 @@
         <v>20</v>
       </c>
       <c r="D169" s="2" t="n">
-        <v>5.127824495334824</v>
+        <v>2.723975507334824</v>
       </c>
       <c r="E169" s="2" t="n">
-        <v>24.15872436525426</v>
+        <v>18.04457542061445</v>
       </c>
       <c r="F169" s="2" t="n">
-        <v>-91.82970231216559</v>
+        <v>-85.71555336752579</v>
       </c>
     </row>
     <row r="170" ht="21" customHeight="1">
@@ -6666,13 +6666,13 @@
         <v>5</v>
       </c>
       <c r="D170" s="2" t="n">
-        <v>3.707486484069566</v>
+        <v>1.747540752069567</v>
       </c>
       <c r="E170" s="2" t="n">
-        <v>25.54868631062882</v>
+        <v>23.58874057862882</v>
       </c>
       <c r="F170" s="2" t="n">
-        <v>-81.89358989879909</v>
+        <v>-79.9336441667991</v>
       </c>
     </row>
     <row r="171" ht="21" customHeight="1">
@@ -6688,13 +6688,13 @@
         <v>10</v>
       </c>
       <c r="D171" s="2" t="n">
-        <v>3.707486484069566</v>
+        <v>1.747540752069567</v>
       </c>
       <c r="E171" s="2" t="n">
-        <v>25.54868631062882</v>
+        <v>23.58874057862882</v>
       </c>
       <c r="F171" s="2" t="n">
-        <v>-86.54915801897928</v>
+        <v>-84.58921228697928</v>
       </c>
     </row>
     <row r="172" ht="21" customHeight="1">
@@ -6710,13 +6710,13 @@
         <v>15</v>
       </c>
       <c r="D172" s="2" t="n">
-        <v>3.707486484069566</v>
+        <v>1.747540752069567</v>
       </c>
       <c r="E172" s="2" t="n">
-        <v>25.54868631062882</v>
+        <v>23.58874057862882</v>
       </c>
       <c r="F172" s="2" t="n">
-        <v>-90.2015082538216</v>
+        <v>-88.24156252182159</v>
       </c>
     </row>
     <row r="173" ht="21" customHeight="1">
@@ -6732,13 +6732,13 @@
         <v>20</v>
       </c>
       <c r="D173" s="2" t="n">
-        <v>3.707486484069566</v>
+        <v>1.747540752069567</v>
       </c>
       <c r="E173" s="2" t="n">
-        <v>25.54868631062882</v>
+        <v>23.58874057862882</v>
       </c>
       <c r="F173" s="2" t="n">
-        <v>-93.03594735682972</v>
+        <v>-91.07600162482971</v>
       </c>
     </row>
     <row r="174" ht="21" customHeight="1">
@@ -6754,13 +6754,13 @@
         <v>5</v>
       </c>
       <c r="D174" s="2" t="n">
-        <v>4.034884875091815</v>
+        <v>1.901892111091816</v>
       </c>
       <c r="E174" s="2" t="n">
-        <v>25.87608470165107</v>
+        <v>23.74309193765107</v>
       </c>
       <c r="F174" s="2" t="n">
-        <v>-82.31053671635061</v>
+        <v>-80.17754395235062</v>
       </c>
     </row>
     <row r="175" ht="21" customHeight="1">
@@ -6776,13 +6776,13 @@
         <v>10</v>
       </c>
       <c r="D175" s="2" t="n">
-        <v>4.034884875091815</v>
+        <v>1.901892111091816</v>
       </c>
       <c r="E175" s="2" t="n">
-        <v>25.87608470165107</v>
+        <v>23.74309193765107</v>
       </c>
       <c r="F175" s="2" t="n">
-        <v>-86.96610483653079</v>
+        <v>-84.83311207253078</v>
       </c>
     </row>
     <row r="176" ht="21" customHeight="1">
@@ -6798,13 +6798,13 @@
         <v>15</v>
       </c>
       <c r="D176" s="2" t="n">
-        <v>4.034884875091815</v>
+        <v>1.901892111091816</v>
       </c>
       <c r="E176" s="2" t="n">
-        <v>25.87608470165107</v>
+        <v>23.74309193765107</v>
       </c>
       <c r="F176" s="2" t="n">
-        <v>-90.61845507137311</v>
+        <v>-88.4854623073731</v>
       </c>
     </row>
     <row r="177" ht="21" customHeight="1">
@@ -6820,13 +6820,13 @@
         <v>20</v>
       </c>
       <c r="D177" s="2" t="n">
-        <v>4.034884875091815</v>
+        <v>1.901892111091816</v>
       </c>
       <c r="E177" s="2" t="n">
-        <v>25.87608470165107</v>
+        <v>23.74309193765107</v>
       </c>
       <c r="F177" s="2" t="n">
-        <v>-93.45289417438123</v>
+        <v>-91.31990141038122</v>
       </c>
     </row>
     <row r="178" ht="21" customHeight="1">
@@ -6842,13 +6842,13 @@
         <v>5</v>
       </c>
       <c r="D178" s="2" t="n">
-        <v>4.547258254061315</v>
+        <v>2.143409266061316</v>
       </c>
       <c r="E178" s="2" t="n">
-        <v>26.38845808062057</v>
+        <v>23.98460909262057</v>
       </c>
       <c r="F178" s="2" t="n">
-        <v>-82.91707856950127</v>
+        <v>-80.51322958150126</v>
       </c>
     </row>
     <row r="179" ht="21" customHeight="1">
@@ -6864,13 +6864,13 @@
         <v>10</v>
       </c>
       <c r="D179" s="2" t="n">
-        <v>4.547258254061315</v>
+        <v>2.143409266061316</v>
       </c>
       <c r="E179" s="2" t="n">
-        <v>26.38845808062057</v>
+        <v>23.98460909262057</v>
       </c>
       <c r="F179" s="2" t="n">
-        <v>-87.57264668968145</v>
+        <v>-85.16879770168146</v>
       </c>
     </row>
     <row r="180" ht="21" customHeight="1">
@@ -6886,13 +6886,13 @@
         <v>15</v>
       </c>
       <c r="D180" s="2" t="n">
-        <v>4.547258254061315</v>
+        <v>2.143409266061316</v>
       </c>
       <c r="E180" s="2" t="n">
-        <v>26.38845808062057</v>
+        <v>23.98460909262057</v>
       </c>
       <c r="F180" s="2" t="n">
-        <v>-91.22499692452377</v>
+        <v>-88.82114793652377</v>
       </c>
     </row>
     <row r="181" ht="21" customHeight="1">
@@ -6908,13 +6908,13 @@
         <v>20</v>
       </c>
       <c r="D181" s="2" t="n">
-        <v>4.547258254061315</v>
+        <v>2.143409266061316</v>
       </c>
       <c r="E181" s="2" t="n">
-        <v>26.38845808062057</v>
+        <v>23.98460909262057</v>
       </c>
       <c r="F181" s="2" t="n">
-        <v>-94.0594360275319</v>
+        <v>-91.65558703953189</v>
       </c>
     </row>
     <row r="182" ht="21" customHeight="1">
@@ -6930,13 +6930,13 @@
         <v>5</v>
       </c>
       <c r="D182" s="2" t="n">
-        <v>4.181848068114553</v>
+        <v>2.221902336114553</v>
       </c>
       <c r="E182" s="2" t="n">
-        <v>26.0230478946738</v>
+        <v>24.0631021626738</v>
       </c>
       <c r="F182" s="2" t="n">
-        <v>-82.36795148284409</v>
+        <v>-80.40800575084408</v>
       </c>
     </row>
     <row r="183" ht="21" customHeight="1">
@@ -6952,13 +6952,13 @@
         <v>10</v>
       </c>
       <c r="D183" s="2" t="n">
-        <v>4.181848068114553</v>
+        <v>2.221902336114553</v>
       </c>
       <c r="E183" s="2" t="n">
-        <v>26.0230478946738</v>
+        <v>24.0631021626738</v>
       </c>
       <c r="F183" s="2" t="n">
-        <v>-87.02351960302425</v>
+        <v>-85.06357387102426</v>
       </c>
     </row>
     <row r="184" ht="21" customHeight="1">
@@ -6974,13 +6974,13 @@
         <v>15</v>
       </c>
       <c r="D184" s="2" t="n">
-        <v>4.181848068114553</v>
+        <v>2.221902336114553</v>
       </c>
       <c r="E184" s="2" t="n">
-        <v>26.0230478946738</v>
+        <v>24.0631021626738</v>
       </c>
       <c r="F184" s="2" t="n">
-        <v>-90.67586983786657</v>
+        <v>-88.71592410586658</v>
       </c>
     </row>
     <row r="185" ht="21" customHeight="1">
@@ -6996,13 +6996,13 @@
         <v>20</v>
       </c>
       <c r="D185" s="2" t="n">
-        <v>4.181848068114553</v>
+        <v>2.221902336114553</v>
       </c>
       <c r="E185" s="2" t="n">
-        <v>26.0230478946738</v>
+        <v>24.0631021626738</v>
       </c>
       <c r="F185" s="2" t="n">
-        <v>-93.51030894087469</v>
+        <v>-91.5503632088747</v>
       </c>
     </row>
     <row r="186" ht="21" customHeight="1">
@@ -7018,13 +7018,13 @@
         <v>5</v>
       </c>
       <c r="D186" s="2" t="n">
-        <v>4.551558196068465</v>
+        <v>2.418565432068466</v>
       </c>
       <c r="E186" s="2" t="n">
-        <v>26.39275802262772</v>
+        <v>24.25976525862772</v>
       </c>
       <c r="F186" s="2" t="n">
-        <v>-82.82721003732726</v>
+        <v>-80.69421727332727</v>
       </c>
     </row>
     <row r="187" ht="21" customHeight="1">
@@ -7040,13 +7040,13 @@
         <v>10</v>
       </c>
       <c r="D187" s="2" t="n">
-        <v>4.551558196068465</v>
+        <v>2.418565432068466</v>
       </c>
       <c r="E187" s="2" t="n">
-        <v>26.39275802262772</v>
+        <v>24.25976525862772</v>
       </c>
       <c r="F187" s="2" t="n">
-        <v>-87.48277815750744</v>
+        <v>-85.34978539350743</v>
       </c>
     </row>
     <row r="188" ht="21" customHeight="1">
@@ -7062,13 +7062,13 @@
         <v>15</v>
       </c>
       <c r="D188" s="2" t="n">
-        <v>4.551558196068465</v>
+        <v>2.418565432068466</v>
       </c>
       <c r="E188" s="2" t="n">
-        <v>26.39275802262772</v>
+        <v>24.25976525862772</v>
       </c>
       <c r="F188" s="2" t="n">
-        <v>-91.13512839234976</v>
+        <v>-89.00213562834975</v>
       </c>
     </row>
     <row r="189" ht="21" customHeight="1">
@@ -7084,13 +7084,13 @@
         <v>20</v>
       </c>
       <c r="D189" s="2" t="n">
-        <v>4.551558196068465</v>
+        <v>2.418565432068466</v>
       </c>
       <c r="E189" s="2" t="n">
-        <v>26.39275802262772</v>
+        <v>24.25976525862772</v>
       </c>
       <c r="F189" s="2" t="n">
-        <v>-93.96956749535788</v>
+        <v>-91.83657473135787</v>
       </c>
     </row>
     <row r="190" ht="21" customHeight="1">
@@ -7106,13 +7106,13 @@
         <v>5</v>
       </c>
       <c r="D190" s="2" t="n">
-        <v>5.129593122350436</v>
+        <v>2.725744134350437</v>
       </c>
       <c r="E190" s="2" t="n">
-        <v>26.97079294890969</v>
+        <v>24.56694396090969</v>
       </c>
       <c r="F190" s="2" t="n">
-        <v>-83.49941343779039</v>
+        <v>-81.0955644497904</v>
       </c>
     </row>
     <row r="191" ht="21" customHeight="1">
@@ -7128,13 +7128,13 @@
         <v>10</v>
       </c>
       <c r="D191" s="2" t="n">
-        <v>5.129593122350436</v>
+        <v>2.725744134350437</v>
       </c>
       <c r="E191" s="2" t="n">
-        <v>26.97079294890969</v>
+        <v>24.56694396090969</v>
       </c>
       <c r="F191" s="2" t="n">
-        <v>-88.15498155797057</v>
+        <v>-85.75113256997057</v>
       </c>
     </row>
     <row r="192" ht="21" customHeight="1">
@@ -7150,13 +7150,13 @@
         <v>15</v>
       </c>
       <c r="D192" s="2" t="n">
-        <v>5.129593122350436</v>
+        <v>2.725744134350437</v>
       </c>
       <c r="E192" s="2" t="n">
-        <v>26.97079294890969</v>
+        <v>24.56694396090969</v>
       </c>
       <c r="F192" s="2" t="n">
-        <v>-91.80733179281289</v>
+        <v>-89.40348280481288</v>
       </c>
     </row>
     <row r="193" ht="21" customHeight="1">
@@ -7172,13 +7172,13 @@
         <v>20</v>
       </c>
       <c r="D193" s="2" t="n">
-        <v>5.129593122350436</v>
+        <v>2.725744134350437</v>
       </c>
       <c r="E193" s="2" t="n">
-        <v>26.97079294890969</v>
+        <v>24.56694396090969</v>
       </c>
       <c r="F193" s="2" t="n">
-        <v>-94.64177089582103</v>
+        <v>-92.23792190782103</v>
       </c>
     </row>
     <row r="194" ht="21" customHeight="1">
@@ -7194,13 +7194,13 @@
         <v>5</v>
       </c>
       <c r="D194" s="2" t="n">
-        <v>1.225188144348781</v>
+        <v>1.103973076968484</v>
       </c>
       <c r="E194" s="2" t="n">
-        <v>20.25608801426822</v>
+        <v>16.42457299024811</v>
       </c>
       <c r="F194" s="2" t="n">
-        <v>-76.6009916024385</v>
+        <v>-72.76947657841839</v>
       </c>
     </row>
     <row r="195" ht="21" customHeight="1">
@@ -7216,13 +7216,13 @@
         <v>10</v>
       </c>
       <c r="D195" s="2" t="n">
-        <v>1.225188144348781</v>
+        <v>1.103973076968484</v>
       </c>
       <c r="E195" s="2" t="n">
-        <v>20.25608801426822</v>
+        <v>16.42457299024811</v>
       </c>
       <c r="F195" s="2" t="n">
-        <v>-81.25655972261868</v>
+        <v>-77.42504469859857</v>
       </c>
     </row>
     <row r="196" ht="21" customHeight="1">
@@ -7238,13 +7238,13 @@
         <v>15</v>
       </c>
       <c r="D196" s="2" t="n">
-        <v>1.225188144348781</v>
+        <v>1.103973076968484</v>
       </c>
       <c r="E196" s="2" t="n">
-        <v>20.25608801426822</v>
+        <v>16.42457299024811</v>
       </c>
       <c r="F196" s="2" t="n">
-        <v>-84.90890995746099</v>
+        <v>-81.07739493344089</v>
       </c>
     </row>
     <row r="197" ht="21" customHeight="1">
@@ -7260,13 +7260,13 @@
         <v>20</v>
       </c>
       <c r="D197" s="2" t="n">
-        <v>1.225188144348781</v>
+        <v>1.103973076968484</v>
       </c>
       <c r="E197" s="2" t="n">
-        <v>20.25608801426822</v>
+        <v>16.42457299024811</v>
       </c>
       <c r="F197" s="2" t="n">
-        <v>-87.74334906046911</v>
+        <v>-83.91183403644901</v>
       </c>
     </row>
     <row r="198" ht="21" customHeight="1">
@@ -7282,13 +7282,13 @@
         <v>5</v>
       </c>
       <c r="D198" s="2" t="n">
-        <v>1.33431598127781</v>
+        <v>1.202075534479603</v>
       </c>
       <c r="E198" s="2" t="n">
-        <v>20.36521585119725</v>
+        <v>16.52267544775923</v>
       </c>
       <c r="F198" s="2" t="n">
-        <v>-76.79966786589679</v>
+        <v>-72.95712746245877</v>
       </c>
     </row>
     <row r="199" ht="21" customHeight="1">
@@ -7304,13 +7304,13 @@
         <v>10</v>
       </c>
       <c r="D199" s="2" t="n">
-        <v>1.33431598127781</v>
+        <v>1.202075534479603</v>
       </c>
       <c r="E199" s="2" t="n">
-        <v>20.36521585119725</v>
+        <v>16.52267544775923</v>
       </c>
       <c r="F199" s="2" t="n">
-        <v>-81.45523598607697</v>
+        <v>-77.61269558263895</v>
       </c>
     </row>
     <row r="200" ht="21" customHeight="1">
@@ -7326,13 +7326,13 @@
         <v>15</v>
       </c>
       <c r="D200" s="2" t="n">
-        <v>1.33431598127781</v>
+        <v>1.202075534479603</v>
       </c>
       <c r="E200" s="2" t="n">
-        <v>20.36521585119725</v>
+        <v>16.52267544775923</v>
       </c>
       <c r="F200" s="2" t="n">
-        <v>-85.10758622091929</v>
+        <v>-81.26504581748127</v>
       </c>
     </row>
     <row r="201" ht="21" customHeight="1">
@@ -7348,13 +7348,13 @@
         <v>20</v>
       </c>
       <c r="D201" s="2" t="n">
-        <v>1.33431598127781</v>
+        <v>1.202075534479603</v>
       </c>
       <c r="E201" s="2" t="n">
-        <v>20.36521585119725</v>
+        <v>16.52267544775923</v>
       </c>
       <c r="F201" s="2" t="n">
-        <v>-87.94202532392741</v>
+        <v>-84.09948492048939</v>
       </c>
     </row>
     <row r="202" ht="21" customHeight="1">
@@ -7370,13 +7370,13 @@
         <v>5</v>
       </c>
       <c r="D202" s="2" t="n">
-        <v>1.503868932308414</v>
+        <v>1.354796755203143</v>
       </c>
       <c r="E202" s="2" t="n">
-        <v>20.53476880222785</v>
+        <v>16.67539666848277</v>
       </c>
       <c r="F202" s="2" t="n">
-        <v>-77.06338929110856</v>
+        <v>-73.20401715736347</v>
       </c>
     </row>
     <row r="203" ht="21" customHeight="1">
@@ -7392,13 +7392,13 @@
         <v>10</v>
       </c>
       <c r="D203" s="2" t="n">
-        <v>1.503868932308414</v>
+        <v>1.354796755203143</v>
       </c>
       <c r="E203" s="2" t="n">
-        <v>20.53476880222785</v>
+        <v>16.67539666848277</v>
       </c>
       <c r="F203" s="2" t="n">
-        <v>-81.71895741128873</v>
+        <v>-77.85958527754366</v>
       </c>
     </row>
     <row r="204" ht="21" customHeight="1">
@@ -7414,13 +7414,13 @@
         <v>15</v>
       </c>
       <c r="D204" s="2" t="n">
-        <v>1.503868932308414</v>
+        <v>1.354796755203143</v>
       </c>
       <c r="E204" s="2" t="n">
-        <v>20.53476880222785</v>
+        <v>16.67539666848277</v>
       </c>
       <c r="F204" s="2" t="n">
-        <v>-85.37130764613104</v>
+        <v>-81.51193551238597</v>
       </c>
     </row>
     <row r="205" ht="21" customHeight="1">
@@ -7436,13 +7436,13 @@
         <v>20</v>
       </c>
       <c r="D205" s="2" t="n">
-        <v>1.503868932308414</v>
+        <v>1.354796755203143</v>
       </c>
       <c r="E205" s="2" t="n">
-        <v>20.53476880222785</v>
+        <v>16.67539666848277</v>
       </c>
       <c r="F205" s="2" t="n">
-        <v>-88.20574674913919</v>
+        <v>-84.3463746153941</v>
       </c>
     </row>
     <row r="206" ht="21" customHeight="1">
@@ -7458,13 +7458,13 @@
         <v>5</v>
       </c>
       <c r="D206" s="2" t="n">
-        <v>1.021395793958125</v>
+        <v>1.185467153807593</v>
       </c>
       <c r="E206" s="2" t="n">
-        <v>20.05229566387756</v>
+        <v>23.02666698036684</v>
       </c>
       <c r="F206" s="2" t="n">
-        <v>-76.39719925204784</v>
+        <v>-79.37157056853712</v>
       </c>
     </row>
     <row r="207" ht="21" customHeight="1">
@@ -7480,13 +7480,13 @@
         <v>10</v>
       </c>
       <c r="D207" s="2" t="n">
-        <v>1.021395793958125</v>
+        <v>1.185467153807593</v>
       </c>
       <c r="E207" s="2" t="n">
-        <v>20.05229566387756</v>
+        <v>23.02666698036684</v>
       </c>
       <c r="F207" s="2" t="n">
-        <v>-81.05276737222802</v>
+        <v>-84.0271386887173</v>
       </c>
     </row>
     <row r="208" ht="21" customHeight="1">
@@ -7502,13 +7502,13 @@
         <v>15</v>
       </c>
       <c r="D208" s="2" t="n">
-        <v>1.021395793958125</v>
+        <v>1.185467153807593</v>
       </c>
       <c r="E208" s="2" t="n">
-        <v>20.05229566387756</v>
+        <v>23.02666698036684</v>
       </c>
       <c r="F208" s="2" t="n">
-        <v>-84.70511760707033</v>
+        <v>-87.67948892355962</v>
       </c>
     </row>
     <row r="209" ht="21" customHeight="1">
@@ -7524,13 +7524,13 @@
         <v>20</v>
       </c>
       <c r="D209" s="2" t="n">
-        <v>1.021395793958125</v>
+        <v>1.185467153807593</v>
       </c>
       <c r="E209" s="2" t="n">
-        <v>20.05229566387756</v>
+        <v>23.02666698036684</v>
       </c>
       <c r="F209" s="2" t="n">
-        <v>-87.53955671007846</v>
+        <v>-90.51392802656774</v>
       </c>
     </row>
     <row r="210" ht="21" customHeight="1">
@@ -7546,13 +7546,13 @@
         <v>5</v>
       </c>
       <c r="D210" s="2" t="n">
-        <v>1.11234591876113</v>
+        <v>1.290448699649698</v>
       </c>
       <c r="E210" s="2" t="n">
-        <v>20.14324578868057</v>
+        <v>23.13164852620895</v>
       </c>
       <c r="F210" s="2" t="n">
-        <v>-76.57769780338012</v>
+        <v>-79.56610054090849</v>
       </c>
     </row>
     <row r="211" ht="21" customHeight="1">
@@ -7568,13 +7568,13 @@
         <v>10</v>
       </c>
       <c r="D211" s="2" t="n">
-        <v>1.11234591876113</v>
+        <v>1.290448699649698</v>
       </c>
       <c r="E211" s="2" t="n">
-        <v>20.14324578868057</v>
+        <v>23.13164852620895</v>
       </c>
       <c r="F211" s="2" t="n">
-        <v>-81.23326592356028</v>
+        <v>-84.22166866108867</v>
       </c>
     </row>
     <row r="212" ht="21" customHeight="1">
@@ -7590,13 +7590,13 @@
         <v>15</v>
       </c>
       <c r="D212" s="2" t="n">
-        <v>1.11234591876113</v>
+        <v>1.290448699649698</v>
       </c>
       <c r="E212" s="2" t="n">
-        <v>20.14324578868057</v>
+        <v>23.13164852620895</v>
       </c>
       <c r="F212" s="2" t="n">
-        <v>-84.8856161584026</v>
+        <v>-87.87401889593099</v>
       </c>
     </row>
     <row r="213" ht="21" customHeight="1">
@@ -7612,13 +7612,13 @@
         <v>20</v>
       </c>
       <c r="D213" s="2" t="n">
-        <v>1.11234591876113</v>
+        <v>1.290448699649698</v>
       </c>
       <c r="E213" s="2" t="n">
-        <v>20.14324578868057</v>
+        <v>23.13164852620895</v>
       </c>
       <c r="F213" s="2" t="n">
-        <v>-87.72005526141072</v>
+        <v>-90.70845799893911</v>
       </c>
     </row>
     <row r="214" ht="21" customHeight="1">
@@ -7634,13 +7634,13 @@
         <v>5</v>
       </c>
       <c r="D214" s="2" t="n">
-        <v>1.253689753566532</v>
+        <v>1.45435345896763</v>
       </c>
       <c r="E214" s="2" t="n">
-        <v>20.28458962348597</v>
+        <v>23.29555328552688</v>
       </c>
       <c r="F214" s="2" t="n">
-        <v>-76.81321011236668</v>
+        <v>-79.82417377440758</v>
       </c>
     </row>
     <row r="215" ht="21" customHeight="1">
@@ -7656,13 +7656,13 @@
         <v>10</v>
       </c>
       <c r="D215" s="2" t="n">
-        <v>1.253689753566532</v>
+        <v>1.45435345896763</v>
       </c>
       <c r="E215" s="2" t="n">
-        <v>20.28458962348597</v>
+        <v>23.29555328552688</v>
       </c>
       <c r="F215" s="2" t="n">
-        <v>-81.46877823254685</v>
+        <v>-84.47974189458776</v>
       </c>
     </row>
     <row r="216" ht="21" customHeight="1">
@@ -7678,13 +7678,13 @@
         <v>15</v>
       </c>
       <c r="D216" s="2" t="n">
-        <v>1.253689753566532</v>
+        <v>1.45435345896763</v>
       </c>
       <c r="E216" s="2" t="n">
-        <v>20.28458962348597</v>
+        <v>23.29555328552688</v>
       </c>
       <c r="F216" s="2" t="n">
-        <v>-85.12112846738917</v>
+        <v>-88.13209212943008</v>
       </c>
     </row>
     <row r="217" ht="21" customHeight="1">
@@ -7700,13 +7700,13 @@
         <v>20</v>
       </c>
       <c r="D217" s="2" t="n">
-        <v>1.253689753566532</v>
+        <v>1.45435345896763</v>
       </c>
       <c r="E217" s="2" t="n">
-        <v>20.28458962348597</v>
+        <v>23.29555328552688</v>
       </c>
       <c r="F217" s="2" t="n">
-        <v>-87.95556757039731</v>
+        <v>-90.96653123243821</v>
       </c>
     </row>
     <row r="218" ht="21" customHeight="1">
@@ -7722,13 +7722,13 @@
         <v>5</v>
       </c>
       <c r="D218" s="2" t="n">
-        <v>1.636722009404119</v>
+        <v>1.120093261827839</v>
       </c>
       <c r="E218" s="2" t="n">
-        <v>23.47792183596337</v>
+        <v>20.15099313174728</v>
       </c>
       <c r="F218" s="2" t="n">
-        <v>-79.82282542413365</v>
+        <v>-76.49589671991757</v>
       </c>
     </row>
     <row r="219" ht="21" customHeight="1">
@@ -7744,13 +7744,13 @@
         <v>10</v>
       </c>
       <c r="D219" s="2" t="n">
-        <v>1.636722009404119</v>
+        <v>1.120093261827839</v>
       </c>
       <c r="E219" s="2" t="n">
-        <v>23.47792183596337</v>
+        <v>20.15099313174728</v>
       </c>
       <c r="F219" s="2" t="n">
-        <v>-84.47839354431383</v>
+        <v>-81.15146484009773</v>
       </c>
     </row>
     <row r="220" ht="21" customHeight="1">
@@ -7766,13 +7766,13 @@
         <v>15</v>
       </c>
       <c r="D220" s="2" t="n">
-        <v>1.636722009404119</v>
+        <v>1.120093261827839</v>
       </c>
       <c r="E220" s="2" t="n">
-        <v>23.47792183596337</v>
+        <v>20.15099313174728</v>
       </c>
       <c r="F220" s="2" t="n">
-        <v>-88.13074377915615</v>
+        <v>-84.80381507494005</v>
       </c>
     </row>
     <row r="221" ht="21" customHeight="1">
@@ -7788,13 +7788,13 @@
         <v>20</v>
       </c>
       <c r="D221" s="2" t="n">
-        <v>1.636722009404119</v>
+        <v>1.120093261827839</v>
       </c>
       <c r="E221" s="2" t="n">
-        <v>23.47792183596337</v>
+        <v>20.15099313174728</v>
       </c>
       <c r="F221" s="2" t="n">
-        <v>-90.96518288216427</v>
+        <v>-87.63825417794817</v>
       </c>
     </row>
     <row r="222" ht="21" customHeight="1">
@@ -7810,13 +7810,13 @@
         <v>5</v>
       </c>
       <c r="D222" s="2" t="n">
-        <v>1.781231054380299</v>
+        <v>1.2196335950945</v>
       </c>
       <c r="E222" s="2" t="n">
-        <v>23.62243088093955</v>
+        <v>20.25053346501394</v>
       </c>
       <c r="F222" s="2" t="n">
-        <v>-80.05688289563909</v>
+        <v>-76.68498547971348</v>
       </c>
     </row>
     <row r="223" ht="21" customHeight="1">
@@ -7832,13 +7832,13 @@
         <v>10</v>
       </c>
       <c r="D223" s="2" t="n">
-        <v>1.781231054380299</v>
+        <v>1.2196335950945</v>
       </c>
       <c r="E223" s="2" t="n">
-        <v>23.62243088093955</v>
+        <v>20.25053346501394</v>
       </c>
       <c r="F223" s="2" t="n">
-        <v>-84.71245101581927</v>
+        <v>-81.34055359989367</v>
       </c>
     </row>
     <row r="224" ht="21" customHeight="1">
@@ -7854,13 +7854,13 @@
         <v>15</v>
       </c>
       <c r="D224" s="2" t="n">
-        <v>1.781231054380299</v>
+        <v>1.2196335950945</v>
       </c>
       <c r="E224" s="2" t="n">
-        <v>23.62243088093955</v>
+        <v>20.25053346501394</v>
       </c>
       <c r="F224" s="2" t="n">
-        <v>-88.36480125066159</v>
+        <v>-84.99290383473598</v>
       </c>
     </row>
     <row r="225" ht="21" customHeight="1">
@@ -7876,13 +7876,13 @@
         <v>20</v>
       </c>
       <c r="D225" s="2" t="n">
-        <v>1.781231054380299</v>
+        <v>1.2196335950945</v>
       </c>
       <c r="E225" s="2" t="n">
-        <v>23.62243088093955</v>
+        <v>20.25053346501394</v>
       </c>
       <c r="F225" s="2" t="n">
-        <v>-91.19924035366971</v>
+        <v>-87.82734293774411</v>
       </c>
     </row>
     <row r="226" ht="21" customHeight="1">
@@ -7898,13 +7898,13 @@
         <v>5</v>
       </c>
       <c r="D226" s="2" t="n">
-        <v>2.007419124777797</v>
+        <v>1.374586185972011</v>
       </c>
       <c r="E226" s="2" t="n">
-        <v>23.84861895133705</v>
+        <v>20.40548605589145</v>
       </c>
       <c r="F226" s="2" t="n">
-        <v>-80.37723944021775</v>
+        <v>-76.93410654477215</v>
       </c>
     </row>
     <row r="227" ht="21" customHeight="1">
@@ -7920,13 +7920,13 @@
         <v>10</v>
       </c>
       <c r="D227" s="2" t="n">
-        <v>2.007419124777797</v>
+        <v>1.374586185972011</v>
       </c>
       <c r="E227" s="2" t="n">
-        <v>23.84861895133705</v>
+        <v>20.40548605589145</v>
       </c>
       <c r="F227" s="2" t="n">
-        <v>-85.03280756039793</v>
+        <v>-81.58967466495233</v>
       </c>
     </row>
     <row r="228" ht="21" customHeight="1">
@@ -7942,13 +7942,13 @@
         <v>15</v>
       </c>
       <c r="D228" s="2" t="n">
-        <v>2.007419124777797</v>
+        <v>1.374586185972011</v>
       </c>
       <c r="E228" s="2" t="n">
-        <v>23.84861895133705</v>
+        <v>20.40548605589145</v>
       </c>
       <c r="F228" s="2" t="n">
-        <v>-88.68515779524024</v>
+        <v>-85.24202489979464</v>
       </c>
     </row>
     <row r="229" ht="21" customHeight="1">
@@ -7964,13 +7964,13 @@
         <v>20</v>
       </c>
       <c r="D229" s="2" t="n">
-        <v>2.007419124777797</v>
+        <v>1.374586185972011</v>
       </c>
       <c r="E229" s="2" t="n">
-        <v>23.84861895133705</v>
+        <v>20.40548605589145</v>
       </c>
       <c r="F229" s="2" t="n">
-        <v>-91.51959689824838</v>
+        <v>-88.07646400280278</v>
       </c>
     </row>
     <row r="230" ht="21" customHeight="1">
@@ -7989,10 +7989,10 @@
         <v>1.549984181112594</v>
       </c>
       <c r="E230" s="2" t="n">
-        <v>16.87058409439222</v>
+        <v>20.58088405103203</v>
       </c>
       <c r="F230" s="2" t="n">
-        <v>-73.2154876825625</v>
+        <v>-76.92578763920231</v>
       </c>
     </row>
     <row r="231" ht="21" customHeight="1">
@@ -8011,10 +8011,10 @@
         <v>1.549984181112594</v>
       </c>
       <c r="E231" s="2" t="n">
-        <v>16.87058409439222</v>
+        <v>20.58088405103203</v>
       </c>
       <c r="F231" s="2" t="n">
-        <v>-77.87105580274269</v>
+        <v>-81.58135575938249</v>
       </c>
     </row>
     <row r="232" ht="21" customHeight="1">
@@ -8033,10 +8033,10 @@
         <v>1.549984181112594</v>
       </c>
       <c r="E232" s="2" t="n">
-        <v>16.87058409439222</v>
+        <v>20.58088405103203</v>
       </c>
       <c r="F232" s="2" t="n">
-        <v>-81.523406037585</v>
+        <v>-85.23370599422481</v>
       </c>
     </row>
     <row r="233" ht="21" customHeight="1">
@@ -8055,10 +8055,10 @@
         <v>1.549984181112594</v>
       </c>
       <c r="E233" s="2" t="n">
-        <v>16.87058409439222</v>
+        <v>20.58088405103203</v>
       </c>
       <c r="F233" s="2" t="n">
-        <v>-84.35784514059313</v>
+        <v>-88.06814509723293</v>
       </c>
     </row>
     <row r="234" ht="21" customHeight="1">
@@ -8077,10 +8077,10 @@
         <v>1.686834991729061</v>
       </c>
       <c r="E234" s="2" t="n">
-        <v>17.00743490500869</v>
+        <v>20.7177348616485</v>
       </c>
       <c r="F234" s="2" t="n">
-        <v>-73.44188691970822</v>
+        <v>-77.15218687634804</v>
       </c>
     </row>
     <row r="235" ht="21" customHeight="1">
@@ -8099,10 +8099,10 @@
         <v>1.686834991729061</v>
       </c>
       <c r="E235" s="2" t="n">
-        <v>17.00743490500869</v>
+        <v>20.7177348616485</v>
       </c>
       <c r="F235" s="2" t="n">
-        <v>-78.09745503988842</v>
+        <v>-81.80775499652822</v>
       </c>
     </row>
     <row r="236" ht="21" customHeight="1">
@@ -8121,10 +8121,10 @@
         <v>1.686834991729061</v>
       </c>
       <c r="E236" s="2" t="n">
-        <v>17.00743490500869</v>
+        <v>20.7177348616485</v>
       </c>
       <c r="F236" s="2" t="n">
-        <v>-81.74980527473073</v>
+        <v>-85.46010523137053</v>
       </c>
     </row>
     <row r="237" ht="21" customHeight="1">
@@ -8143,10 +8143,10 @@
         <v>1.686834991729061</v>
       </c>
       <c r="E237" s="2" t="n">
-        <v>17.00743490500869</v>
+        <v>20.7177348616485</v>
       </c>
       <c r="F237" s="2" t="n">
-        <v>-84.58424437773886</v>
+        <v>-88.29454433437866</v>
       </c>
     </row>
     <row r="238" ht="21" customHeight="1">
@@ -8165,10 +8165,10 @@
         <v>1.901036260520053</v>
       </c>
       <c r="E238" s="2" t="n">
-        <v>17.22163617379968</v>
+        <v>20.93193613043949</v>
       </c>
       <c r="F238" s="2" t="n">
-        <v>-73.75025666268039</v>
+        <v>-77.4605566193202</v>
       </c>
     </row>
     <row r="239" ht="21" customHeight="1">
@@ -8187,10 +8187,10 @@
         <v>1.901036260520053</v>
       </c>
       <c r="E239" s="2" t="n">
-        <v>17.22163617379968</v>
+        <v>20.93193613043949</v>
       </c>
       <c r="F239" s="2" t="n">
-        <v>-78.40582478286056</v>
+        <v>-82.11612473950038</v>
       </c>
     </row>
     <row r="240" ht="21" customHeight="1">
@@ -8209,10 +8209,10 @@
         <v>1.901036260520053</v>
       </c>
       <c r="E240" s="2" t="n">
-        <v>17.22163617379968</v>
+        <v>20.93193613043949</v>
       </c>
       <c r="F240" s="2" t="n">
-        <v>-82.05817501770288</v>
+        <v>-85.76847497434269</v>
       </c>
     </row>
     <row r="241" ht="21" customHeight="1">
@@ -8231,10 +8231,10 @@
         <v>1.901036260520053</v>
       </c>
       <c r="E241" s="2" t="n">
-        <v>17.22163617379968</v>
+        <v>20.93193613043949</v>
       </c>
       <c r="F241" s="2" t="n">
-        <v>-84.89261412071102</v>
+        <v>-88.60291407735083</v>
       </c>
     </row>
     <row r="242" ht="21" customHeight="1">
@@ -8778,13 +8778,13 @@
         <v>5</v>
       </c>
       <c r="D266" s="2" t="n">
-        <v>1.633318459280647</v>
+        <v>1.291933078</v>
       </c>
       <c r="E266" s="2" t="n">
-        <v>23.4745182858399</v>
+        <v>16.61253299127963</v>
       </c>
       <c r="F266" s="2" t="n">
-        <v>-79.81942187401017</v>
+        <v>-72.9574365794499</v>
       </c>
     </row>
     <row r="267" ht="21" customHeight="1">
@@ -8800,13 +8800,13 @@
         <v>10</v>
       </c>
       <c r="D267" s="2" t="n">
-        <v>1.633318459280647</v>
+        <v>1.291933078</v>
       </c>
       <c r="E267" s="2" t="n">
-        <v>23.4745182858399</v>
+        <v>16.61253299127963</v>
       </c>
       <c r="F267" s="2" t="n">
-        <v>-84.47498999419037</v>
+        <v>-77.61300469963008</v>
       </c>
     </row>
     <row r="268" ht="21" customHeight="1">
@@ -8822,13 +8822,13 @@
         <v>15</v>
       </c>
       <c r="D268" s="2" t="n">
-        <v>1.633318459280647</v>
+        <v>1.291933078</v>
       </c>
       <c r="E268" s="2" t="n">
-        <v>23.4745182858399</v>
+        <v>16.61253299127963</v>
       </c>
       <c r="F268" s="2" t="n">
-        <v>-88.12734022903268</v>
+        <v>-81.2653549344724</v>
       </c>
     </row>
     <row r="269" ht="21" customHeight="1">
@@ -8844,13 +8844,13 @@
         <v>20</v>
       </c>
       <c r="D269" s="2" t="n">
-        <v>1.633318459280647</v>
+        <v>1.291933078</v>
       </c>
       <c r="E269" s="2" t="n">
-        <v>23.4745182858399</v>
+        <v>16.61253299127963</v>
       </c>
       <c r="F269" s="2" t="n">
-        <v>-90.96177933204081</v>
+        <v>-84.09979403748052</v>
       </c>
     </row>
     <row r="270" ht="21" customHeight="1">
@@ -8866,13 +8866,13 @@
         <v>5</v>
       </c>
       <c r="D270" s="2" t="n">
-        <v>1.778247098772479</v>
+        <v>1.406000106</v>
       </c>
       <c r="E270" s="2" t="n">
-        <v>23.61944692533173</v>
+        <v>16.72660001927963</v>
       </c>
       <c r="F270" s="2" t="n">
-        <v>-80.05389894003127</v>
+        <v>-73.16105203397917</v>
       </c>
     </row>
     <row r="271" ht="21" customHeight="1">
@@ -8888,13 +8888,13 @@
         <v>10</v>
       </c>
       <c r="D271" s="2" t="n">
-        <v>1.778247098772479</v>
+        <v>1.406000106</v>
       </c>
       <c r="E271" s="2" t="n">
-        <v>23.61944692533173</v>
+        <v>16.72660001927963</v>
       </c>
       <c r="F271" s="2" t="n">
-        <v>-84.70946706021145</v>
+        <v>-77.81662015415935</v>
       </c>
     </row>
     <row r="272" ht="21" customHeight="1">
@@ -8910,13 +8910,13 @@
         <v>15</v>
       </c>
       <c r="D272" s="2" t="n">
-        <v>1.778247098772479</v>
+        <v>1.406000106</v>
       </c>
       <c r="E272" s="2" t="n">
-        <v>23.61944692533173</v>
+        <v>16.72660001927963</v>
       </c>
       <c r="F272" s="2" t="n">
-        <v>-88.36181729505377</v>
+        <v>-81.46897038900167</v>
       </c>
     </row>
     <row r="273" ht="21" customHeight="1">
@@ -8932,13 +8932,13 @@
         <v>20</v>
       </c>
       <c r="D273" s="2" t="n">
-        <v>1.778247098772479</v>
+        <v>1.406000106</v>
       </c>
       <c r="E273" s="2" t="n">
-        <v>23.61944692533173</v>
+        <v>16.72660001927963</v>
       </c>
       <c r="F273" s="2" t="n">
-        <v>-91.19625639806189</v>
+        <v>-84.30340949200979</v>
       </c>
     </row>
     <row r="274" ht="21" customHeight="1">
@@ -8954,13 +8954,13 @@
         <v>5</v>
       </c>
       <c r="D274" s="2" t="n">
-        <v>2.00414382934684</v>
+        <v>1.584539802</v>
       </c>
       <c r="E274" s="2" t="n">
-        <v>23.84534365590609</v>
+        <v>16.90513971527962</v>
       </c>
       <c r="F274" s="2" t="n">
-        <v>-80.3739641447868</v>
+        <v>-73.43376020416034</v>
       </c>
     </row>
     <row r="275" ht="21" customHeight="1">
@@ -8976,13 +8976,13 @@
         <v>10</v>
       </c>
       <c r="D275" s="2" t="n">
-        <v>2.00414382934684</v>
+        <v>1.584539802</v>
       </c>
       <c r="E275" s="2" t="n">
-        <v>23.84534365590609</v>
+        <v>16.90513971527962</v>
       </c>
       <c r="F275" s="2" t="n">
-        <v>-85.02953226496697</v>
+        <v>-78.0893283243405</v>
       </c>
     </row>
     <row r="276" ht="21" customHeight="1">
@@ -8998,13 +8998,13 @@
         <v>15</v>
       </c>
       <c r="D276" s="2" t="n">
-        <v>2.00414382934684</v>
+        <v>1.584539802</v>
       </c>
       <c r="E276" s="2" t="n">
-        <v>23.84534365590609</v>
+        <v>16.90513971527962</v>
       </c>
       <c r="F276" s="2" t="n">
-        <v>-88.68188249980929</v>
+        <v>-81.74167855918282</v>
       </c>
     </row>
     <row r="277" ht="21" customHeight="1">
@@ -9020,13 +9020,13 @@
         <v>20</v>
       </c>
       <c r="D277" s="2" t="n">
-        <v>2.00414382934684</v>
+        <v>1.584539802</v>
       </c>
       <c r="E277" s="2" t="n">
-        <v>23.84534365590609</v>
+        <v>16.90513971527962</v>
       </c>
       <c r="F277" s="2" t="n">
-        <v>-91.51632160281743</v>
+        <v>-84.57611766219097</v>
       </c>
     </row>
     <row r="278" ht="21" customHeight="1">
@@ -9042,13 +9042,13 @@
         <v>5</v>
       </c>
       <c r="D278" s="2" t="n">
-        <v>1.040457951460749</v>
+        <v>1.230047031861604</v>
       </c>
       <c r="E278" s="2" t="n">
-        <v>16.36105786474037</v>
+        <v>23.07124685842086</v>
       </c>
       <c r="F278" s="2" t="n">
-        <v>-72.70596145291066</v>
+        <v>-79.41615044659113</v>
       </c>
     </row>
     <row r="279" ht="21" customHeight="1">
@@ -9064,13 +9064,13 @@
         <v>10</v>
       </c>
       <c r="D279" s="2" t="n">
-        <v>1.040457951460749</v>
+        <v>1.230047031861604</v>
       </c>
       <c r="E279" s="2" t="n">
-        <v>16.36105786474037</v>
+        <v>23.07124685842086</v>
       </c>
       <c r="F279" s="2" t="n">
-        <v>-77.36152957309083</v>
+        <v>-84.07171856677132</v>
       </c>
     </row>
     <row r="280" ht="21" customHeight="1">
@@ -9086,13 +9086,13 @@
         <v>15</v>
       </c>
       <c r="D280" s="2" t="n">
-        <v>1.040457951460749</v>
+        <v>1.230047031861604</v>
       </c>
       <c r="E280" s="2" t="n">
-        <v>16.36105786474037</v>
+        <v>23.07124685842086</v>
       </c>
       <c r="F280" s="2" t="n">
-        <v>-81.01387980793315</v>
+        <v>-87.72406880161364</v>
       </c>
     </row>
     <row r="281" ht="21" customHeight="1">
@@ -9108,13 +9108,13 @@
         <v>20</v>
       </c>
       <c r="D281" s="2" t="n">
-        <v>1.040457951460749</v>
+        <v>1.230047031861604</v>
       </c>
       <c r="E281" s="2" t="n">
-        <v>16.36105786474037</v>
+        <v>23.07124685842086</v>
       </c>
       <c r="F281" s="2" t="n">
-        <v>-83.84831891094127</v>
+        <v>-90.55850790462176</v>
       </c>
     </row>
     <row r="282" ht="21" customHeight="1">
@@ -9130,13 +9130,13 @@
         <v>5</v>
       </c>
       <c r="D282" s="2" t="n">
-        <v>1.132321801301813</v>
+        <v>1.33900497911586</v>
       </c>
       <c r="E282" s="2" t="n">
-        <v>16.45292171458144</v>
+        <v>23.18020480567511</v>
       </c>
       <c r="F282" s="2" t="n">
-        <v>-72.88737372928098</v>
+        <v>-79.61465682037465</v>
       </c>
     </row>
     <row r="283" ht="21" customHeight="1">
@@ -9152,13 +9152,13 @@
         <v>10</v>
       </c>
       <c r="D283" s="2" t="n">
-        <v>1.132321801301813</v>
+        <v>1.33900497911586</v>
       </c>
       <c r="E283" s="2" t="n">
-        <v>16.45292171458144</v>
+        <v>23.18020480567511</v>
       </c>
       <c r="F283" s="2" t="n">
-        <v>-77.54294184946116</v>
+        <v>-84.27022494055484</v>
       </c>
     </row>
     <row r="284" ht="21" customHeight="1">
@@ -9174,13 +9174,13 @@
         <v>15</v>
       </c>
       <c r="D284" s="2" t="n">
-        <v>1.132321801301813</v>
+        <v>1.33900497911586</v>
       </c>
       <c r="E284" s="2" t="n">
-        <v>16.45292171458144</v>
+        <v>23.18020480567511</v>
       </c>
       <c r="F284" s="2" t="n">
-        <v>-81.19529208430347</v>
+        <v>-87.92257517539716</v>
       </c>
     </row>
     <row r="285" ht="21" customHeight="1">
@@ -9196,13 +9196,13 @@
         <v>20</v>
       </c>
       <c r="D285" s="2" t="n">
-        <v>1.132321801301813</v>
+        <v>1.33900497911586</v>
       </c>
       <c r="E285" s="2" t="n">
-        <v>16.45292171458144</v>
+        <v>23.18020480567511</v>
       </c>
       <c r="F285" s="2" t="n">
-        <v>-84.0297311873116</v>
+        <v>-90.75701427840528</v>
       </c>
     </row>
     <row r="286" ht="21" customHeight="1">
@@ -9218,13 +9218,13 @@
         <v>5</v>
       </c>
       <c r="D286" s="2" t="n">
-        <v>1.276108696705218</v>
+        <v>1.509080524328946</v>
       </c>
       <c r="E286" s="2" t="n">
-        <v>16.59670860998484</v>
+        <v>23.3502803508882</v>
       </c>
       <c r="F286" s="2" t="n">
-        <v>-73.12532909886555</v>
+        <v>-79.8789008397689</v>
       </c>
     </row>
     <row r="287" ht="21" customHeight="1">
@@ -9240,13 +9240,13 @@
         <v>10</v>
       </c>
       <c r="D287" s="2" t="n">
-        <v>1.276108696705218</v>
+        <v>1.509080524328946</v>
       </c>
       <c r="E287" s="2" t="n">
-        <v>16.59670860998484</v>
+        <v>23.3502803508882</v>
       </c>
       <c r="F287" s="2" t="n">
-        <v>-77.78089721904573</v>
+        <v>-84.53446895994908</v>
       </c>
     </row>
     <row r="288" ht="21" customHeight="1">
@@ -9262,13 +9262,13 @@
         <v>15</v>
       </c>
       <c r="D288" s="2" t="n">
-        <v>1.276108696705218</v>
+        <v>1.509080524328946</v>
       </c>
       <c r="E288" s="2" t="n">
-        <v>16.59670860998484</v>
+        <v>23.3502803508882</v>
       </c>
       <c r="F288" s="2" t="n">
-        <v>-81.43324745388804</v>
+        <v>-88.1868191947914</v>
       </c>
     </row>
     <row r="289" ht="21" customHeight="1">
@@ -9284,13 +9284,13 @@
         <v>20</v>
       </c>
       <c r="D289" s="2" t="n">
-        <v>1.276108696705218</v>
+        <v>1.509080524328946</v>
       </c>
       <c r="E289" s="2" t="n">
-        <v>16.59670860998484</v>
+        <v>23.3502803508882</v>
       </c>
       <c r="F289" s="2" t="n">
-        <v>-84.26768655689618</v>
+        <v>-91.02125829779953</v>
       </c>
     </row>
     <row r="290" ht="21" customHeight="1">
@@ -9309,10 +9309,10 @@
         <v>2.421786435898717</v>
       </c>
       <c r="E290" s="2" t="n">
-        <v>24.26298626245797</v>
+        <v>21.25268630581816</v>
       </c>
       <c r="F290" s="2" t="n">
-        <v>-80.60788985062825</v>
+        <v>-77.59758989398844</v>
       </c>
     </row>
     <row r="291" ht="21" customHeight="1">
@@ -9331,10 +9331,10 @@
         <v>2.421786435898717</v>
       </c>
       <c r="E291" s="2" t="n">
-        <v>24.26298626245797</v>
+        <v>21.25268630581816</v>
       </c>
       <c r="F291" s="2" t="n">
-        <v>-85.26345797080843</v>
+        <v>-82.25315801416862</v>
       </c>
     </row>
     <row r="292" ht="21" customHeight="1">
@@ -9353,10 +9353,10 @@
         <v>2.421786435898717</v>
       </c>
       <c r="E292" s="2" t="n">
-        <v>24.26298626245797</v>
+        <v>21.25268630581816</v>
       </c>
       <c r="F292" s="2" t="n">
-        <v>-88.91580820565075</v>
+        <v>-85.90550824901094</v>
       </c>
     </row>
     <row r="293" ht="21" customHeight="1">
@@ -9375,10 +9375,10 @@
         <v>2.421786435898717</v>
       </c>
       <c r="E293" s="2" t="n">
-        <v>24.26298626245797</v>
+        <v>21.25268630581816</v>
       </c>
       <c r="F293" s="2" t="n">
-        <v>-91.75024730865887</v>
+        <v>-88.73994735201906</v>
       </c>
     </row>
     <row r="294" ht="21" customHeight="1">
@@ -9397,10 +9397,10 @@
         <v>2.635694024341009</v>
       </c>
       <c r="E294" s="2" t="n">
-        <v>24.47689385090026</v>
+        <v>21.46659389426045</v>
       </c>
       <c r="F294" s="2" t="n">
-        <v>-80.9113458655998</v>
+        <v>-77.90104590895999</v>
       </c>
     </row>
     <row r="295" ht="21" customHeight="1">
@@ -9419,10 +9419,10 @@
         <v>2.635694024341009</v>
       </c>
       <c r="E295" s="2" t="n">
-        <v>24.47689385090026</v>
+        <v>21.46659389426045</v>
       </c>
       <c r="F295" s="2" t="n">
-        <v>-85.56691398577999</v>
+        <v>-82.55661402914018</v>
       </c>
     </row>
     <row r="296" ht="21" customHeight="1">
@@ -9441,10 +9441,10 @@
         <v>2.635694024341009</v>
       </c>
       <c r="E296" s="2" t="n">
-        <v>24.47689385090026</v>
+        <v>21.46659389426045</v>
       </c>
       <c r="F296" s="2" t="n">
-        <v>-89.21926422062231</v>
+        <v>-86.20896426398249</v>
       </c>
     </row>
     <row r="297" ht="21" customHeight="1">
@@ -9463,10 +9463,10 @@
         <v>2.635694024341009</v>
       </c>
       <c r="E297" s="2" t="n">
-        <v>24.47689385090026</v>
+        <v>21.46659389426045</v>
       </c>
       <c r="F297" s="2" t="n">
-        <v>-92.05370332363043</v>
+        <v>-89.04340336699062</v>
       </c>
     </row>
     <row r="298" ht="21" customHeight="1">
@@ -9485,10 +9485,10 @@
         <v>2.970395524520421</v>
       </c>
       <c r="E298" s="2" t="n">
-        <v>24.81159535107967</v>
+        <v>21.80129539443986</v>
       </c>
       <c r="F298" s="2" t="n">
-        <v>-81.34021583996038</v>
+        <v>-78.32991588332057</v>
       </c>
     </row>
     <row r="299" ht="21" customHeight="1">
@@ -9507,10 +9507,10 @@
         <v>2.970395524520421</v>
       </c>
       <c r="E299" s="2" t="n">
-        <v>24.81159535107967</v>
+        <v>21.80129539443986</v>
       </c>
       <c r="F299" s="2" t="n">
-        <v>-85.99578396014056</v>
+        <v>-82.98548400350074</v>
       </c>
     </row>
     <row r="300" ht="21" customHeight="1">
@@ -9529,10 +9529,10 @@
         <v>2.970395524520421</v>
       </c>
       <c r="E300" s="2" t="n">
-        <v>24.81159535107967</v>
+        <v>21.80129539443986</v>
       </c>
       <c r="F300" s="2" t="n">
-        <v>-89.64813419498287</v>
+        <v>-86.63783423834306</v>
       </c>
     </row>
     <row r="301" ht="21" customHeight="1">
@@ -9551,10 +9551,10 @@
         <v>2.970395524520421</v>
       </c>
       <c r="E301" s="2" t="n">
-        <v>24.81159535107967</v>
+        <v>21.80129539443986</v>
       </c>
       <c r="F301" s="2" t="n">
-        <v>-92.48257329799101</v>
+        <v>-89.4722733413512</v>
       </c>
     </row>
     <row r="302" ht="21" customHeight="1">
@@ -9570,13 +9570,13 @@
         <v>5</v>
       </c>
       <c r="D302" s="2" t="n">
-        <v>4.418748100526224</v>
+        <v>3.98688641115</v>
       </c>
       <c r="E302" s="2" t="n">
-        <v>23.24964797044566</v>
+        <v>19.30748632442963</v>
       </c>
       <c r="F302" s="2" t="n">
-        <v>-79.59455155861595</v>
+        <v>-75.65238991259992</v>
       </c>
     </row>
     <row r="303" ht="21" customHeight="1">
@@ -9592,13 +9592,13 @@
         <v>10</v>
       </c>
       <c r="D303" s="2" t="n">
-        <v>4.418748100526224</v>
+        <v>3.98688641115</v>
       </c>
       <c r="E303" s="2" t="n">
-        <v>23.24964797044566</v>
+        <v>19.30748632442963</v>
       </c>
       <c r="F303" s="2" t="n">
-        <v>-84.25011967879612</v>
+        <v>-80.30795803278008</v>
       </c>
     </row>
     <row r="304" ht="21" customHeight="1">
@@ -9614,13 +9614,13 @@
         <v>15</v>
       </c>
       <c r="D304" s="2" t="n">
-        <v>4.418748100526224</v>
+        <v>3.98688641115</v>
       </c>
       <c r="E304" s="2" t="n">
-        <v>23.24964797044566</v>
+        <v>19.30748632442963</v>
       </c>
       <c r="F304" s="2" t="n">
-        <v>-87.90246991363844</v>
+        <v>-83.96030826762239</v>
       </c>
     </row>
     <row r="305" ht="21" customHeight="1">
@@ -9636,13 +9636,13 @@
         <v>20</v>
       </c>
       <c r="D305" s="2" t="n">
-        <v>4.418748100526224</v>
+        <v>3.98688641115</v>
       </c>
       <c r="E305" s="2" t="n">
-        <v>23.24964797044566</v>
+        <v>19.30748632442963</v>
       </c>
       <c r="F305" s="2" t="n">
-        <v>-90.73690901664656</v>
+        <v>-86.79474737063052</v>
       </c>
     </row>
     <row r="306" ht="21" customHeight="1">
@@ -9658,13 +9658,13 @@
         <v>5</v>
       </c>
       <c r="D306" s="2" t="n">
-        <v>4.809695787837147</v>
+        <v>4.338895576050001</v>
       </c>
       <c r="E306" s="2" t="n">
-        <v>23.64059565775658</v>
+        <v>19.65949548932963</v>
       </c>
       <c r="F306" s="2" t="n">
-        <v>-80.07504767245612</v>
+        <v>-76.09394750402917</v>
       </c>
     </row>
     <row r="307" ht="21" customHeight="1">
@@ -9680,13 +9680,13 @@
         <v>10</v>
       </c>
       <c r="D307" s="2" t="n">
-        <v>4.809695787837147</v>
+        <v>4.338895576050001</v>
       </c>
       <c r="E307" s="2" t="n">
-        <v>23.64059565775658</v>
+        <v>19.65949548932963</v>
       </c>
       <c r="F307" s="2" t="n">
-        <v>-84.73061579263631</v>
+        <v>-80.74951562420935</v>
       </c>
     </row>
     <row r="308" ht="21" customHeight="1">
@@ -9702,13 +9702,13 @@
         <v>15</v>
       </c>
       <c r="D308" s="2" t="n">
-        <v>4.809695787837147</v>
+        <v>4.338895576050001</v>
       </c>
       <c r="E308" s="2" t="n">
-        <v>23.64059565775658</v>
+        <v>19.65949548932963</v>
       </c>
       <c r="F308" s="2" t="n">
-        <v>-88.38296602747863</v>
+        <v>-84.40186585905167</v>
       </c>
     </row>
     <row r="309" ht="21" customHeight="1">
@@ -9724,13 +9724,13 @@
         <v>20</v>
       </c>
       <c r="D309" s="2" t="n">
-        <v>4.809695787837147</v>
+        <v>4.338895576050001</v>
       </c>
       <c r="E309" s="2" t="n">
-        <v>23.64059565775658</v>
+        <v>19.65949548932963</v>
       </c>
       <c r="F309" s="2" t="n">
-        <v>-91.21740513048675</v>
+        <v>-87.23630496205979</v>
       </c>
     </row>
     <row r="310" ht="21" customHeight="1">
@@ -9746,13 +9746,13 @@
         <v>5</v>
       </c>
       <c r="D310" s="2" t="n">
-        <v>5.420549158763428</v>
+        <v>4.889866442850001</v>
       </c>
       <c r="E310" s="2" t="n">
-        <v>24.25144902868287</v>
+        <v>20.21046635612963</v>
       </c>
       <c r="F310" s="2" t="n">
-        <v>-80.78006951756358</v>
+        <v>-76.73908684501033</v>
       </c>
     </row>
     <row r="311" ht="21" customHeight="1">
@@ -9768,13 +9768,13 @@
         <v>10</v>
       </c>
       <c r="D311" s="2" t="n">
-        <v>5.420549158763428</v>
+        <v>4.889866442850001</v>
       </c>
       <c r="E311" s="2" t="n">
-        <v>24.25144902868287</v>
+        <v>20.21046635612963</v>
       </c>
       <c r="F311" s="2" t="n">
-        <v>-85.43563763774375</v>
+        <v>-81.39465496519051</v>
       </c>
     </row>
     <row r="312" ht="21" customHeight="1">
@@ -9790,13 +9790,13 @@
         <v>15</v>
       </c>
       <c r="D312" s="2" t="n">
-        <v>5.420549158763428</v>
+        <v>4.889866442850001</v>
       </c>
       <c r="E312" s="2" t="n">
-        <v>24.25144902868287</v>
+        <v>20.21046635612963</v>
       </c>
       <c r="F312" s="2" t="n">
-        <v>-89.08798787258607</v>
+        <v>-85.04700520003283</v>
       </c>
     </row>
     <row r="313" ht="21" customHeight="1">
@@ -9812,13 +9812,13 @@
         <v>20</v>
       </c>
       <c r="D313" s="2" t="n">
-        <v>5.420549158763428</v>
+        <v>4.889866442850001</v>
       </c>
       <c r="E313" s="2" t="n">
-        <v>24.25144902868287</v>
+        <v>20.21046635612963</v>
       </c>
       <c r="F313" s="2" t="n">
-        <v>-91.92242697559421</v>
+        <v>-87.88144430304096</v>
       </c>
     </row>
     <row r="314" ht="21" customHeight="1">
@@ -9834,13 +9834,13 @@
         <v>5</v>
       </c>
       <c r="D314" s="2" t="n">
-        <v>2.498696569064261</v>
+        <v>1.869650025018349</v>
       </c>
       <c r="E314" s="2" t="n">
-        <v>17.81929648234389</v>
+        <v>17.19024993829797</v>
       </c>
       <c r="F314" s="2" t="n">
-        <v>-74.16420007051417</v>
+        <v>-73.53515352646826</v>
       </c>
     </row>
     <row r="315" ht="21" customHeight="1">
@@ -9856,13 +9856,13 @@
         <v>10</v>
       </c>
       <c r="D315" s="2" t="n">
-        <v>2.498696569064261</v>
+        <v>1.869650025018349</v>
       </c>
       <c r="E315" s="2" t="n">
-        <v>17.81929648234389</v>
+        <v>17.19024993829797</v>
       </c>
       <c r="F315" s="2" t="n">
-        <v>-78.81976819069435</v>
+        <v>-78.19072164664843</v>
       </c>
     </row>
     <row r="316" ht="21" customHeight="1">
@@ -9878,13 +9878,13 @@
         <v>15</v>
       </c>
       <c r="D316" s="2" t="n">
-        <v>2.498696569064261</v>
+        <v>1.869650025018349</v>
       </c>
       <c r="E316" s="2" t="n">
-        <v>17.81929648234389</v>
+        <v>17.19024993829797</v>
       </c>
       <c r="F316" s="2" t="n">
-        <v>-82.47211842553666</v>
+        <v>-81.84307188149074</v>
       </c>
     </row>
     <row r="317" ht="21" customHeight="1">
@@ -9900,13 +9900,13 @@
         <v>20</v>
       </c>
       <c r="D317" s="2" t="n">
-        <v>2.498696569064261</v>
+        <v>1.869650025018349</v>
       </c>
       <c r="E317" s="2" t="n">
-        <v>17.81929648234389</v>
+        <v>17.19024993829797</v>
       </c>
       <c r="F317" s="2" t="n">
-        <v>-85.30655752854479</v>
+        <v>-84.67751098449887</v>
       </c>
     </row>
     <row r="318" ht="21" customHeight="1">
@@ -9922,13 +9922,13 @@
         <v>5</v>
       </c>
       <c r="D318" s="2" t="n">
-        <v>2.719892863392689</v>
+        <v>2.03495609605998</v>
       </c>
       <c r="E318" s="2" t="n">
-        <v>18.04049277667232</v>
+        <v>17.3555560093396</v>
       </c>
       <c r="F318" s="2" t="n">
-        <v>-74.47494479137185</v>
+        <v>-73.79000802403915</v>
       </c>
     </row>
     <row r="319" ht="21" customHeight="1">
@@ -9944,13 +9944,13 @@
         <v>10</v>
       </c>
       <c r="D319" s="2" t="n">
-        <v>2.719892863392689</v>
+        <v>2.03495609605998</v>
       </c>
       <c r="E319" s="2" t="n">
-        <v>18.04049277667232</v>
+        <v>17.3555560093396</v>
       </c>
       <c r="F319" s="2" t="n">
-        <v>-79.13051291155205</v>
+        <v>-78.44557614421933</v>
       </c>
     </row>
     <row r="320" ht="21" customHeight="1">
@@ -9966,13 +9966,13 @@
         <v>15</v>
       </c>
       <c r="D320" s="2" t="n">
-        <v>2.719892863392689</v>
+        <v>2.03495609605998</v>
       </c>
       <c r="E320" s="2" t="n">
-        <v>18.04049277667232</v>
+        <v>17.3555560093396</v>
       </c>
       <c r="F320" s="2" t="n">
-        <v>-82.78286314639436</v>
+        <v>-82.09792637906165</v>
       </c>
     </row>
     <row r="321" ht="21" customHeight="1">
@@ -9988,13 +9988,13 @@
         <v>20</v>
       </c>
       <c r="D321" s="2" t="n">
-        <v>2.719892863392689</v>
+        <v>2.03495609605998</v>
       </c>
       <c r="E321" s="2" t="n">
-        <v>18.04049277667232</v>
+        <v>17.3555560093396</v>
       </c>
       <c r="F321" s="2" t="n">
-        <v>-85.61730224940248</v>
+        <v>-84.93236548206977</v>
       </c>
     </row>
     <row r="322" ht="21" customHeight="1">
@@ -10010,13 +10010,13 @@
         <v>5</v>
       </c>
       <c r="D322" s="2" t="n">
-        <v>3.065346865459397</v>
+        <v>2.293391361727224</v>
       </c>
       <c r="E322" s="2" t="n">
-        <v>18.38594677873902</v>
+        <v>17.61399127500685</v>
       </c>
       <c r="F322" s="2" t="n">
-        <v>-74.91456726761973</v>
+        <v>-74.14261176388756</v>
       </c>
     </row>
     <row r="323" ht="21" customHeight="1">
@@ -10032,13 +10032,13 @@
         <v>10</v>
       </c>
       <c r="D323" s="2" t="n">
-        <v>3.065346865459397</v>
+        <v>2.293391361727224</v>
       </c>
       <c r="E323" s="2" t="n">
-        <v>18.38594677873902</v>
+        <v>17.61399127500685</v>
       </c>
       <c r="F323" s="2" t="n">
-        <v>-79.57013538779991</v>
+        <v>-78.79817988406774</v>
       </c>
     </row>
     <row r="324" ht="21" customHeight="1">
@@ -10054,13 +10054,13 @@
         <v>15</v>
       </c>
       <c r="D324" s="2" t="n">
-        <v>3.065346865459397</v>
+        <v>2.293391361727224</v>
       </c>
       <c r="E324" s="2" t="n">
-        <v>18.38594677873902</v>
+        <v>17.61399127500685</v>
       </c>
       <c r="F324" s="2" t="n">
-        <v>-83.22248562264222</v>
+        <v>-82.45053011891005</v>
       </c>
     </row>
     <row r="325" ht="21" customHeight="1">
@@ -10076,13 +10076,13 @@
         <v>20</v>
       </c>
       <c r="D325" s="2" t="n">
-        <v>3.065346865459397</v>
+        <v>2.293391361727224</v>
       </c>
       <c r="E325" s="2" t="n">
-        <v>18.38594677873902</v>
+        <v>17.61399127500685</v>
       </c>
       <c r="F325" s="2" t="n">
-        <v>-86.05692472565036</v>
+        <v>-85.28496922191819</v>
       </c>
     </row>
     <row r="326" ht="21" customHeight="1">
@@ -10098,13 +10098,13 @@
         <v>5</v>
       </c>
       <c r="D326" s="2" t="n">
-        <v>5.827441257903809</v>
+        <v>4.99881072399825</v>
       </c>
       <c r="E326" s="2" t="n">
-        <v>27.66864108446306</v>
+        <v>26.8400105505575</v>
       </c>
       <c r="F326" s="2" t="n">
-        <v>-84.01354467263334</v>
+        <v>-83.18491413872778</v>
       </c>
     </row>
     <row r="327" ht="21" customHeight="1">
@@ -10120,13 +10120,13 @@
         <v>10</v>
       </c>
       <c r="D327" s="2" t="n">
-        <v>5.827441257903809</v>
+        <v>4.99881072399825</v>
       </c>
       <c r="E327" s="2" t="n">
-        <v>27.66864108446306</v>
+        <v>26.8400105505575</v>
       </c>
       <c r="F327" s="2" t="n">
-        <v>-88.66911279281352</v>
+        <v>-87.84048225890797</v>
       </c>
     </row>
     <row r="328" ht="21" customHeight="1">
@@ -10142,13 +10142,13 @@
         <v>15</v>
       </c>
       <c r="D328" s="2" t="n">
-        <v>5.827441257903809</v>
+        <v>4.99881072399825</v>
       </c>
       <c r="E328" s="2" t="n">
-        <v>27.66864108446306</v>
+        <v>26.8400105505575</v>
       </c>
       <c r="F328" s="2" t="n">
-        <v>-92.32146302765584</v>
+        <v>-91.49283249375029</v>
       </c>
     </row>
     <row r="329" ht="21" customHeight="1">
@@ -10164,13 +10164,13 @@
         <v>20</v>
       </c>
       <c r="D329" s="2" t="n">
-        <v>5.827441257903809</v>
+        <v>4.99881072399825</v>
       </c>
       <c r="E329" s="2" t="n">
-        <v>27.66864108446306</v>
+        <v>26.8400105505575</v>
       </c>
       <c r="F329" s="2" t="n">
-        <v>-95.15590213066396</v>
+        <v>-94.32727159675841</v>
       </c>
     </row>
     <row r="330" ht="21" customHeight="1">
@@ -10186,13 +10186,13 @@
         <v>5</v>
       </c>
       <c r="D330" s="2" t="n">
-        <v>6.341956225012398</v>
+        <v>5.440164453948192</v>
       </c>
       <c r="E330" s="2" t="n">
-        <v>28.18315605157165</v>
+        <v>27.28136428050744</v>
       </c>
       <c r="F330" s="2" t="n">
-        <v>-84.6176080662712</v>
+        <v>-83.71581629520699</v>
       </c>
     </row>
     <row r="331" ht="21" customHeight="1">
@@ -10208,13 +10208,13 @@
         <v>10</v>
       </c>
       <c r="D331" s="2" t="n">
-        <v>6.341956225012398</v>
+        <v>5.440164453948192</v>
       </c>
       <c r="E331" s="2" t="n">
-        <v>28.18315605157165</v>
+        <v>27.28136428050744</v>
       </c>
       <c r="F331" s="2" t="n">
-        <v>-89.27317618645137</v>
+        <v>-88.37138441538717</v>
       </c>
     </row>
     <row r="332" ht="21" customHeight="1">
@@ -10230,13 +10230,13 @@
         <v>15</v>
       </c>
       <c r="D332" s="2" t="n">
-        <v>6.341956225012398</v>
+        <v>5.440164453948192</v>
       </c>
       <c r="E332" s="2" t="n">
-        <v>28.18315605157165</v>
+        <v>27.28136428050744</v>
       </c>
       <c r="F332" s="2" t="n">
-        <v>-92.92552642129368</v>
+        <v>-92.02373465022949</v>
       </c>
     </row>
     <row r="333" ht="21" customHeight="1">
@@ -10252,13 +10252,13 @@
         <v>20</v>
       </c>
       <c r="D333" s="2" t="n">
-        <v>6.341956225012398</v>
+        <v>5.440164453948192</v>
       </c>
       <c r="E333" s="2" t="n">
-        <v>28.18315605157165</v>
+        <v>27.28136428050744</v>
       </c>
       <c r="F333" s="2" t="n">
-        <v>-95.7599655243018</v>
+        <v>-94.85817375323761</v>
       </c>
     </row>
     <row r="334" ht="21" customHeight="1">
@@ -10274,13 +10274,13 @@
         <v>5</v>
       </c>
       <c r="D334" s="2" t="n">
-        <v>7.147283999617145</v>
+        <v>6.130978987782884</v>
       </c>
       <c r="E334" s="2" t="n">
-        <v>28.9884838261764</v>
+        <v>27.97217881434214</v>
       </c>
       <c r="F334" s="2" t="n">
-        <v>-85.5171043150571</v>
+        <v>-84.50079930322283</v>
       </c>
     </row>
     <row r="335" ht="21" customHeight="1">
@@ -10296,13 +10296,13 @@
         <v>10</v>
       </c>
       <c r="D335" s="2" t="n">
-        <v>7.147283999617145</v>
+        <v>6.130978987782884</v>
       </c>
       <c r="E335" s="2" t="n">
-        <v>28.9884838261764</v>
+        <v>27.97217881434214</v>
       </c>
       <c r="F335" s="2" t="n">
-        <v>-90.17267243523727</v>
+        <v>-89.15636742340303</v>
       </c>
     </row>
     <row r="336" ht="21" customHeight="1">
@@ -10318,13 +10318,13 @@
         <v>15</v>
       </c>
       <c r="D336" s="2" t="n">
-        <v>7.147283999617145</v>
+        <v>6.130978987782884</v>
       </c>
       <c r="E336" s="2" t="n">
-        <v>28.9884838261764</v>
+        <v>27.97217881434214</v>
       </c>
       <c r="F336" s="2" t="n">
-        <v>-93.82502267007959</v>
+        <v>-92.80871765824534</v>
       </c>
     </row>
     <row r="337" ht="21" customHeight="1">
@@ -10340,13 +10340,13 @@
         <v>20</v>
       </c>
       <c r="D337" s="2" t="n">
-        <v>7.147283999617145</v>
+        <v>6.130978987782884</v>
       </c>
       <c r="E337" s="2" t="n">
-        <v>28.9884838261764</v>
+        <v>27.97217881434214</v>
       </c>
       <c r="F337" s="2" t="n">
-        <v>-96.65946177308773</v>
+        <v>-95.64315676125346</v>
       </c>
     </row>
     <row r="338" ht="21" customHeight="1">
@@ -10626,13 +10626,13 @@
         <v>5</v>
       </c>
       <c r="D350" s="2" t="n">
-        <v>3.957309006044786</v>
+        <v>3.74852842909125</v>
       </c>
       <c r="E350" s="2" t="n">
-        <v>22.78820887596422</v>
+        <v>25.5897282556505</v>
       </c>
       <c r="F350" s="2" t="n">
-        <v>-79.13311246413451</v>
+        <v>-81.93463184382078</v>
       </c>
     </row>
     <row r="351" ht="21" customHeight="1">
@@ -10648,13 +10648,13 @@
         <v>10</v>
       </c>
       <c r="D351" s="2" t="n">
-        <v>3.957309006044786</v>
+        <v>3.74852842909125</v>
       </c>
       <c r="E351" s="2" t="n">
-        <v>22.78820887596422</v>
+        <v>25.5897282556505</v>
       </c>
       <c r="F351" s="2" t="n">
-        <v>-83.78868058431468</v>
+        <v>-86.59019996400096</v>
       </c>
     </row>
     <row r="352" ht="21" customHeight="1">
@@ -10670,13 +10670,13 @@
         <v>15</v>
       </c>
       <c r="D352" s="2" t="n">
-        <v>3.957309006044786</v>
+        <v>3.74852842909125</v>
       </c>
       <c r="E352" s="2" t="n">
-        <v>22.78820887596422</v>
+        <v>25.5897282556505</v>
       </c>
       <c r="F352" s="2" t="n">
-        <v>-87.44103081915699</v>
+        <v>-90.24255019884328</v>
       </c>
     </row>
     <row r="353" ht="21" customHeight="1">
@@ -10692,13 +10692,13 @@
         <v>20</v>
       </c>
       <c r="D353" s="2" t="n">
-        <v>3.957309006044786</v>
+        <v>3.74852842909125</v>
       </c>
       <c r="E353" s="2" t="n">
-        <v>22.78820887596422</v>
+        <v>25.5897282556505</v>
       </c>
       <c r="F353" s="2" t="n">
-        <v>-90.27546992216512</v>
+        <v>-93.0769893018514</v>
       </c>
     </row>
     <row r="354" ht="21" customHeight="1">
@@ -10714,13 +10714,13 @@
         <v>5</v>
       </c>
       <c r="D354" s="2" t="n">
-        <v>4.307097606632885</v>
+        <v>4.079492551429442</v>
       </c>
       <c r="E354" s="2" t="n">
-        <v>23.13799747655232</v>
+        <v>25.92069237798869</v>
       </c>
       <c r="F354" s="2" t="n">
-        <v>-79.57244949125186</v>
+        <v>-82.35514439268823</v>
       </c>
     </row>
     <row r="355" ht="21" customHeight="1">
@@ -10736,13 +10736,13 @@
         <v>10</v>
       </c>
       <c r="D355" s="2" t="n">
-        <v>4.307097606632885</v>
+        <v>4.079492551429442</v>
       </c>
       <c r="E355" s="2" t="n">
-        <v>23.13799747655232</v>
+        <v>25.92069237798869</v>
       </c>
       <c r="F355" s="2" t="n">
-        <v>-84.22801761143205</v>
+        <v>-87.01071251286842</v>
       </c>
     </row>
     <row r="356" ht="21" customHeight="1">
@@ -10758,13 +10758,13 @@
         <v>15</v>
       </c>
       <c r="D356" s="2" t="n">
-        <v>4.307097606632885</v>
+        <v>4.079492551429442</v>
       </c>
       <c r="E356" s="2" t="n">
-        <v>23.13799747655232</v>
+        <v>25.92069237798869</v>
       </c>
       <c r="F356" s="2" t="n">
-        <v>-87.88036784627437</v>
+        <v>-90.66306274771074</v>
       </c>
     </row>
     <row r="357" ht="21" customHeight="1">
@@ -10780,13 +10780,13 @@
         <v>20</v>
       </c>
       <c r="D357" s="2" t="n">
-        <v>4.307097606632885</v>
+        <v>4.079492551429442</v>
       </c>
       <c r="E357" s="2" t="n">
-        <v>23.13799747655232</v>
+        <v>25.92069237798869</v>
       </c>
       <c r="F357" s="2" t="n">
-        <v>-90.71480694928249</v>
+        <v>-93.49750185071886</v>
       </c>
     </row>
     <row r="358" ht="21" customHeight="1">
@@ -10802,13 +10802,13 @@
         <v>5</v>
       </c>
       <c r="D358" s="2" t="n">
-        <v>4.854078172607822</v>
+        <v>4.597523351610957</v>
       </c>
       <c r="E358" s="2" t="n">
-        <v>23.68497804252726</v>
+        <v>26.43872317817021</v>
       </c>
       <c r="F358" s="2" t="n">
-        <v>-80.21359853140797</v>
+        <v>-82.96734366705091</v>
       </c>
     </row>
     <row r="359" ht="21" customHeight="1">
@@ -10824,13 +10824,13 @@
         <v>10</v>
       </c>
       <c r="D359" s="2" t="n">
-        <v>4.854078172607822</v>
+        <v>4.597523351610957</v>
       </c>
       <c r="E359" s="2" t="n">
-        <v>23.68497804252726</v>
+        <v>26.43872317817021</v>
       </c>
       <c r="F359" s="2" t="n">
-        <v>-84.86916665158815</v>
+        <v>-87.62291178723109</v>
       </c>
     </row>
     <row r="360" ht="21" customHeight="1">
@@ -10846,13 +10846,13 @@
         <v>15</v>
       </c>
       <c r="D360" s="2" t="n">
-        <v>4.854078172607822</v>
+        <v>4.597523351610957</v>
       </c>
       <c r="E360" s="2" t="n">
-        <v>23.68497804252726</v>
+        <v>26.43872317817021</v>
       </c>
       <c r="F360" s="2" t="n">
-        <v>-88.52151688643046</v>
+        <v>-91.27526202207341</v>
       </c>
     </row>
     <row r="361" ht="21" customHeight="1">
@@ -10868,13 +10868,13 @@
         <v>20</v>
       </c>
       <c r="D361" s="2" t="n">
-        <v>4.854078172607822</v>
+        <v>4.597523351610957</v>
       </c>
       <c r="E361" s="2" t="n">
-        <v>23.68497804252726</v>
+        <v>26.43872317817021</v>
       </c>
       <c r="F361" s="2" t="n">
-        <v>-91.3559559894386</v>
+        <v>-94.10970112508154</v>
       </c>
     </row>
     <row r="362" ht="21" customHeight="1">
@@ -10890,13 +10890,13 @@
         <v>5</v>
       </c>
       <c r="D362" s="2" t="n">
-        <v>1.975539099613481</v>
+        <v>1.9215713053</v>
       </c>
       <c r="E362" s="2" t="n">
-        <v>17.29613901289311</v>
+        <v>23.76277113185925</v>
       </c>
       <c r="F362" s="2" t="n">
-        <v>-73.64104260106339</v>
+        <v>-80.10767472002954</v>
       </c>
     </row>
     <row r="363" ht="21" customHeight="1">
@@ -10912,13 +10912,13 @@
         <v>10</v>
       </c>
       <c r="D363" s="2" t="n">
-        <v>1.975539099613481</v>
+        <v>1.9215713053</v>
       </c>
       <c r="E363" s="2" t="n">
-        <v>17.29613901289311</v>
+        <v>23.76277113185925</v>
       </c>
       <c r="F363" s="2" t="n">
-        <v>-78.29661072124357</v>
+        <v>-84.76324284020971</v>
       </c>
     </row>
     <row r="364" ht="21" customHeight="1">
@@ -10934,13 +10934,13 @@
         <v>15</v>
       </c>
       <c r="D364" s="2" t="n">
-        <v>1.975539099613481</v>
+        <v>1.9215713053</v>
       </c>
       <c r="E364" s="2" t="n">
-        <v>17.29613901289311</v>
+        <v>23.76277113185925</v>
       </c>
       <c r="F364" s="2" t="n">
-        <v>-81.94896095608588</v>
+        <v>-88.41559307505203</v>
       </c>
     </row>
     <row r="365" ht="21" customHeight="1">
@@ -10956,13 +10956,13 @@
         <v>20</v>
       </c>
       <c r="D365" s="2" t="n">
-        <v>1.975539099613481</v>
+        <v>1.9215713053</v>
       </c>
       <c r="E365" s="2" t="n">
-        <v>17.29613901289311</v>
+        <v>23.76277113185925</v>
       </c>
       <c r="F365" s="2" t="n">
-        <v>-84.78340005909401</v>
+        <v>-91.25003217806015</v>
       </c>
     </row>
     <row r="366" ht="21" customHeight="1">
@@ -10978,13 +10978,13 @@
         <v>5</v>
       </c>
       <c r="D366" s="2" t="n">
-        <v>2.15007119944184</v>
+        <v>2.0912362457</v>
       </c>
       <c r="E366" s="2" t="n">
-        <v>17.47067111272147</v>
+        <v>23.93243607225925</v>
       </c>
       <c r="F366" s="2" t="n">
-        <v>-73.90512312742101</v>
+        <v>-80.3668880869588</v>
       </c>
     </row>
     <row r="367" ht="21" customHeight="1">
@@ -11000,13 +11000,13 @@
         <v>10</v>
       </c>
       <c r="D367" s="2" t="n">
-        <v>2.15007119944184</v>
+        <v>2.0912362457</v>
       </c>
       <c r="E367" s="2" t="n">
-        <v>17.47067111272147</v>
+        <v>23.93243607225925</v>
       </c>
       <c r="F367" s="2" t="n">
-        <v>-78.56069124760118</v>
+        <v>-85.02245620713897</v>
       </c>
     </row>
     <row r="368" ht="21" customHeight="1">
@@ -11022,13 +11022,13 @@
         <v>15</v>
       </c>
       <c r="D368" s="2" t="n">
-        <v>2.15007119944184</v>
+        <v>2.0912362457</v>
       </c>
       <c r="E368" s="2" t="n">
-        <v>17.47067111272147</v>
+        <v>23.93243607225925</v>
       </c>
       <c r="F368" s="2" t="n">
-        <v>-82.2130414824435</v>
+        <v>-88.67480644198129</v>
       </c>
     </row>
     <row r="369" ht="21" customHeight="1">
@@ -11044,13 +11044,13 @@
         <v>20</v>
       </c>
       <c r="D369" s="2" t="n">
-        <v>2.15007119944184</v>
+        <v>2.0912362457</v>
       </c>
       <c r="E369" s="2" t="n">
-        <v>17.47067111272147</v>
+        <v>23.93243607225925</v>
       </c>
       <c r="F369" s="2" t="n">
-        <v>-85.04748058545162</v>
+        <v>-91.50924554498941</v>
       </c>
     </row>
     <row r="370" ht="21" customHeight="1">
@@ -11066,13 +11066,13 @@
         <v>5</v>
       </c>
       <c r="D370" s="2" t="n">
-        <v>2.42310928485844</v>
+        <v>2.356790790883333</v>
       </c>
       <c r="E370" s="2" t="n">
-        <v>17.74370919813807</v>
+        <v>24.19799061744258</v>
       </c>
       <c r="F370" s="2" t="n">
-        <v>-74.27232968701877</v>
+        <v>-80.72661110632329</v>
       </c>
     </row>
     <row r="371" ht="21" customHeight="1">
@@ -11088,13 +11088,13 @@
         <v>10</v>
       </c>
       <c r="D371" s="2" t="n">
-        <v>2.42310928485844</v>
+        <v>2.356790790883333</v>
       </c>
       <c r="E371" s="2" t="n">
-        <v>17.74370919813807</v>
+        <v>24.19799061744258</v>
       </c>
       <c r="F371" s="2" t="n">
-        <v>-78.92789780719895</v>
+        <v>-85.38217922650347</v>
       </c>
     </row>
     <row r="372" ht="21" customHeight="1">
@@ -11110,13 +11110,13 @@
         <v>15</v>
       </c>
       <c r="D372" s="2" t="n">
-        <v>2.42310928485844</v>
+        <v>2.356790790883333</v>
       </c>
       <c r="E372" s="2" t="n">
-        <v>17.74370919813807</v>
+        <v>24.19799061744258</v>
       </c>
       <c r="F372" s="2" t="n">
-        <v>-82.58024804204126</v>
+        <v>-89.03452946134578</v>
       </c>
     </row>
     <row r="373" ht="21" customHeight="1">
@@ -11132,13 +11132,13 @@
         <v>20</v>
       </c>
       <c r="D373" s="2" t="n">
-        <v>2.42310928485844</v>
+        <v>2.356790790883333</v>
       </c>
       <c r="E373" s="2" t="n">
-        <v>17.74370919813807</v>
+        <v>24.19799061744258</v>
       </c>
       <c r="F373" s="2" t="n">
-        <v>-85.4146871450494</v>
+        <v>-91.86896856435392</v>
       </c>
     </row>
     <row r="374" ht="21" customHeight="1">
@@ -11157,10 +11157,10 @@
         <v>3.991097726204553</v>
       </c>
       <c r="E374" s="2" t="n">
-        <v>25.83229755276381</v>
+        <v>22.82199759612399</v>
       </c>
       <c r="F374" s="2" t="n">
-        <v>-82.17720114093409</v>
+        <v>-79.16690118429428</v>
       </c>
     </row>
     <row r="375" ht="21" customHeight="1">
@@ -11179,10 +11179,10 @@
         <v>3.991097726204553</v>
       </c>
       <c r="E375" s="2" t="n">
-        <v>25.83229755276381</v>
+        <v>22.82199759612399</v>
       </c>
       <c r="F375" s="2" t="n">
-        <v>-86.83276926111427</v>
+        <v>-83.82246930447445</v>
       </c>
     </row>
     <row r="376" ht="21" customHeight="1">
@@ -11201,10 +11201,10 @@
         <v>3.991097726204553</v>
       </c>
       <c r="E376" s="2" t="n">
-        <v>25.83229755276381</v>
+        <v>22.82199759612399</v>
       </c>
       <c r="F376" s="2" t="n">
-        <v>-90.48511949595658</v>
+        <v>-87.47481953931677</v>
       </c>
     </row>
     <row r="377" ht="21" customHeight="1">
@@ -11223,10 +11223,10 @@
         <v>3.991097726204553</v>
       </c>
       <c r="E377" s="2" t="n">
-        <v>25.83229755276381</v>
+        <v>22.82199759612399</v>
       </c>
       <c r="F377" s="2" t="n">
-        <v>-93.3195585989647</v>
+        <v>-90.30925864232489</v>
       </c>
     </row>
     <row r="378" ht="21" customHeight="1">
@@ -11245,10 +11245,10 @@
         <v>4.343478715466376</v>
       </c>
       <c r="E378" s="2" t="n">
-        <v>26.18467854202563</v>
+        <v>23.17437858538581</v>
       </c>
       <c r="F378" s="2" t="n">
-        <v>-82.61913055672517</v>
+        <v>-79.60883060008535</v>
       </c>
     </row>
     <row r="379" ht="21" customHeight="1">
@@ -11267,10 +11267,10 @@
         <v>4.343478715466376</v>
       </c>
       <c r="E379" s="2" t="n">
-        <v>26.18467854202563</v>
+        <v>23.17437858538581</v>
       </c>
       <c r="F379" s="2" t="n">
-        <v>-87.27469867690534</v>
+        <v>-84.26439872026553</v>
       </c>
     </row>
     <row r="380" ht="21" customHeight="1">
@@ -11289,10 +11289,10 @@
         <v>4.343478715466376</v>
       </c>
       <c r="E380" s="2" t="n">
-        <v>26.18467854202563</v>
+        <v>23.17437858538581</v>
       </c>
       <c r="F380" s="2" t="n">
-        <v>-90.92704891174766</v>
+        <v>-87.91674895510785</v>
       </c>
     </row>
     <row r="381" ht="21" customHeight="1">
@@ -11311,10 +11311,10 @@
         <v>4.343478715466376</v>
       </c>
       <c r="E381" s="2" t="n">
-        <v>26.18467854202563</v>
+        <v>23.17437858538581</v>
       </c>
       <c r="F381" s="2" t="n">
-        <v>-93.76148801475578</v>
+        <v>-90.75118805811597</v>
       </c>
     </row>
     <row r="382" ht="21" customHeight="1">
@@ -11333,10 +11333,10 @@
         <v>4.89503156822401</v>
       </c>
       <c r="E382" s="2" t="n">
-        <v>26.73623139478326</v>
+        <v>23.72593143814345</v>
       </c>
       <c r="F382" s="2" t="n">
-        <v>-83.26485188366397</v>
+        <v>-80.25455192702415</v>
       </c>
     </row>
     <row r="383" ht="21" customHeight="1">
@@ -11355,10 +11355,10 @@
         <v>4.89503156822401</v>
       </c>
       <c r="E383" s="2" t="n">
-        <v>26.73623139478326</v>
+        <v>23.72593143814345</v>
       </c>
       <c r="F383" s="2" t="n">
-        <v>-87.92042000384414</v>
+        <v>-84.91012004720433</v>
       </c>
     </row>
     <row r="384" ht="21" customHeight="1">
@@ -11377,10 +11377,10 @@
         <v>4.89503156822401</v>
       </c>
       <c r="E384" s="2" t="n">
-        <v>26.73623139478326</v>
+        <v>23.72593143814345</v>
       </c>
       <c r="F384" s="2" t="n">
-        <v>-91.57277023868646</v>
+        <v>-88.56247028204665</v>
       </c>
     </row>
     <row r="385" ht="21" customHeight="1">
@@ -11399,10 +11399,10 @@
         <v>4.89503156822401</v>
       </c>
       <c r="E385" s="2" t="n">
-        <v>26.73623139478326</v>
+        <v>23.72593143814345</v>
       </c>
       <c r="F385" s="2" t="n">
-        <v>-94.4072093416946</v>
+        <v>-91.39690938505478</v>
       </c>
     </row>
   </sheetData>
@@ -11419,7 +11419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -11496,16 +11496,16 @@
         <v>32</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>2027.698772162835</v>
+        <v>2028.297243789426</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>96.55708438870644</v>
+        <v>96.58558303759173</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>98.96832260440748</v>
+        <v>98.9974910516087</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>-141.3734294869009</v>
+        <v>-140.3406708132619</v>
       </c>
       <c r="I2" s="2" t="b">
         <v>1</v>
@@ -11527,16 +11527,16 @@
         <v>32</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>2036.812310873982</v>
+        <v>2032.759371978508</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>96.99106242257058</v>
+        <v>96.79806533230992</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>99.33915649590762</v>
+        <v>99.19037761212888</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>-136.5695354439322</v>
+        <v>-135.7500870119923</v>
       </c>
       <c r="I3" s="2" t="b">
         <v>1</v>
@@ -11558,25 +11558,25 @@
         <v>32</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1938.053628964273</v>
+        <v>2026.081796222425</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>92.28826804591776</v>
+        <v>96.48008553440121</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>94.67743292921254</v>
+        <v>98.89006734706808</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>-146.1773235298697</v>
+        <v>-144.9312584292286</v>
       </c>
       <c r="I4" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" ht="21" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>P1_extra_RF_3dB</t>
+          <t>P1_n3_closed_gaps</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -11589,16 +11589,16 @@
         <v>32</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>2027.088015409037</v>
+        <v>2018.511075508131</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>96.52800073376365</v>
+        <v>96.11957502419672</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>98.93914449718068</v>
+        <v>98.54314362885191</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>-144.3734294869009</v>
+        <v>-144.9312584292286</v>
       </c>
       <c r="I5" s="2" t="b">
         <v>1</v>
@@ -11607,7 +11607,7 @@
     <row r="6" ht="21" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>P1_closed_gaps</t>
+          <t>P1_extra_RF_3dB</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -11620,16 +11620,16 @@
         <v>32</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2023.569410846496</v>
+        <v>2027.370972447764</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>96.36044813554744</v>
+        <v>96.54147487846497</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>98.78658049338374</v>
+        <v>98.95163974025233</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>-141.5230365047649</v>
+        <v>-143.3406708132619</v>
       </c>
       <c r="I6" s="2" t="b">
         <v>1</v>
@@ -11638,7 +11638,7 @@
     <row r="7" ht="21" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>P1_two_ports_total</t>
+          <t>P1_closed_gaps</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -11651,16 +11651,16 @@
         <v>32</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>2027.088015409037</v>
+        <v>2024.273583491351</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>96.52800073376365</v>
+        <v>96.39398016625481</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>98.93914449718068</v>
+        <v>98.82075283382896</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>-144.3837294435407</v>
+        <v>-140.3406708132619</v>
       </c>
       <c r="I7" s="2" t="b">
         <v>1</v>
@@ -11669,7 +11669,7 @@
     <row r="8" ht="21" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>P2_carrier23</t>
+          <t>P1_two_ports_total</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -11682,25 +11682,25 @@
         <v>32</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1746.153391179678</v>
+        <v>2027.370972447764</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>83.15016148474656</v>
+        <v>96.54147487846497</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>85.49955588117076</v>
+        <v>98.95163974025233</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>-149.1549419907373</v>
+        <v>-143.3509707699017</v>
       </c>
       <c r="I8" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" ht="21" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>P1_cable78_plus5pct</t>
+          <t>P2_carrier23</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -11713,25 +11713,25 @@
         <v>32</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>2027.684880094466</v>
+        <v>1984.286349075521</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>96.55642286164122</v>
+        <v>94.48982614645337</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>98.96766572266887</v>
+        <v>96.89466910557503</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>-141.5497109615734</v>
+        <v>-148.1221833170983</v>
       </c>
       <c r="I9" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" ht="36" customHeight="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" ht="21" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>P1_geometry_uncertain_fail</t>
+          <t>P1_cable78_plus5pct</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -11744,25 +11744,25 @@
         <v>32</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>2027.698772162835</v>
+        <v>2028.27057044491</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>96.55708438870644</v>
+        <v>96.58431287832906</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>98.96832260440748</v>
+        <v>98.99620626820823</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>-141.3734294869009</v>
+        <v>-140.5402256995721</v>
       </c>
       <c r="I10" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="11" ht="21" customHeight="1">
+    <row r="11" ht="36" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>P1_closed_gaps_RF3</t>
+          <t>P1_geometry_uncertain_fail</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -11775,25 +11775,25 @@
         <v>32</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>2022.788680550294</v>
+        <v>2028.297243789426</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>96.32327050239496</v>
+        <v>96.58558303759173</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>98.74936524488473</v>
+        <v>98.9974910516087</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>-144.5230365047649</v>
+        <v>-140.3406708132619</v>
       </c>
       <c r="I11" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="12" ht="36" customHeight="1">
+    <row r="12" ht="21" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>P1_geometry_uncertain_fail_RF3</t>
+          <t>P1_closed_gaps_RF3</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -11806,25 +11806,25 @@
         <v>32</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>2027.088015409037</v>
+        <v>2023.347312149689</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>96.52800073376365</v>
+        <v>96.34987200712803</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>98.93914449718068</v>
+        <v>98.77490152247255</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>-144.3734294869009</v>
+        <v>-143.3406708132619</v>
       </c>
       <c r="I12" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="13" ht="51" customHeight="1">
+    <row r="13" ht="36" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>P1_closed_gaps_geometry_uncertain_fail_RF3</t>
+          <t>P1_geometry_uncertain_fail_RF3</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -11837,29 +11837,29 @@
         <v>32</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>2022.788680550294</v>
+        <v>2027.370972447764</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>96.32327050239496</v>
+        <v>96.54147487846497</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>98.74936524488473</v>
+        <v>98.95163974025233</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>-144.5230365047649</v>
+        <v>-143.3406708132619</v>
       </c>
       <c r="I13" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="14" ht="21" customHeight="1">
+    <row r="14" ht="51" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>P1_n2.5</t>
+          <t>P1_closed_gaps_geometry_uncertain_fail_RF3</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>2100</v>
+        <v>1800</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>0.25</v>
@@ -11868,16 +11868,16 @@
         <v>32</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>2027.641467380811</v>
+        <v>2023.347312149689</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>96.55435558956242</v>
+        <v>96.34987200712803</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>98.96561296723577</v>
+        <v>98.77490152247255</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>-141.8127665734568</v>
+        <v>-143.3406708132619</v>
       </c>
       <c r="I14" s="2" t="b">
         <v>1</v>
@@ -11886,7 +11886,7 @@
     <row r="15" ht="21" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>P1_n2</t>
+          <t>P1_n2.5</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -11899,16 +11899,16 @@
         <v>32</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>2034.713154428414</v>
+        <v>2028.27057044491</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>96.89110259182925</v>
+        <v>96.58431287832906</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>99.25765003018137</v>
+        <v>98.99620626820823</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>-137.008872530488</v>
+        <v>-140.7826002884914</v>
       </c>
       <c r="I15" s="2" t="b">
         <v>1</v>
@@ -11917,7 +11917,7 @@
     <row r="16" ht="21" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>P1_n3</t>
+          <t>P1_n2</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -11930,25 +11930,25 @@
         <v>32</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1918.419650614274</v>
+        <v>2032.161034579611</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>91.35331669591783</v>
+        <v>96.7695730752196</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>93.735532136248</v>
+        <v>99.16526154565324</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>-146.616652987031</v>
+        <v>-136.1920164872219</v>
       </c>
       <c r="I16" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" ht="21" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>P1_extra_RF_3dB</t>
+          <t>P1_n3</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -11961,16 +11961,16 @@
         <v>32</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>2026.496413134856</v>
+        <v>2025.453213426999</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>96.49982919689791</v>
+        <v>96.4501530203333</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>98.91119804321372</v>
+        <v>98.86001017751462</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>-144.8127665734568</v>
+        <v>-145.3731879044582</v>
       </c>
       <c r="I17" s="2" t="b">
         <v>1</v>
@@ -11979,7 +11979,7 @@
     <row r="18" ht="21" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>P1_closed_gaps</t>
+          <t>P1_n3_closed_gaps</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -11992,16 +11992,16 @@
         <v>32</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>2023.569410846496</v>
+        <v>2016.509243678576</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>96.36044813554744</v>
+        <v>96.0242496989798</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>98.78658049338374</v>
+        <v>98.4472775351195</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>-141.9649659799945</v>
+        <v>-145.3731879044582</v>
       </c>
       <c r="I18" s="2" t="b">
         <v>1</v>
@@ -12010,7 +12010,7 @@
     <row r="19" ht="21" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>P1_two_ports_total</t>
+          <t>P1_extra_RF_3dB</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -12023,16 +12023,16 @@
         <v>32</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>2026.404288470194</v>
+        <v>2027.293222843391</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>96.49544230810447</v>
+        <v>96.53777251635194</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>98.90685103170834</v>
+        <v>98.94789648034488</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>-144.8230665300966</v>
+        <v>-143.7826002884914</v>
       </c>
       <c r="I19" s="2" t="b">
         <v>1</v>
@@ -12041,7 +12041,7 @@
     <row r="20" ht="21" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>P2_carrier23</t>
+          <t>P1_closed_gaps</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -12054,25 +12054,25 @@
         <v>32</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>1700.682116278469</v>
+        <v>2024.246910146835</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>80.98486267992712</v>
+        <v>96.39271000699216</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>83.33438190052263</v>
+        <v>98.81946805042847</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>-149.5942790772932</v>
+        <v>-140.7826002884914</v>
       </c>
       <c r="I20" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" ht="21" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>P1_cable78_plus5pct</t>
+          <t>P1_two_ports_total</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -12085,25 +12085,25 @@
         <v>32</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>2027.598054667156</v>
+        <v>2027.249737346482</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>96.55228831748363</v>
+        <v>96.53570177840389</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>98.96356021180269</v>
+        <v>98.94596447523138</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>-142.0046122474286</v>
+        <v>-143.7929002451312</v>
       </c>
       <c r="I21" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="22" ht="36" customHeight="1">
+    <row r="22" ht="21" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>P1_geometry_uncertain_fail</t>
+          <t>P2_carrier23</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -12116,25 +12116,25 @@
         <v>32</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>2027.641467380811</v>
+        <v>1963.842690107272</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>96.55435558956242</v>
+        <v>93.51631857653675</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>98.96561296723577</v>
+        <v>95.92222814177863</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>-141.8127665734568</v>
+        <v>-148.5641127923279</v>
       </c>
       <c r="I22" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" ht="21" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>P1_closed_gaps_RF3</t>
+          <t>P1_cable78_plus5pct</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
@@ -12147,16 +12147,16 @@
         <v>32</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>2022.158772940536</v>
+        <v>2028.27057044491</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>96.29327490193027</v>
+        <v>96.58431287832906</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>98.71960753612386</v>
+        <v>98.99620626820823</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>-144.9649659799945</v>
+        <v>-140.9997742242648</v>
       </c>
       <c r="I23" s="2" t="b">
         <v>1</v>
@@ -12165,7 +12165,7 @@
     <row r="24" ht="36" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>P1_geometry_uncertain_fail_RF3</t>
+          <t>P1_geometry_uncertain_fail</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -12178,25 +12178,25 @@
         <v>32</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>2026.496413134856</v>
+        <v>2028.27057044491</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>96.49982919689791</v>
+        <v>96.58431287832906</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>98.91119804321372</v>
+        <v>98.99620626820823</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>-144.8127665734568</v>
+        <v>-140.7826002884914</v>
       </c>
       <c r="I24" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="25" ht="51" customHeight="1">
+    <row r="25" ht="21" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>P1_closed_gaps_geometry_uncertain_fail_RF3</t>
+          <t>P1_closed_gaps_RF3</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
@@ -12209,29 +12209,29 @@
         <v>32</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>2022.158772940536</v>
+        <v>2023.269562545315</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>96.29327490193027</v>
+        <v>96.34616964501501</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>98.71960753612386</v>
+        <v>98.77115826256512</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>-144.9649659799945</v>
+        <v>-143.7826002884914</v>
       </c>
       <c r="I25" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="26" ht="21" customHeight="1">
+    <row r="26" ht="36" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>P1_n2.5</t>
+          <t>P1_geometry_uncertain_fail_RF3</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>2600</v>
+        <v>2100</v>
       </c>
       <c r="C26" s="2" t="n">
         <v>0.25</v>
@@ -12240,29 +12240,29 @@
         <v>32</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>2027.58989988568</v>
+        <v>2027.293222843391</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>96.55189999455619</v>
+        <v>96.53777251635194</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>98.96316898076721</v>
+        <v>98.94789648034488</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>-142.4539141997538</v>
+        <v>-143.7826002884914</v>
       </c>
       <c r="I26" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="27" ht="21" customHeight="1">
+    <row r="27" ht="51" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>P1_n2</t>
+          <t>P1_closed_gaps_geometry_uncertain_fail_RF3</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>2600</v>
+        <v>2100</v>
       </c>
       <c r="C27" s="2" t="n">
         <v>0.25</v>
@@ -12271,16 +12271,16 @@
         <v>32</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>2031.672243827987</v>
+        <v>2023.269562545315</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>96.74629732514222</v>
+        <v>96.34616964501501</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>99.1394306372856</v>
+        <v>98.77115826256512</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>-137.6500201567851</v>
+        <v>-143.7826002884914</v>
       </c>
       <c r="I27" s="2" t="b">
         <v>1</v>
@@ -12289,7 +12289,7 @@
     <row r="28" ht="21" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>P1_n3</t>
+          <t>P1_n2.5</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -12302,25 +12302,25 @@
         <v>32</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>1887.925845208622</v>
+        <v>2028.27057044491</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>89.9012307242201</v>
+        <v>96.58431287832906</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>92.27353073671341</v>
+        <v>98.99620626820823</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>-147.2578082427226</v>
+        <v>-141.4283202015712</v>
       </c>
       <c r="I28" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" ht="21" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>P1_extra_RF_3dB</t>
+          <t>P1_n2</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
@@ -12333,16 +12333,16 @@
         <v>32</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>2022.676323625124</v>
+        <v>2031.495765114362</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>96.31792017262497</v>
+        <v>96.73789357687438</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>98.72920388791584</v>
+        <v>99.13869647534247</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>-145.4539141997538</v>
+        <v>-136.8377364003017</v>
       </c>
       <c r="I29" s="2" t="b">
         <v>1</v>
@@ -12351,7 +12351,7 @@
     <row r="30" ht="21" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>P1_closed_gaps</t>
+          <t>P1_n3</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -12364,16 +12364,16 @@
         <v>32</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>2023.56125606502</v>
+        <v>2023.667713207768</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>96.36005981262001</v>
+        <v>96.36512920036991</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>98.78618926234824</v>
+        <v>98.77464453157414</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>-142.6106858930743</v>
+        <v>-146.018907817538</v>
       </c>
       <c r="I30" s="2" t="b">
         <v>1</v>
@@ -12382,7 +12382,7 @@
     <row r="31" ht="21" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>P1_two_ports_total</t>
+          <t>P1_n3_closed_gaps</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
@@ -12395,16 +12395,16 @@
         <v>32</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>2022.613400928551</v>
+        <v>2012.940712784849</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>96.31492385374051</v>
+        <v>95.8543196564214</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>98.72618512992599</v>
+        <v>98.27642066290612</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>-145.4642141563936</v>
+        <v>-146.018907817538</v>
       </c>
       <c r="I31" s="2" t="b">
         <v>1</v>
@@ -12413,7 +12413,7 @@
     <row r="32" ht="21" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>P2_carrier23</t>
+          <t>P1_extra_RF_3dB</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -12426,25 +12426,25 @@
         <v>32</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>1635.46688428857</v>
+        <v>2026.797372186855</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>77.87937544231285</v>
+        <v>96.51416058032642</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>80.22182506240034</v>
+        <v>98.92461098871428</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>-150.2354267035903</v>
+        <v>-144.4283202015712</v>
       </c>
       <c r="I32" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" ht="21" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>P1_cable78_plus5pct</t>
+          <t>P1_closed_gaps</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
@@ -12457,25 +12457,25 @@
         <v>32</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>2027.58989988568</v>
+        <v>2024.246910146835</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>96.55189999455619</v>
+        <v>96.39271000699216</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>98.96316898076721</v>
+        <v>98.81946805042847</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>-142.6701212291506</v>
+        <v>-141.4283202015712</v>
       </c>
       <c r="I33" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="34" ht="36" customHeight="1">
+    <row r="34" ht="21" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>P1_geometry_uncertain_fail</t>
+          <t>P1_two_ports_total</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -12488,16 +12488,16 @@
         <v>32</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>2027.58989988568</v>
+        <v>2026.764733153943</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>96.55189999455619</v>
+        <v>96.51260634066394</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>98.96316898076721</v>
+        <v>98.92304123455956</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>-142.4539141997538</v>
+        <v>-144.438620158211</v>
       </c>
       <c r="I34" s="2" t="b">
         <v>1</v>
@@ -12506,7 +12506,7 @@
     <row r="35" ht="21" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>P1_closed_gaps_RF3</t>
+          <t>P2_carrier23</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
@@ -12519,25 +12519,25 @@
         <v>32</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>2018.338683430805</v>
+        <v>1925.264679477561</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>96.11136587765736</v>
+        <v>91.67927045131245</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>98.53761338082599</v>
+        <v>94.08689090412193</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>-145.6106858930743</v>
+        <v>-149.2098327054076</v>
       </c>
       <c r="I35" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" ht="36" customHeight="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" ht="21" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>P1_geometry_uncertain_fail_RF3</t>
+          <t>P1_cable78_plus5pct</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -12550,25 +12550,25 @@
         <v>32</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>2022.676323625124</v>
+        <v>2028.207869151061</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>96.31792017262497</v>
+        <v>96.58132710243146</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>98.72920388791584</v>
+        <v>98.99318751021835</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>-145.4539141997538</v>
+        <v>-141.6730717799824</v>
       </c>
       <c r="I36" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="37" ht="51" customHeight="1">
+    <row r="37" ht="36" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>P1_closed_gaps_geometry_uncertain_fail_RF3</t>
+          <t>P1_geometry_uncertain_fail</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
@@ -12581,23 +12581,116 @@
         <v>32</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>2018.338683430805</v>
+        <v>2028.27057044491</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>96.11136587765736</v>
+        <v>96.58431287832906</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>98.53761338082599</v>
+        <v>98.99620626820823</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>-145.6106858930743</v>
+        <v>-141.4283202015712</v>
       </c>
       <c r="I37" s="2" t="b">
         <v>1</v>
       </c>
     </row>
+    <row r="38" ht="21" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>P1_closed_gaps_RF3</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>2600</v>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>2022.77371188878</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>96.32255770898951</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>98.74787277093455</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>-144.4283202015712</v>
+      </c>
+      <c r="I38" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" ht="36" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>P1_geometry_uncertain_fail_RF3</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>2600</v>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>2026.797372186855</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>96.51416058032642</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>98.92461098871428</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>-144.4283202015712</v>
+      </c>
+      <c r="I39" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" ht="51" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>P1_closed_gaps_geometry_uncertain_fail_RF3</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>2600</v>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>2022.77371188878</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>96.32255770898951</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>98.74787277093455</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>-144.4283202015712</v>
+      </c>
+      <c r="I40" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I37"/>
+  <autoFilter ref="A1:I40"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
@@ -12671,10 +12764,10 @@
         <v>65.23999999999999</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>65.18034283754862</v>
+        <v>65.17538792372375</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>99.90855738434799</v>
+        <v>99.90096248271574</v>
       </c>
     </row>
     <row r="3" ht="36" customHeight="1">
@@ -12695,10 +12788,10 @@
         <v>172.94</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>172.8460985423309</v>
+        <v>172.8486065940849</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>99.94570286939455</v>
+        <v>99.94715311326756</v>
       </c>
     </row>
     <row r="4" ht="36" customHeight="1">
@@ -12719,10 +12812,10 @@
         <v>22.26</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>22.25890362503134</v>
+        <v>22.21504862628506</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>99.99507468567538</v>
+        <v>99.79806211269117</v>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1">
@@ -12767,10 +12860,10 @@
         <v>28.57</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>28.56859401088994</v>
+        <v>28.56387390459184</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>99.99507879205437</v>
+        <v>99.97855759395117</v>
       </c>
     </row>
     <row r="7" ht="21" customHeight="1">
@@ -12863,10 +12956,10 @@
         <v>18.29</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>18.00125630052306</v>
+        <v>18.23205557536852</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>98.42130290061816</v>
+        <v>99.68319067998098</v>
       </c>
     </row>
     <row r="11" ht="36" customHeight="1">
@@ -12911,10 +13004,10 @@
         <v>255.98</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>255.9718452185239</v>
+        <v>255.9636904370479</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>99.99681428960228</v>
+        <v>99.9936285792046</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1">
@@ -12959,13 +13052,13 @@
         <v>140.99</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>140.9327695519497</v>
+        <v>140.969812893104</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>99.95940815089705</v>
-      </c>
-    </row>
-    <row r="15" ht="36" customHeight="1">
+        <v>99.98568188744166</v>
+      </c>
+    </row>
+    <row r="15" ht="21" customHeight="1">
       <c r="A15" s="2" t="n">
         <v>1800</v>
       </c>
@@ -12983,10 +13076,10 @@
         <v>45.21</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>45.1665872863453</v>
+        <v>45.21</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>99.90397541770693</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1">
@@ -13175,10 +13268,10 @@
         <v>47.91</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>47.91000000000003</v>
+        <v>47.80693267618774</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>100.0000000000001</v>
+        <v>99.78487304568513</v>
       </c>
     </row>
     <row r="24" ht="36" customHeight="1">
@@ -13247,10 +13340,10 @@
         <v>31.2</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>31.17543362354052</v>
+        <v>31.1995989163027</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>99.92126161391194</v>
+        <v>99.99871447532917</v>
       </c>
     </row>
     <row r="27" ht="21" customHeight="1">
@@ -13319,10 +13412,10 @@
         <v>575.97</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>575.5447049234222</v>
+        <v>575.9700000000005</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>99.92616020338249</v>
+        <v>100.0000000000001</v>
       </c>
     </row>
     <row r="30" ht="36" customHeight="1">
@@ -13535,10 +13628,10 @@
         <v>65.23999999999999</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>65.18034283754862</v>
+        <v>65.17538792372375</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>99.90855738434799</v>
+        <v>99.90096248271574</v>
       </c>
     </row>
     <row r="39" ht="36" customHeight="1">
@@ -13583,10 +13676,10 @@
         <v>22.26</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>22.25890362503134</v>
+        <v>22.21504862628506</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>99.99507468567538</v>
+        <v>99.79806211269117</v>
       </c>
     </row>
     <row r="41" ht="36" customHeight="1">
@@ -13631,10 +13724,10 @@
         <v>28.57</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>28.56859401088994</v>
+        <v>28.56387390459184</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>99.99507879205437</v>
+        <v>99.97855759395117</v>
       </c>
     </row>
     <row r="43" ht="21" customHeight="1">
@@ -13727,10 +13820,10 @@
         <v>18.29</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>18.00125630052306</v>
+        <v>18.23205557536852</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>98.42130290061816</v>
+        <v>99.68319067998098</v>
       </c>
     </row>
     <row r="47" ht="36" customHeight="1">
@@ -13775,10 +13868,10 @@
         <v>255.98</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>255.9718452185239</v>
+        <v>255.9636904370479</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>99.99681428960228</v>
+        <v>99.9936285792046</v>
       </c>
     </row>
     <row r="49" ht="36" customHeight="1">
@@ -13823,13 +13916,13 @@
         <v>140.99</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>140.9327695519497</v>
+        <v>140.969812893104</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>99.95940815089705</v>
-      </c>
-    </row>
-    <row r="51" ht="36" customHeight="1">
+        <v>99.98568188744166</v>
+      </c>
+    </row>
+    <row r="51" ht="21" customHeight="1">
       <c r="A51" s="2" t="n">
         <v>2100</v>
       </c>
@@ -13847,10 +13940,10 @@
         <v>45.21</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>45.1092825043211</v>
+        <v>45.21</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>99.77722296908007</v>
+        <v>100</v>
       </c>
     </row>
     <row r="52" ht="36" customHeight="1">
@@ -14039,10 +14132,10 @@
         <v>47.91</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>47.91000000000003</v>
+        <v>47.80693267618774</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>100.0000000000001</v>
+        <v>99.78487304568513</v>
       </c>
     </row>
     <row r="60" ht="36" customHeight="1">
@@ -14183,10 +14276,10 @@
         <v>575.97</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>575.5447049234222</v>
+        <v>575.9700000000005</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>99.92616020338249</v>
+        <v>100.0000000000001</v>
       </c>
     </row>
     <row r="66" ht="36" customHeight="1">
@@ -14399,10 +14492,10 @@
         <v>65.23999999999999</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>65.18034283754862</v>
+        <v>65.17538792372375</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>99.90855738434799</v>
+        <v>99.90096248271574</v>
       </c>
     </row>
     <row r="75" ht="36" customHeight="1">
@@ -14447,10 +14540,10 @@
         <v>22.26</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>22.25890362503134</v>
+        <v>22.21504862628506</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>99.99507468567538</v>
+        <v>99.79806211269117</v>
       </c>
     </row>
     <row r="77" ht="36" customHeight="1">
@@ -14495,10 +14588,10 @@
         <v>28.57</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>28.56859401088994</v>
+        <v>28.56387390459184</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>99.99507879205437</v>
+        <v>99.97855759395117</v>
       </c>
     </row>
     <row r="79" ht="21" customHeight="1">
@@ -14591,10 +14684,10 @@
         <v>18.29</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>18.00125630052306</v>
+        <v>18.23205557536852</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>98.42130290061816</v>
+        <v>99.68319067998098</v>
       </c>
     </row>
     <row r="83" ht="36" customHeight="1">
@@ -14687,13 +14780,13 @@
         <v>140.99</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>140.9327695519497</v>
+        <v>140.969812893104</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>99.95940815089705</v>
-      </c>
-    </row>
-    <row r="87" ht="36" customHeight="1">
+        <v>99.98568188744166</v>
+      </c>
+    </row>
+    <row r="87" ht="21" customHeight="1">
       <c r="A87" s="2" t="n">
         <v>2600</v>
       </c>
@@ -14711,10 +14804,10 @@
         <v>45.21</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>45.06586979066641</v>
+        <v>45.21</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>99.68119838678702</v>
+        <v>100</v>
       </c>
     </row>
     <row r="88" ht="36" customHeight="1">
@@ -14903,10 +14996,10 @@
         <v>47.91</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>47.91000000000003</v>
+        <v>47.80693267618774</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>100.0000000000001</v>
+        <v>99.78487304568513</v>
       </c>
     </row>
     <row r="96" ht="36" customHeight="1">
@@ -15047,10 +15140,10 @@
         <v>575.97</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>575.5447049234222</v>
+        <v>575.9700000000005</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>99.92616020338249</v>
+        <v>100.0000000000001</v>
       </c>
     </row>
     <row r="102" ht="36" customHeight="1">
@@ -15848,12 +15941,12 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>A05:P1</t>
+          <t>A04:P1</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>A05-M1, 7/8 + джампер 3 м</t>
+          <t>A04-M1, 7/8 + джампер 3 м</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -15897,7 +15990,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>A03-M1, 1/2 + джампер 3 м</t>
+          <t>A03-M1, 7/8 + джампер 3 м</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -15914,12 +16007,12 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>A04:P1</t>
+          <t>A06:P1</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>A04-M1, 1/2 + джампер 3 м</t>
+          <t>A06-M1, 1/2 + джампер 3 м</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -15941,7 +16034,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>F1-2-M1, 7/8</t>
+          <t>F1-2-M1, джампер 3 м</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -15980,12 +16073,12 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>A06:P1</t>
+          <t>A05:P1</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>A06-M1, 1/2 + джампер 3 м</t>
+          <t>A05-M1, 7/8 + джампер 3 м</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -16068,12 +16161,12 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>A09:P1</t>
+          <t>A12:P1</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>A09-M1, 1/2 + джампер 3 м</t>
+          <t>A12-M1, 7/8 + джампер 3 м</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -16090,12 +16183,12 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>A12:P1</t>
+          <t>A14:P1</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>A12-M1, 7/8 + джампер 3 м</t>
+          <t>A14-M1, 7/8 + джампер 3 м</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -16117,7 +16210,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>F2-1-M1, джампер 3 м</t>
+          <t>F2-1-M1, 7/8</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -16134,12 +16227,12 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>A11:P1</t>
+          <t>A10:P1</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>A11-M1, 1/2 + джампер 3 м</t>
+          <t>A10-M1, 1/2 + джампер 3 м</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -16156,12 +16249,12 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>A14:P1</t>
+          <t>A11:P1</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>A14-M1, 7/8 + джампер 3 м</t>
+          <t>A11-M1, 7/8 + джампер 3 м</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -16200,12 +16293,12 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>A10:P1</t>
+          <t>A09:P1</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>A10-M1, 7/8 + джампер 3 м</t>
+          <t>A09-M1, 7/8 + джампер 3 м</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -16310,12 +16403,12 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>A20:P1</t>
+          <t>A17:P1</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>A20-M1, 7/8 + джампер 3 м</t>
+          <t>A17-M1, 1/2 + джампер 3 м</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -16332,12 +16425,12 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>A24:P1</t>
+          <t>A23:P1</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>A24-M1, 7/8 + джампер 3 м</t>
+          <t>A23-M1, 7/8 + джампер 3 м</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -16376,12 +16469,12 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>A17:P1</t>
+          <t>A19:P1</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>A17-M1, 1/2 + джампер 3 м</t>
+          <t>A19-M1, 1/2 + джампер 3 м</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -16398,12 +16491,12 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>A18:P1</t>
+          <t>A20:P1</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>A18-M1, 1/2 + джампер 3 м</t>
+          <t>A20-M1, 7/8 + джампер 3 м</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -16442,12 +16535,12 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>A19:P1</t>
+          <t>A18:P1</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>A19-M1, 7/8 + джампер 3 м</t>
+          <t>A18-M1, 1/2 + джампер 3 м</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -16508,12 +16601,12 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>A23:P1</t>
+          <t>A24:P1</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>A23-M1, 1/2 + джампер 3 м</t>
+          <t>A24-M1, 1/2 + джампер 3 м</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -16552,12 +16645,12 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>A27:P1</t>
+          <t>A26:P1</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>A27-M1, 1/2 + джампер 3 м</t>
+          <t>A26-M1, 7/8 + джампер 3 м</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -16574,12 +16667,12 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>A31:P1</t>
+          <t>A27:P1</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>A31-M1, 1/2 + джампер 3 м</t>
+          <t>A27-M1, 1/2 + джампер 3 м</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -16618,12 +16711,12 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>A26:P1</t>
+          <t>A25:P1</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>A26-M1, 1/2 + джампер 3 м</t>
+          <t>A25-M1, 1/2 + джампер 3 м</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -16640,12 +16733,12 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>A30:P1</t>
+          <t>A32:P1</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>A30-M1, 1/2 + джампер 3 м</t>
+          <t>A32-M1, 7/8 + джампер 3 м</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -16684,12 +16777,12 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>A25:P1</t>
+          <t>A28:P1</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>A25-M1, 1/2 + джампер 3 м</t>
+          <t>A28-M1, 7/8 + джампер 3 м</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -16706,12 +16799,12 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>A28:P1</t>
+          <t>A29:P1</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>A28-M1, 7/8 + джампер 3 м</t>
+          <t>A29-M1, 7/8 + джампер 3 м</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -16728,12 +16821,12 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>A29:P1</t>
+          <t>A30:P1</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>A29-M1, 7/8 + джампер 3 м</t>
+          <t>A30-M1, 7/8 + джампер 3 м</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -16750,12 +16843,12 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>A32:P1</t>
+          <t>A31:P1</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>A32-M1, 7/8 + джампер 3 м</t>
+          <t>A31-M1, 1/2 + джампер 3 м</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -17322,12 +17415,12 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>A05:P2</t>
+          <t>A04:P2</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>A05-M2, 7/8 + джампер 3 м</t>
+          <t>A04-M2, 7/8 + джампер 3 м</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -17371,7 +17464,7 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>A03-M2, 1/2 + джампер 3 м</t>
+          <t>A03-M2, 7/8 + джампер 3 м</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -17388,12 +17481,12 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>A04:P2</t>
+          <t>A06:P2</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>A04-M2, 1/2 + джампер 3 м</t>
+          <t>A06-M2, 1/2 + джампер 3 м</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -17415,7 +17508,7 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>F1-2-M2, 7/8</t>
+          <t>F1-2-M2, джампер 3 м</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -17454,12 +17547,12 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>A06:P2</t>
+          <t>A05:P2</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>A06-M2, 1/2 + джампер 3 м</t>
+          <t>A05-M2, 7/8 + джампер 3 м</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
@@ -17542,12 +17635,12 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>A09:P2</t>
+          <t>A12:P2</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>A09-M2, 1/2 + джампер 3 м</t>
+          <t>A12-M2, 7/8 + джампер 3 м</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
@@ -17564,12 +17657,12 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>A12:P2</t>
+          <t>A14:P2</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>A12-M2, 7/8 + джампер 3 м</t>
+          <t>A14-M2, 7/8 + джампер 3 м</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
@@ -17591,7 +17684,7 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>F2-1-M2, джампер 3 м</t>
+          <t>F2-1-M2, 7/8</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -17608,12 +17701,12 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>A11:P2</t>
+          <t>A10:P2</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>A11-M2, 1/2 + джампер 3 м</t>
+          <t>A10-M2, 1/2 + джампер 3 м</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
@@ -17630,12 +17723,12 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>A14:P2</t>
+          <t>A11:P2</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>A14-M2, 7/8 + джампер 3 м</t>
+          <t>A11-M2, 7/8 + джампер 3 м</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -17674,12 +17767,12 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>A10:P2</t>
+          <t>A09:P2</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>A10-M2, 7/8 + джампер 3 м</t>
+          <t>A09-M2, 7/8 + джампер 3 м</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -17784,12 +17877,12 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>A20:P2</t>
+          <t>A17:P2</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>A20-M2, 7/8 + джампер 3 м</t>
+          <t>A17-M2, 1/2 + джампер 3 м</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
@@ -17806,12 +17899,12 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>A24:P2</t>
+          <t>A23:P2</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>A24-M2, 7/8 + джампер 3 м</t>
+          <t>A23-M2, 7/8 + джампер 3 м</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -17850,12 +17943,12 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>A17:P2</t>
+          <t>A19:P2</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>A17-M2, 1/2 + джампер 3 м</t>
+          <t>A19-M2, 1/2 + джампер 3 м</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
@@ -17872,12 +17965,12 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>A18:P2</t>
+          <t>A20:P2</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>A18-M2, 1/2 + джампер 3 м</t>
+          <t>A20-M2, 7/8 + джампер 3 м</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
@@ -17916,12 +18009,12 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>A19:P2</t>
+          <t>A18:P2</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>A19-M2, 7/8 + джампер 3 м</t>
+          <t>A18-M2, 1/2 + джампер 3 м</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
@@ -17982,12 +18075,12 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>A23:P2</t>
+          <t>A24:P2</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>A23-M2, 1/2 + джампер 3 м</t>
+          <t>A24-M2, 1/2 + джампер 3 м</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
@@ -18026,12 +18119,12 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>A27:P2</t>
+          <t>A26:P2</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>A27-M2, 1/2 + джампер 3 м</t>
+          <t>A26-M2, 7/8 + джампер 3 м</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
@@ -18048,12 +18141,12 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>A31:P2</t>
+          <t>A27:P2</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>A31-M2, 1/2 + джампер 3 м</t>
+          <t>A27-M2, 1/2 + джампер 3 м</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
@@ -18092,12 +18185,12 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>A26:P2</t>
+          <t>A25:P2</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>A26-M2, 1/2 + джампер 3 м</t>
+          <t>A25-M2, 1/2 + джампер 3 м</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
@@ -18114,12 +18207,12 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>A30:P2</t>
+          <t>A32:P2</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>A30-M2, 1/2 + джампер 3 м</t>
+          <t>A32-M2, 7/8 + джампер 3 м</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
@@ -18158,12 +18251,12 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>A25:P2</t>
+          <t>A28:P2</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>A25-M2, 1/2 + джампер 3 м</t>
+          <t>A28-M2, 7/8 + джампер 3 м</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
@@ -18180,12 +18273,12 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>A28:P2</t>
+          <t>A29:P2</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>A28-M2, 7/8 + джампер 3 м</t>
+          <t>A29-M2, 7/8 + джампер 3 м</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
@@ -18202,12 +18295,12 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>A29:P2</t>
+          <t>A30:P2</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>A29-M2, 7/8 + джампер 3 м</t>
+          <t>A30-M2, 7/8 + джампер 3 м</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
@@ -18224,12 +18317,12 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>A32:P2</t>
+          <t>A31:P2</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>A32-M2, 7/8 + джампер 3 м</t>
+          <t>A31-M2, 1/2 + джампер 3 м</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
@@ -18462,7 +18555,7 @@
         <v>11.40886</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>49</v>
+        <v>43.21100027232224</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -18485,7 +18578,7 @@
         <v>11.40886</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>54.232997</v>
+        <v>46.02057642602261</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -18508,7 +18601,7 @@
         <v>11.40886</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>46.02057642602261</v>
+        <v>43.21100027232224</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
@@ -18551,10 +18644,10 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>25.987715</v>
+        <v>22.63781769212248</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>49</v>
+        <v>30.542096</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
@@ -18574,10 +18667,10 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>25.987715</v>
+        <v>22.86</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>49</v>
+        <v>30.542096</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
@@ -18643,10 +18736,10 @@
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>11.839271</v>
+        <v>11.37315902428026</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>30.542096</v>
+        <v>26.486112</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
@@ -18666,10 +18759,10 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>11.839271</v>
+        <v>11.37315902428026</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>30.542096</v>
+        <v>26.486112</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
@@ -18738,7 +18831,7 @@
         <v>1.315304</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>12</v>
+        <v>16.64188377635066</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
@@ -18758,7 +18851,7 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>25.94794473608991</v>
+        <v>2.98386788680957</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>4.584693</v>
@@ -18781,10 +18874,10 @@
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>2.98386788680957</v>
+        <v>1.315304</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>4.584693</v>
+        <v>10.8684375</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
@@ -18899,7 +18992,7 @@
         <v>11.40886</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>49</v>
+        <v>43.21100027232224</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
@@ -18922,7 +19015,7 @@
         <v>11.40886</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>54.232997</v>
+        <v>46.02057642602261</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
@@ -18945,7 +19038,7 @@
         <v>11.40886</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>46.02057642602261</v>
+        <v>43.21100027232224</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
@@ -18988,10 +19081,10 @@
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>25.987715</v>
+        <v>22.63781769212248</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>49</v>
+        <v>30.542096</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
@@ -19011,10 +19104,10 @@
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>25.987715</v>
+        <v>22.86</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>49</v>
+        <v>30.542096</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
@@ -19080,10 +19173,10 @@
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>11.839271</v>
+        <v>11.37315902428026</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>30.542096</v>
+        <v>26.486112</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
@@ -19103,10 +19196,10 @@
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>11.839271</v>
+        <v>11.37315902428026</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>30.542096</v>
+        <v>26.486112</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
@@ -19175,7 +19268,7 @@
         <v>1.315304</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>12</v>
+        <v>16.64188377635066</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
@@ -19195,7 +19288,7 @@
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>25.94794473608991</v>
+        <v>2.98386788680957</v>
       </c>
       <c r="D38" s="2" t="n">
         <v>4.584693</v>
@@ -19218,10 +19311,10 @@
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>2.98386788680957</v>
+        <v>1.315304</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>4.584693</v>
+        <v>10.8684375</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
@@ -19271,11 +19364,11 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Проектная точка у метки помещения; не утверждённое место крепления</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="36" customHeight="1">
+          <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="21" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
           <t>A02</t>
@@ -19294,11 +19387,11 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Проектная позиция внутри восстановленного CAD-контура; выбранная по сценарию +3 дБ/закрытые проёмы</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="36" customHeight="1">
+          <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="21" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
           <t>A03</t>
@@ -19313,15 +19406,15 @@
         <v>17.81482442176836</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>60.42404058032748</v>
+        <v>63.42404058032748</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Проектная позиция внутри восстановленного CAD-контура; выбранная по сценарию +3 дБ/закрытые проёмы</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="36" customHeight="1">
+          <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="21" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
           <t>A04</t>
@@ -19340,7 +19433,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Проектная позиция внутри восстановленного CAD-контура; выбранная по сценарию +3 дБ/закрытые проёмы</t>
+          <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
         </is>
       </c>
     </row>
@@ -19363,7 +19456,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Проектная точка у метки помещения; не утверждённое место крепления</t>
+          <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
         </is>
       </c>
     </row>
@@ -19386,7 +19479,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Проектная точка у метки помещения; не утверждённое место крепления</t>
+          <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
         </is>
       </c>
     </row>
@@ -19409,7 +19502,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Проектная точка у метки помещения; не утверждённое место крепления</t>
+          <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
         </is>
       </c>
     </row>
@@ -19425,18 +19518,18 @@
         </is>
       </c>
       <c r="C48" s="2" t="n">
-        <v>21.15567090665015</v>
+        <v>24.15567090665015</v>
       </c>
       <c r="D48" s="2" t="n">
-        <v>43.21100027232223</v>
+        <v>40.21100027232223</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Проектная точка у метки помещения; не утверждённое место крепления</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="36" customHeight="1">
+          <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="21" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
           <t>A09</t>
@@ -19448,18 +19541,18 @@
         </is>
       </c>
       <c r="C49" s="2" t="n">
-        <v>27.69373086464296</v>
+        <v>28.58</v>
       </c>
       <c r="D49" s="2" t="n">
-        <v>50.39514233149479</v>
+        <v>50.48999999999999</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Проектная позиция внутри восстановленного CAD-контура; выбранная по сценарию +3 дБ/закрытые проёмы</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="36" customHeight="1">
+          <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="21" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
           <t>A10</t>
@@ -19471,18 +19564,18 @@
         </is>
       </c>
       <c r="C50" s="2" t="n">
-        <v>28.71498086464297</v>
+        <v>22.86</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>48.08240239668498</v>
+        <v>26.095</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Проектная позиция внутри восстановленного CAD-контура; выбранная по сценарию +3 дБ/закрытые проёмы</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="36" customHeight="1">
+          <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="21" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
           <t>A11</t>
@@ -19501,11 +19594,11 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Проектная позиция внутри восстановленного CAD-контура; выбранная по сценарию +3 дБ/закрытые проёмы</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="36" customHeight="1">
+          <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="21" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
           <t>A12</t>
@@ -19524,7 +19617,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Проектная позиция внутри восстановленного CAD-контура; выбранная по сценарию +3 дБ/закрытые проёмы</t>
+          <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
         </is>
       </c>
     </row>
@@ -19547,7 +19640,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Проектная точка у метки помещения; не утверждённое место крепления</t>
+          <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
         </is>
       </c>
     </row>
@@ -19570,7 +19663,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Проектная точка у метки помещения; не утверждённое место крепления</t>
+          <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
         </is>
       </c>
     </row>
@@ -19593,11 +19686,11 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Проектная точка у метки помещения; не утверждённое место крепления</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="36" customHeight="1">
+          <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="21" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
           <t>A16</t>
@@ -19616,11 +19709,11 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Проектная позиция внутри восстановленного CAD-контура; выбранная по сценарию +3 дБ/закрытые проёмы</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="36" customHeight="1">
+          <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="21" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
           <t>A17</t>
@@ -19632,14 +19725,14 @@
         </is>
       </c>
       <c r="C57" s="2" t="n">
-        <v>11.37315902428026</v>
+        <v>14.37315902428026</v>
       </c>
       <c r="D57" s="2" t="n">
         <v>20.56811553916096</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Проектная позиция внутри восстановленного CAD-контура; выбранная по сценарию +3 дБ/закрытые проёмы</t>
+          <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
         </is>
       </c>
     </row>
@@ -19655,14 +19748,14 @@
         </is>
       </c>
       <c r="C58" s="2" t="n">
-        <v>17.76328876497633</v>
+        <v>6.815109400363969</v>
       </c>
       <c r="D58" s="2" t="n">
-        <v>28.04576712019808</v>
+        <v>30.86086281460469</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Проектная точка у метки помещения; не утверждённое место крепления</t>
+          <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
         </is>
       </c>
     </row>
@@ -19685,7 +19778,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Проектная точка у метки помещения; не утверждённое место крепления</t>
+          <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
         </is>
       </c>
     </row>
@@ -19708,11 +19801,11 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Проектная точка у метки помещения; не утверждённое место крепления</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="36" customHeight="1">
+          <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="21" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
           <t>A21</t>
@@ -19731,7 +19824,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Проектная позиция внутри восстановленного CAD-контура; выбранная по сценарию +3 дБ/закрытые проёмы</t>
+          <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
         </is>
       </c>
     </row>
@@ -19754,7 +19847,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Проектная позиция внутри восстановленного CAD-контура; выбранная по сценарию +3 дБ/закрытые проёмы</t>
+          <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
         </is>
       </c>
     </row>
@@ -19770,14 +19863,14 @@
         </is>
       </c>
       <c r="C63" s="2" t="n">
-        <v>2.781136557840948</v>
+        <v>3.07</v>
       </c>
       <c r="D63" s="2" t="n">
-        <v>25.12117083652631</v>
+        <v>24.58</v>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Проектная точка у метки помещения; не утверждённое место крепления</t>
+          <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
         </is>
       </c>
     </row>
@@ -19800,7 +19893,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Проектная точка у метки помещения; не утверждённое место крепления</t>
+          <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
         </is>
       </c>
     </row>
@@ -19823,7 +19916,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Проектная точка у метки помещения; не утверждённое место крепления</t>
+          <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
         </is>
       </c>
     </row>
@@ -19839,18 +19932,18 @@
         </is>
       </c>
       <c r="C66" s="2" t="n">
-        <v>25.94794473608991</v>
+        <v>26.9351953125</v>
       </c>
       <c r="D66" s="2" t="n">
-        <v>13.43621536943447</v>
+        <v>12.4507421875</v>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Проектная точка у метки помещения; не утверждённое место крепления</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="36" customHeight="1">
+          <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="21" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
           <t>A27</t>
@@ -19862,14 +19955,14 @@
         </is>
       </c>
       <c r="C67" s="2" t="n">
-        <v>3.043738882363523</v>
+        <v>3.145</v>
       </c>
       <c r="D67" s="2" t="n">
-        <v>16.64188377635066</v>
+        <v>17.345</v>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Проектная позиция внутри восстановленного CAD-контура; выбранная по сценарию +3 дБ/закрытые проёмы</t>
+          <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
         </is>
       </c>
     </row>
@@ -19892,11 +19985,11 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Проектная точка у метки помещения; не утверждённое место крепления</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="36" customHeight="1">
+          <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="21" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
           <t>A29</t>
@@ -19915,7 +20008,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Проектная позиция внутри восстановленного CAD-контура; выбранная по сценарию +3 дБ/закрытые проёмы</t>
+          <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
         </is>
       </c>
     </row>
@@ -19938,11 +20031,11 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Проектная точка у метки помещения; не утверждённое место крепления</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="36" customHeight="1">
+          <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="21" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
           <t>A31</t>
@@ -19954,14 +20047,14 @@
         </is>
       </c>
       <c r="C71" s="2" t="n">
-        <v>0.6465742752551239</v>
+        <v>1.3815625</v>
       </c>
       <c r="D71" s="2" t="n">
-        <v>11.48332156603843</v>
+        <v>10.8684375</v>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Проектная позиция внутри восстановленного CAD-контура; выбранная по сценарию +3 дБ/закрытые проёмы</t>
+          <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
         </is>
       </c>
     </row>
@@ -19984,7 +20077,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Проектная точка у метки помещения; не утверждённое место крепления</t>
+          <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
         </is>
       </c>
     </row>
